--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="219">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -469,6 +469,12 @@
     <t>['39', '70', '72']</t>
   </si>
   <si>
+    <t>['64', '82']</t>
+  </si>
+  <si>
+    <t>['45+2', '80']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -662,6 +668,9 @@
   </si>
   <si>
     <t>['56']</t>
+  </si>
+  <si>
+    <t>['17', '47', '68']</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP95"/>
+  <dimension ref="A1:BP98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1279,7 +1288,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1485,7 +1494,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1563,10 +1572,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ3">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1691,7 +1700,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -1772,7 +1781,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ4">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2387,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ7">
         <v>1.1</v>
@@ -2515,7 +2524,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2802,7 +2811,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ9">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2927,7 +2936,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3005,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ10">
         <v>2.1</v>
@@ -3339,7 +3348,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3545,7 +3554,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3751,7 +3760,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3832,7 +3841,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ14">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR14">
         <v>1.19</v>
@@ -3957,7 +3966,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4038,7 +4047,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ15">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>1.72</v>
@@ -4163,7 +4172,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4369,7 +4378,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4447,7 +4456,7 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ17">
         <v>2.1</v>
@@ -4575,7 +4584,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4656,7 +4665,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ18">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR18">
         <v>1.54</v>
@@ -4781,7 +4790,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -4987,7 +4996,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5065,7 +5074,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ20">
         <v>0.89</v>
@@ -5193,7 +5202,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5271,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ21">
         <v>0.8</v>
@@ -5477,10 +5486,10 @@
         <v>1.5</v>
       </c>
       <c r="AP22">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR22">
         <v>1.91</v>
@@ -5605,7 +5614,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5892,7 +5901,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ24">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>1.47</v>
@@ -6017,7 +6026,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6223,7 +6232,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6429,7 +6438,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6635,7 +6644,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7047,7 +7056,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7125,10 +7134,10 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ30">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR30">
         <v>1.62</v>
@@ -7253,7 +7262,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7537,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ32">
         <v>1.2</v>
@@ -7665,7 +7674,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7746,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="AQ33">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1.62</v>
@@ -7871,7 +7880,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -7949,10 +7958,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR34">
         <v>1.52</v>
@@ -8077,7 +8086,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8283,7 +8292,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8489,7 +8498,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8773,10 +8782,10 @@
         <v>2.33</v>
       </c>
       <c r="AP38">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ38">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR38">
         <v>2.02</v>
@@ -8901,7 +8910,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9107,7 +9116,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9519,7 +9528,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9597,10 +9606,10 @@
         <v>1.75</v>
       </c>
       <c r="AP42">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ42">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>1.36</v>
@@ -9725,7 +9734,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9803,7 +9812,7 @@
         <v>0.25</v>
       </c>
       <c r="AP43">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ43">
         <v>1.2</v>
@@ -9931,7 +9940,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10218,7 +10227,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR45">
         <v>1.73</v>
@@ -10343,7 +10352,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10549,7 +10558,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10836,7 +10845,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ48">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR48">
         <v>1.41</v>
@@ -10961,7 +10970,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11373,7 +11382,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11451,7 +11460,7 @@
         <v>0.8</v>
       </c>
       <c r="AP51">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -11579,7 +11588,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11660,7 +11669,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ52">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR52">
         <v>1.69</v>
@@ -11785,7 +11794,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11991,7 +12000,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12069,7 +12078,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ54">
         <v>2.1</v>
@@ -12197,7 +12206,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12275,7 +12284,7 @@
         <v>1.4</v>
       </c>
       <c r="AP55">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ55">
         <v>1.33</v>
@@ -12484,7 +12493,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ56">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR56">
         <v>1.95</v>
@@ -12609,7 +12618,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13021,7 +13030,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13102,7 +13111,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ59">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR59">
         <v>1.44</v>
@@ -13305,7 +13314,7 @@
         <v>0.4</v>
       </c>
       <c r="AP60">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ60">
         <v>0.8</v>
@@ -13433,7 +13442,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13639,7 +13648,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13923,7 +13932,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ63">
         <v>1.33</v>
@@ -14051,7 +14060,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14129,7 +14138,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ64">
         <v>0.8</v>
@@ -14463,7 +14472,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14544,7 +14553,7 @@
         <v>1</v>
       </c>
       <c r="AQ66">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR66">
         <v>1.6</v>
@@ -14669,7 +14678,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14747,7 +14756,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ67">
         <v>0.89</v>
@@ -14875,7 +14884,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -14956,7 +14965,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ68">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15081,7 +15090,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15287,7 +15296,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15368,7 +15377,7 @@
         <v>2</v>
       </c>
       <c r="AQ70">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR70">
         <v>1.92</v>
@@ -15493,7 +15502,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15571,7 +15580,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ71">
         <v>1.1</v>
@@ -15699,7 +15708,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15905,7 +15914,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -15986,7 +15995,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ73">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR73">
         <v>1.6</v>
@@ -16111,7 +16120,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16317,7 +16326,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16395,10 +16404,10 @@
         <v>1.29</v>
       </c>
       <c r="AP75">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ75">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR75">
         <v>1.68</v>
@@ -16523,7 +16532,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16729,7 +16738,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16935,7 +16944,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17141,7 +17150,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17219,10 +17228,10 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ79">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR79">
         <v>1.71</v>
@@ -17553,7 +17562,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q81">
         <v>3.6</v>
@@ -17634,7 +17643,7 @@
         <v>1</v>
       </c>
       <c r="AQ81">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR81">
         <v>1.63</v>
@@ -17759,7 +17768,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18377,7 +18386,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18661,7 +18670,7 @@
         <v>0.63</v>
       </c>
       <c r="AP86">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ86">
         <v>0.89</v>
@@ -18789,7 +18798,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -18867,10 +18876,10 @@
         <v>1.88</v>
       </c>
       <c r="AP87">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ87">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR87">
         <v>1.73</v>
@@ -18995,7 +19004,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19201,7 +19210,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19282,7 +19291,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ89">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>1.97</v>
@@ -19407,7 +19416,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19485,7 +19494,7 @@
         <v>1.13</v>
       </c>
       <c r="AP90">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ90">
         <v>1.33</v>
@@ -19613,7 +19622,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19819,7 +19828,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20025,7 +20034,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20231,7 +20240,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20594,6 +20603,624 @@
       </c>
       <c r="BP95">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7776408</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45688.64583333334</v>
+      </c>
+      <c r="F96">
+        <v>20</v>
+      </c>
+      <c r="G96" t="s">
+        <v>71</v>
+      </c>
+      <c r="H96" t="s">
+        <v>79</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1</v>
+      </c>
+      <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="L96">
+        <v>2</v>
+      </c>
+      <c r="M96">
+        <v>3</v>
+      </c>
+      <c r="N96">
+        <v>5</v>
+      </c>
+      <c r="O96" t="s">
+        <v>151</v>
+      </c>
+      <c r="P96" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q96">
+        <v>3.75</v>
+      </c>
+      <c r="R96">
+        <v>2.2</v>
+      </c>
+      <c r="S96">
+        <v>2.6</v>
+      </c>
+      <c r="T96">
+        <v>1.34</v>
+      </c>
+      <c r="U96">
+        <v>3.24</v>
+      </c>
+      <c r="V96">
+        <v>2.7</v>
+      </c>
+      <c r="W96">
+        <v>1.46</v>
+      </c>
+      <c r="X96">
+        <v>6.4</v>
+      </c>
+      <c r="Y96">
+        <v>1.1</v>
+      </c>
+      <c r="Z96">
+        <v>4.1</v>
+      </c>
+      <c r="AA96">
+        <v>3.7</v>
+      </c>
+      <c r="AB96">
+        <v>1.77</v>
+      </c>
+      <c r="AC96">
+        <v>1.01</v>
+      </c>
+      <c r="AD96">
+        <v>11</v>
+      </c>
+      <c r="AE96">
+        <v>1.21</v>
+      </c>
+      <c r="AF96">
+        <v>3.58</v>
+      </c>
+      <c r="AG96">
+        <v>1.77</v>
+      </c>
+      <c r="AH96">
+        <v>1.98</v>
+      </c>
+      <c r="AI96">
+        <v>1.73</v>
+      </c>
+      <c r="AJ96">
+        <v>2</v>
+      </c>
+      <c r="AK96">
+        <v>1.95</v>
+      </c>
+      <c r="AL96">
+        <v>1.22</v>
+      </c>
+      <c r="AM96">
+        <v>1.18</v>
+      </c>
+      <c r="AN96">
+        <v>0.63</v>
+      </c>
+      <c r="AO96">
+        <v>1.78</v>
+      </c>
+      <c r="AP96">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ96">
+        <v>1.9</v>
+      </c>
+      <c r="AR96">
+        <v>1.68</v>
+      </c>
+      <c r="AS96">
+        <v>1.77</v>
+      </c>
+      <c r="AT96">
+        <v>3.45</v>
+      </c>
+      <c r="AU96">
+        <v>6</v>
+      </c>
+      <c r="AV96">
+        <v>9</v>
+      </c>
+      <c r="AW96">
+        <v>3</v>
+      </c>
+      <c r="AX96">
+        <v>9</v>
+      </c>
+      <c r="AY96">
+        <v>9</v>
+      </c>
+      <c r="AZ96">
+        <v>18</v>
+      </c>
+      <c r="BA96">
+        <v>6</v>
+      </c>
+      <c r="BB96">
+        <v>5</v>
+      </c>
+      <c r="BC96">
+        <v>11</v>
+      </c>
+      <c r="BD96">
+        <v>2.85</v>
+      </c>
+      <c r="BE96">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF96">
+        <v>1.53</v>
+      </c>
+      <c r="BG96">
+        <v>1.25</v>
+      </c>
+      <c r="BH96">
+        <v>3.98</v>
+      </c>
+      <c r="BI96">
+        <v>1.32</v>
+      </c>
+      <c r="BJ96">
+        <v>2.88</v>
+      </c>
+      <c r="BK96">
+        <v>2.2</v>
+      </c>
+      <c r="BL96">
+        <v>2.14</v>
+      </c>
+      <c r="BM96">
+        <v>1.97</v>
+      </c>
+      <c r="BN96">
+        <v>1.71</v>
+      </c>
+      <c r="BO96">
+        <v>2.52</v>
+      </c>
+      <c r="BP96">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7776409</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45688.64583333334</v>
+      </c>
+      <c r="F97">
+        <v>20</v>
+      </c>
+      <c r="G97" t="s">
+        <v>75</v>
+      </c>
+      <c r="H97" t="s">
+        <v>77</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>1</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="O97" t="s">
+        <v>147</v>
+      </c>
+      <c r="P97" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q97">
+        <v>2.88</v>
+      </c>
+      <c r="R97">
+        <v>2.2</v>
+      </c>
+      <c r="S97">
+        <v>3.25</v>
+      </c>
+      <c r="T97">
+        <v>1.32</v>
+      </c>
+      <c r="U97">
+        <v>3.2</v>
+      </c>
+      <c r="V97">
+        <v>2.62</v>
+      </c>
+      <c r="W97">
+        <v>1.45</v>
+      </c>
+      <c r="X97">
+        <v>6.9</v>
+      </c>
+      <c r="Y97">
+        <v>1.08</v>
+      </c>
+      <c r="Z97">
+        <v>2.43</v>
+      </c>
+      <c r="AA97">
+        <v>3.4</v>
+      </c>
+      <c r="AB97">
+        <v>2.7</v>
+      </c>
+      <c r="AC97">
+        <v>1.01</v>
+      </c>
+      <c r="AD97">
+        <v>11</v>
+      </c>
+      <c r="AE97">
+        <v>1.18</v>
+      </c>
+      <c r="AF97">
+        <v>3.92</v>
+      </c>
+      <c r="AG97">
+        <v>1.75</v>
+      </c>
+      <c r="AH97">
+        <v>2.01</v>
+      </c>
+      <c r="AI97">
+        <v>1.62</v>
+      </c>
+      <c r="AJ97">
+        <v>2.2</v>
+      </c>
+      <c r="AK97">
+        <v>1.42</v>
+      </c>
+      <c r="AL97">
+        <v>1.25</v>
+      </c>
+      <c r="AM97">
+        <v>1.5</v>
+      </c>
+      <c r="AN97">
+        <v>1.22</v>
+      </c>
+      <c r="AO97">
+        <v>1.11</v>
+      </c>
+      <c r="AP97">
+        <v>1.4</v>
+      </c>
+      <c r="AQ97">
+        <v>1</v>
+      </c>
+      <c r="AR97">
+        <v>1.69</v>
+      </c>
+      <c r="AS97">
+        <v>1.74</v>
+      </c>
+      <c r="AT97">
+        <v>3.43</v>
+      </c>
+      <c r="AU97">
+        <v>10</v>
+      </c>
+      <c r="AV97">
+        <v>2</v>
+      </c>
+      <c r="AW97">
+        <v>8</v>
+      </c>
+      <c r="AX97">
+        <v>4</v>
+      </c>
+      <c r="AY97">
+        <v>18</v>
+      </c>
+      <c r="AZ97">
+        <v>6</v>
+      </c>
+      <c r="BA97">
+        <v>7</v>
+      </c>
+      <c r="BB97">
+        <v>3</v>
+      </c>
+      <c r="BC97">
+        <v>10</v>
+      </c>
+      <c r="BD97">
+        <v>1.92</v>
+      </c>
+      <c r="BE97">
+        <v>5.95</v>
+      </c>
+      <c r="BF97">
+        <v>2.33</v>
+      </c>
+      <c r="BG97">
+        <v>1.41</v>
+      </c>
+      <c r="BH97">
+        <v>2.52</v>
+      </c>
+      <c r="BI97">
+        <v>1.77</v>
+      </c>
+      <c r="BJ97">
+        <v>1.9</v>
+      </c>
+      <c r="BK97">
+        <v>2.26</v>
+      </c>
+      <c r="BL97">
+        <v>1.51</v>
+      </c>
+      <c r="BM97">
+        <v>3.08</v>
+      </c>
+      <c r="BN97">
+        <v>1.28</v>
+      </c>
+      <c r="BO97">
+        <v>4.85</v>
+      </c>
+      <c r="BP97">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7776410</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45688.67708333334</v>
+      </c>
+      <c r="F98">
+        <v>20</v>
+      </c>
+      <c r="G98" t="s">
+        <v>78</v>
+      </c>
+      <c r="H98" t="s">
+        <v>70</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>2</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>2</v>
+      </c>
+      <c r="O98" t="s">
+        <v>152</v>
+      </c>
+      <c r="P98" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q98">
+        <v>2.75</v>
+      </c>
+      <c r="R98">
+        <v>2.25</v>
+      </c>
+      <c r="S98">
+        <v>3.25</v>
+      </c>
+      <c r="T98">
+        <v>1.3</v>
+      </c>
+      <c r="U98">
+        <v>3.32</v>
+      </c>
+      <c r="V98">
+        <v>2.51</v>
+      </c>
+      <c r="W98">
+        <v>1.49</v>
+      </c>
+      <c r="X98">
+        <v>6.45</v>
+      </c>
+      <c r="Y98">
+        <v>1.09</v>
+      </c>
+      <c r="Z98">
+        <v>2.34</v>
+      </c>
+      <c r="AA98">
+        <v>3.45</v>
+      </c>
+      <c r="AB98">
+        <v>2.75</v>
+      </c>
+      <c r="AC98">
+        <v>1.01</v>
+      </c>
+      <c r="AD98">
+        <v>11</v>
+      </c>
+      <c r="AE98">
+        <v>1.16</v>
+      </c>
+      <c r="AF98">
+        <v>4.2</v>
+      </c>
+      <c r="AG98">
+        <v>1.67</v>
+      </c>
+      <c r="AH98">
+        <v>2.1</v>
+      </c>
+      <c r="AI98">
+        <v>1.57</v>
+      </c>
+      <c r="AJ98">
+        <v>2.25</v>
+      </c>
+      <c r="AK98">
+        <v>1.39</v>
+      </c>
+      <c r="AL98">
+        <v>1.24</v>
+      </c>
+      <c r="AM98">
+        <v>1.55</v>
+      </c>
+      <c r="AN98">
+        <v>1.22</v>
+      </c>
+      <c r="AO98">
+        <v>1.33</v>
+      </c>
+      <c r="AP98">
+        <v>1.4</v>
+      </c>
+      <c r="AQ98">
+        <v>1.2</v>
+      </c>
+      <c r="AR98">
+        <v>1.61</v>
+      </c>
+      <c r="AS98">
+        <v>1.71</v>
+      </c>
+      <c r="AT98">
+        <v>3.32</v>
+      </c>
+      <c r="AU98">
+        <v>6</v>
+      </c>
+      <c r="AV98">
+        <v>3</v>
+      </c>
+      <c r="AW98">
+        <v>6</v>
+      </c>
+      <c r="AX98">
+        <v>8</v>
+      </c>
+      <c r="AY98">
+        <v>12</v>
+      </c>
+      <c r="AZ98">
+        <v>11</v>
+      </c>
+      <c r="BA98">
+        <v>6</v>
+      </c>
+      <c r="BB98">
+        <v>3</v>
+      </c>
+      <c r="BC98">
+        <v>9</v>
+      </c>
+      <c r="BD98">
+        <v>1.9</v>
+      </c>
+      <c r="BE98">
+        <v>6</v>
+      </c>
+      <c r="BF98">
+        <v>2.35</v>
+      </c>
+      <c r="BG98">
+        <v>1.45</v>
+      </c>
+      <c r="BH98">
+        <v>2.6</v>
+      </c>
+      <c r="BI98">
+        <v>1.81</v>
+      </c>
+      <c r="BJ98">
+        <v>1.99</v>
+      </c>
+      <c r="BK98">
+        <v>2.26</v>
+      </c>
+      <c r="BL98">
+        <v>1.6</v>
+      </c>
+      <c r="BM98">
+        <v>2.83</v>
+      </c>
+      <c r="BN98">
+        <v>1.33</v>
+      </c>
+      <c r="BO98">
+        <v>4</v>
+      </c>
+      <c r="BP98">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="221">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -473,6 +473,12 @@
   </si>
   <si>
     <t>['45+2', '80']</t>
+  </si>
+  <si>
+    <t>['-1']</t>
+  </si>
+  <si>
+    <t>['66', '82']</t>
   </si>
   <si>
     <t>['25', '90+2']</t>
@@ -1032,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP98"/>
+  <dimension ref="A1:BP100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1288,7 +1294,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1494,7 +1500,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1700,7 +1706,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -1778,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ4">
         <v>1.9</v>
@@ -2190,10 +2196,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ6">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2524,7 +2530,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2605,7 +2611,7 @@
         <v>1</v>
       </c>
       <c r="AQ8">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2936,7 +2942,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3348,7 +3354,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3554,7 +3560,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3760,7 +3766,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3838,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ14">
         <v>1.2</v>
@@ -3966,7 +3972,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4172,7 +4178,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4250,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ16">
         <v>1.2</v>
@@ -4378,7 +4384,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4584,7 +4590,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4790,7 +4796,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -4871,7 +4877,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ19">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR19">
         <v>1.52</v>
@@ -4996,7 +5002,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5077,7 +5083,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ20">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR20">
         <v>1.99</v>
@@ -5202,7 +5208,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5614,7 +5620,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5898,7 +5904,7 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6026,7 +6032,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6104,7 +6110,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6232,7 +6238,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6313,7 +6319,7 @@
         <v>2</v>
       </c>
       <c r="AQ26">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR26">
         <v>1.45</v>
@@ -6438,7 +6444,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6644,7 +6650,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7056,7 +7062,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7262,7 +7268,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7340,10 +7346,10 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ31">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR31">
         <v>1.17</v>
@@ -7674,7 +7680,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7880,7 +7886,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8086,7 +8092,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8167,7 +8173,7 @@
         <v>2</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR35">
         <v>1.63</v>
@@ -8292,7 +8298,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8370,7 +8376,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ36">
         <v>2.1</v>
@@ -8498,7 +8504,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8579,7 +8585,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ37">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -8910,7 +8916,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -8988,7 +8994,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ39">
         <v>1.1</v>
@@ -9116,7 +9122,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9528,7 +9534,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9734,7 +9740,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9940,7 +9946,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10352,7 +10358,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10430,10 +10436,10 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ46">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR46">
         <v>2</v>
@@ -10558,7 +10564,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10970,7 +10976,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11051,7 +11057,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ49">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR49">
         <v>1.57</v>
@@ -11254,7 +11260,7 @@
         <v>0.25</v>
       </c>
       <c r="AP50">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ50">
         <v>0.8</v>
@@ -11382,7 +11388,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11588,7 +11594,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11794,7 +11800,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12000,7 +12006,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12206,7 +12212,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12287,7 +12293,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ55">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR55">
         <v>1.41</v>
@@ -12490,7 +12496,7 @@
         <v>1.8</v>
       </c>
       <c r="AP56">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ56">
         <v>1.9</v>
@@ -12618,7 +12624,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12902,10 +12908,10 @@
         <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ58">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR58">
         <v>1.33</v>
@@ -13030,7 +13036,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13442,7 +13448,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13648,7 +13654,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13935,7 +13941,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ63">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR63">
         <v>1.59</v>
@@ -14060,7 +14066,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14472,7 +14478,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14678,7 +14684,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14759,7 +14765,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ67">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR67">
         <v>1.46</v>
@@ -14884,7 +14890,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -14962,7 +14968,7 @@
         <v>1.5</v>
       </c>
       <c r="AP68">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ68">
         <v>1.2</v>
@@ -15090,7 +15096,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15296,7 +15302,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15502,7 +15508,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15708,7 +15714,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15789,7 +15795,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR72">
         <v>1.68</v>
@@ -15914,7 +15920,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16120,7 +16126,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16198,7 +16204,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ74">
         <v>1.2</v>
@@ -16326,7 +16332,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16532,7 +16538,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16610,7 +16616,7 @@
         <v>1.43</v>
       </c>
       <c r="AP76">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ76">
         <v>1.1</v>
@@ -16738,7 +16744,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16944,7 +16950,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17025,7 +17031,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ78">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR78">
         <v>1.35</v>
@@ -17150,7 +17156,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17562,7 +17568,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q81">
         <v>3.6</v>
@@ -17768,7 +17774,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18258,7 +18264,7 @@
         <v>0.86</v>
       </c>
       <c r="AP84">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18386,7 +18392,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18673,7 +18679,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ86">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR86">
         <v>1.62</v>
@@ -18798,7 +18804,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19004,7 +19010,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19210,7 +19216,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19288,7 +19294,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -19416,7 +19422,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19497,7 +19503,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ90">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -19622,7 +19628,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19828,7 +19834,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20034,7 +20040,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20240,7 +20246,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20652,7 +20658,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21221,6 +21227,418 @@
       </c>
       <c r="BP98">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7776412</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45689.58333333334</v>
+      </c>
+      <c r="F99">
+        <v>20</v>
+      </c>
+      <c r="G99" t="s">
+        <v>74</v>
+      </c>
+      <c r="H99" t="s">
+        <v>76</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99">
+        <v>2</v>
+      </c>
+      <c r="O99" t="s">
+        <v>153</v>
+      </c>
+      <c r="P99" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q99">
+        <v>2.2</v>
+      </c>
+      <c r="R99">
+        <v>2.4</v>
+      </c>
+      <c r="S99">
+        <v>4.33</v>
+      </c>
+      <c r="T99">
+        <v>1.27</v>
+      </c>
+      <c r="U99">
+        <v>3.54</v>
+      </c>
+      <c r="V99">
+        <v>2.25</v>
+      </c>
+      <c r="W99">
+        <v>1.6</v>
+      </c>
+      <c r="X99">
+        <v>5.05</v>
+      </c>
+      <c r="Y99">
+        <v>1.15</v>
+      </c>
+      <c r="Z99">
+        <v>1.71</v>
+      </c>
+      <c r="AA99">
+        <v>4</v>
+      </c>
+      <c r="AB99">
+        <v>4.2</v>
+      </c>
+      <c r="AC99">
+        <v>1.01</v>
+      </c>
+      <c r="AD99">
+        <v>13</v>
+      </c>
+      <c r="AE99">
+        <v>1.12</v>
+      </c>
+      <c r="AF99">
+        <v>4.65</v>
+      </c>
+      <c r="AG99">
+        <v>1.53</v>
+      </c>
+      <c r="AH99">
+        <v>2.25</v>
+      </c>
+      <c r="AI99">
+        <v>1.57</v>
+      </c>
+      <c r="AJ99">
+        <v>2.25</v>
+      </c>
+      <c r="AK99">
+        <v>1.18</v>
+      </c>
+      <c r="AL99">
+        <v>1.19</v>
+      </c>
+      <c r="AM99">
+        <v>2.03</v>
+      </c>
+      <c r="AN99">
+        <v>2.22</v>
+      </c>
+      <c r="AO99">
+        <v>0.89</v>
+      </c>
+      <c r="AP99">
+        <v>2.1</v>
+      </c>
+      <c r="AQ99">
+        <v>0.9</v>
+      </c>
+      <c r="AR99">
+        <v>1.93</v>
+      </c>
+      <c r="AS99">
+        <v>1.34</v>
+      </c>
+      <c r="AT99">
+        <v>3.27</v>
+      </c>
+      <c r="AU99">
+        <v>6</v>
+      </c>
+      <c r="AV99">
+        <v>7</v>
+      </c>
+      <c r="AW99">
+        <v>6</v>
+      </c>
+      <c r="AX99">
+        <v>10</v>
+      </c>
+      <c r="AY99">
+        <v>12</v>
+      </c>
+      <c r="AZ99">
+        <v>17</v>
+      </c>
+      <c r="BA99">
+        <v>1</v>
+      </c>
+      <c r="BB99">
+        <v>6</v>
+      </c>
+      <c r="BC99">
+        <v>7</v>
+      </c>
+      <c r="BD99">
+        <v>1.51</v>
+      </c>
+      <c r="BE99">
+        <v>6.8</v>
+      </c>
+      <c r="BF99">
+        <v>3.24</v>
+      </c>
+      <c r="BG99">
+        <v>1.18</v>
+      </c>
+      <c r="BH99">
+        <v>3.86</v>
+      </c>
+      <c r="BI99">
+        <v>1.36</v>
+      </c>
+      <c r="BJ99">
+        <v>2.69</v>
+      </c>
+      <c r="BK99">
+        <v>1.72</v>
+      </c>
+      <c r="BL99">
+        <v>2.06</v>
+      </c>
+      <c r="BM99">
+        <v>2.15</v>
+      </c>
+      <c r="BN99">
+        <v>1.67</v>
+      </c>
+      <c r="BO99">
+        <v>2.74</v>
+      </c>
+      <c r="BP99">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7776411</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45689.58333333334</v>
+      </c>
+      <c r="F100">
+        <v>20</v>
+      </c>
+      <c r="G100" t="s">
+        <v>72</v>
+      </c>
+      <c r="H100" t="s">
+        <v>73</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>2</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>3</v>
+      </c>
+      <c r="O100" t="s">
+        <v>154</v>
+      </c>
+      <c r="P100" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q100">
+        <v>2.2</v>
+      </c>
+      <c r="R100">
+        <v>2.25</v>
+      </c>
+      <c r="S100">
+        <v>4.75</v>
+      </c>
+      <c r="T100">
+        <v>1.32</v>
+      </c>
+      <c r="U100">
+        <v>3.2</v>
+      </c>
+      <c r="V100">
+        <v>2.6</v>
+      </c>
+      <c r="W100">
+        <v>1.46</v>
+      </c>
+      <c r="X100">
+        <v>6.8</v>
+      </c>
+      <c r="Y100">
+        <v>1.08</v>
+      </c>
+      <c r="Z100">
+        <v>1.7</v>
+      </c>
+      <c r="AA100">
+        <v>3.84</v>
+      </c>
+      <c r="AB100">
+        <v>4.5</v>
+      </c>
+      <c r="AC100">
+        <v>1.01</v>
+      </c>
+      <c r="AD100">
+        <v>11</v>
+      </c>
+      <c r="AE100">
+        <v>1.17</v>
+      </c>
+      <c r="AF100">
+        <v>3.95</v>
+      </c>
+      <c r="AG100">
+        <v>1.7</v>
+      </c>
+      <c r="AH100">
+        <v>2</v>
+      </c>
+      <c r="AI100">
+        <v>1.73</v>
+      </c>
+      <c r="AJ100">
+        <v>2</v>
+      </c>
+      <c r="AK100">
+        <v>1.15</v>
+      </c>
+      <c r="AL100">
+        <v>1.21</v>
+      </c>
+      <c r="AM100">
+        <v>2.11</v>
+      </c>
+      <c r="AN100">
+        <v>1.22</v>
+      </c>
+      <c r="AO100">
+        <v>1.33</v>
+      </c>
+      <c r="AP100">
+        <v>1.4</v>
+      </c>
+      <c r="AQ100">
+        <v>1.2</v>
+      </c>
+      <c r="AR100">
+        <v>1.58</v>
+      </c>
+      <c r="AS100">
+        <v>1.51</v>
+      </c>
+      <c r="AT100">
+        <v>3.09</v>
+      </c>
+      <c r="AU100">
+        <v>3</v>
+      </c>
+      <c r="AV100">
+        <v>10</v>
+      </c>
+      <c r="AW100">
+        <v>6</v>
+      </c>
+      <c r="AX100">
+        <v>5</v>
+      </c>
+      <c r="AY100">
+        <v>9</v>
+      </c>
+      <c r="AZ100">
+        <v>15</v>
+      </c>
+      <c r="BA100">
+        <v>5</v>
+      </c>
+      <c r="BB100">
+        <v>10</v>
+      </c>
+      <c r="BC100">
+        <v>15</v>
+      </c>
+      <c r="BD100">
+        <v>1.44</v>
+      </c>
+      <c r="BE100">
+        <v>6.8</v>
+      </c>
+      <c r="BF100">
+        <v>3.62</v>
+      </c>
+      <c r="BG100">
+        <v>1.32</v>
+      </c>
+      <c r="BH100">
+        <v>2.88</v>
+      </c>
+      <c r="BI100">
+        <v>1.65</v>
+      </c>
+      <c r="BJ100">
+        <v>2.17</v>
+      </c>
+      <c r="BK100">
+        <v>2.1</v>
+      </c>
+      <c r="BL100">
+        <v>1.69</v>
+      </c>
+      <c r="BM100">
+        <v>2.47</v>
+      </c>
+      <c r="BN100">
+        <v>1.5</v>
+      </c>
+      <c r="BO100">
+        <v>3.75</v>
+      </c>
+      <c r="BP100">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -475,9 +475,6 @@
     <t>['45+2', '80']</t>
   </si>
   <si>
-    <t>['-1']</t>
-  </si>
-  <si>
     <t>['66', '82']</t>
   </si>
   <si>
@@ -677,6 +674,9 @@
   </si>
   <si>
     <t>['17', '47', '68']</t>
+  </si>
+  <si>
+    <t>['55']</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1294,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1500,7 +1500,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1706,7 +1706,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2530,7 +2530,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2942,7 +2942,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3354,7 +3354,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3560,7 +3560,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3766,7 +3766,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3972,7 +3972,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4178,7 +4178,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4384,7 +4384,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4590,7 +4590,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4796,7 +4796,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5002,7 +5002,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5208,7 +5208,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5620,7 +5620,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6032,7 +6032,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6238,7 +6238,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6444,7 +6444,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6650,7 +6650,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7062,7 +7062,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7268,7 +7268,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7680,7 +7680,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7886,7 +7886,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8092,7 +8092,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8298,7 +8298,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8504,7 +8504,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8916,7 +8916,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9122,7 +9122,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9534,7 +9534,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9740,7 +9740,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9946,7 +9946,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10358,7 +10358,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10564,7 +10564,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10976,7 +10976,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11388,7 +11388,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11594,7 +11594,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11800,7 +11800,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12006,7 +12006,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12212,7 +12212,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12624,7 +12624,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13036,7 +13036,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13448,7 +13448,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13654,7 +13654,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -14066,7 +14066,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14478,7 +14478,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14684,7 +14684,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14890,7 +14890,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15096,7 +15096,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15302,7 +15302,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15508,7 +15508,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15714,7 +15714,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15920,7 +15920,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16126,7 +16126,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16332,7 +16332,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16538,7 +16538,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16744,7 +16744,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16950,7 +16950,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17156,7 +17156,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17568,7 +17568,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q81">
         <v>3.6</v>
@@ -17774,7 +17774,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18392,7 +18392,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18804,7 +18804,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19010,7 +19010,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19216,7 +19216,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19422,7 +19422,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19628,7 +19628,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19834,7 +19834,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20040,7 +20040,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20246,7 +20246,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20658,7 +20658,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21273,10 +21273,10 @@
         <v>2</v>
       </c>
       <c r="O99" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="P99" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="Q99">
         <v>2.2</v>
@@ -21479,10 +21479,10 @@
         <v>3</v>
       </c>
       <c r="O100" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P100" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q100">
         <v>2.2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="221">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -475,6 +475,9 @@
     <t>['45+2', '80']</t>
   </si>
   <si>
+    <t>['-1']</t>
+  </si>
+  <si>
     <t>['66', '82']</t>
   </si>
   <si>
@@ -674,9 +677,6 @@
   </si>
   <si>
     <t>['17', '47', '68']</t>
-  </si>
-  <si>
-    <t>['55']</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP100"/>
+  <dimension ref="A1:BP101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1294,7 +1294,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1375,7 +1375,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -1706,7 +1706,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2530,7 +2530,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2942,7 +2942,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3354,7 +3354,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3560,7 +3560,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3641,7 +3641,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR13">
         <v>1.92</v>
@@ -3766,7 +3766,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3972,7 +3972,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4178,7 +4178,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4384,7 +4384,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4590,7 +4590,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4796,7 +4796,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5002,7 +5002,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5208,7 +5208,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5286,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ21">
         <v>0.8</v>
@@ -5620,7 +5620,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6032,7 +6032,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6113,7 +6113,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR25">
         <v>1.92</v>
@@ -6238,7 +6238,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6444,7 +6444,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6650,7 +6650,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6731,7 +6731,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR28">
         <v>1.43</v>
@@ -7062,7 +7062,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7140,7 +7140,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ30">
         <v>1.9</v>
@@ -7268,7 +7268,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7680,7 +7680,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7886,7 +7886,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -7964,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ34">
         <v>1.2</v>
@@ -8092,7 +8092,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8298,7 +8298,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8504,7 +8504,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8916,7 +8916,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9122,7 +9122,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9203,7 +9203,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR40">
         <v>1.35</v>
@@ -9534,7 +9534,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9740,7 +9740,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9818,7 +9818,7 @@
         <v>0.25</v>
       </c>
       <c r="AP43">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ43">
         <v>1.2</v>
@@ -9946,7 +9946,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10358,7 +10358,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10564,7 +10564,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10976,7 +10976,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11388,7 +11388,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11469,7 +11469,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR51">
         <v>1.86</v>
@@ -11594,7 +11594,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11800,7 +11800,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12006,7 +12006,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12084,7 +12084,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ54">
         <v>2.1</v>
@@ -12212,7 +12212,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12624,7 +12624,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12705,7 +12705,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR57">
         <v>1.74</v>
@@ -13036,7 +13036,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13448,7 +13448,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13654,7 +13654,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13938,7 +13938,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ63">
         <v>1.2</v>
@@ -14066,7 +14066,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14478,7 +14478,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14684,7 +14684,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14890,7 +14890,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15096,7 +15096,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15302,7 +15302,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15508,7 +15508,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15714,7 +15714,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15920,7 +15920,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16126,7 +16126,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16332,7 +16332,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16538,7 +16538,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16744,7 +16744,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16950,7 +16950,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17156,7 +17156,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17568,7 +17568,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q81">
         <v>3.6</v>
@@ -17774,7 +17774,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18267,7 +18267,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR84">
         <v>1.62</v>
@@ -18392,7 +18392,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18676,7 +18676,7 @@
         <v>0.63</v>
       </c>
       <c r="AP86">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ86">
         <v>0.9</v>
@@ -18804,7 +18804,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19010,7 +19010,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19216,7 +19216,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19422,7 +19422,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19628,7 +19628,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19709,7 +19709,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ91">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR91">
         <v>1.62</v>
@@ -19834,7 +19834,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20040,7 +20040,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20246,7 +20246,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20658,7 +20658,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -20736,7 +20736,7 @@
         <v>1.78</v>
       </c>
       <c r="AP96">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ96">
         <v>1.9</v>
@@ -21273,10 +21273,10 @@
         <v>2</v>
       </c>
       <c r="O99" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>220</v>
+        <v>153</v>
       </c>
       <c r="Q99">
         <v>2.2</v>
@@ -21479,10 +21479,10 @@
         <v>3</v>
       </c>
       <c r="O100" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21639,6 +21639,212 @@
       </c>
       <c r="BP100">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7487408</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45692.64583333334</v>
+      </c>
+      <c r="F101">
+        <v>15</v>
+      </c>
+      <c r="G101" t="s">
+        <v>71</v>
+      </c>
+      <c r="H101" t="s">
+        <v>75</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>1</v>
+      </c>
+      <c r="N101">
+        <v>1</v>
+      </c>
+      <c r="O101" t="s">
+        <v>84</v>
+      </c>
+      <c r="P101" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q101">
+        <v>3.5</v>
+      </c>
+      <c r="R101">
+        <v>2.2</v>
+      </c>
+      <c r="S101">
+        <v>2.75</v>
+      </c>
+      <c r="T101">
+        <v>1.34</v>
+      </c>
+      <c r="U101">
+        <v>3.1</v>
+      </c>
+      <c r="V101">
+        <v>2.51</v>
+      </c>
+      <c r="W101">
+        <v>1.49</v>
+      </c>
+      <c r="X101">
+        <v>5.7</v>
+      </c>
+      <c r="Y101">
+        <v>1.12</v>
+      </c>
+      <c r="Z101">
+        <v>3.02</v>
+      </c>
+      <c r="AA101">
+        <v>3.36</v>
+      </c>
+      <c r="AB101">
+        <v>2.27</v>
+      </c>
+      <c r="AC101">
+        <v>1</v>
+      </c>
+      <c r="AD101">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE101">
+        <v>1.2</v>
+      </c>
+      <c r="AF101">
+        <v>3.55</v>
+      </c>
+      <c r="AG101">
+        <v>1.8</v>
+      </c>
+      <c r="AH101">
+        <v>1.94</v>
+      </c>
+      <c r="AI101">
+        <v>1.67</v>
+      </c>
+      <c r="AJ101">
+        <v>2.1</v>
+      </c>
+      <c r="AK101">
+        <v>1.46</v>
+      </c>
+      <c r="AL101">
+        <v>1.26</v>
+      </c>
+      <c r="AM101">
+        <v>1.45</v>
+      </c>
+      <c r="AN101">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AO101">
+        <v>1</v>
+      </c>
+      <c r="AP101">
+        <v>0.5</v>
+      </c>
+      <c r="AQ101">
+        <v>1.2</v>
+      </c>
+      <c r="AR101">
+        <v>1.64</v>
+      </c>
+      <c r="AS101">
+        <v>1.65</v>
+      </c>
+      <c r="AT101">
+        <v>3.29</v>
+      </c>
+      <c r="AU101">
+        <v>3</v>
+      </c>
+      <c r="AV101">
+        <v>6</v>
+      </c>
+      <c r="AW101">
+        <v>5</v>
+      </c>
+      <c r="AX101">
+        <v>8</v>
+      </c>
+      <c r="AY101">
+        <v>8</v>
+      </c>
+      <c r="AZ101">
+        <v>14</v>
+      </c>
+      <c r="BA101">
+        <v>4</v>
+      </c>
+      <c r="BB101">
+        <v>10</v>
+      </c>
+      <c r="BC101">
+        <v>14</v>
+      </c>
+      <c r="BD101">
+        <v>2</v>
+      </c>
+      <c r="BE101">
+        <v>7.8</v>
+      </c>
+      <c r="BF101">
+        <v>2.04</v>
+      </c>
+      <c r="BG101">
+        <v>1.28</v>
+      </c>
+      <c r="BH101">
+        <v>2.97</v>
+      </c>
+      <c r="BI101">
+        <v>1.54</v>
+      </c>
+      <c r="BJ101">
+        <v>2.14</v>
+      </c>
+      <c r="BK101">
+        <v>1.97</v>
+      </c>
+      <c r="BL101">
+        <v>1.71</v>
+      </c>
+      <c r="BM101">
+        <v>2.54</v>
+      </c>
+      <c r="BN101">
+        <v>1.38</v>
+      </c>
+      <c r="BO101">
+        <v>3.52</v>
+      </c>
+      <c r="BP101">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="222">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -677,6 +677,9 @@
   </si>
   <si>
     <t>['17', '47', '68']</t>
+  </si>
+  <si>
+    <t>['16']</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP101"/>
+  <dimension ref="A1:BP102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2405,7 +2408,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ7">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2608,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ8">
         <v>1.2</v>
@@ -3432,10 +3435,10 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ12">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR12">
         <v>1.34</v>
@@ -5701,7 +5704,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ23">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR23">
         <v>1.3</v>
@@ -6728,7 +6731,7 @@
         <v>0.33</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ28">
         <v>1.2</v>
@@ -7758,7 +7761,7 @@
         <v>1.33</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -8997,7 +9000,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ39">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR39">
         <v>1.16</v>
@@ -10024,7 +10027,7 @@
         <v>1.67</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ44">
         <v>2.1</v>
@@ -10645,7 +10648,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ47">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR47">
         <v>1.79</v>
@@ -11878,7 +11881,7 @@
         <v>0.8</v>
       </c>
       <c r="AP53">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ53">
         <v>1.2</v>
@@ -13529,7 +13532,7 @@
         <v>2</v>
       </c>
       <c r="AQ61">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -14556,7 +14559,7 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ66">
         <v>1.9</v>
@@ -15589,7 +15592,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ71">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR71">
         <v>1.83</v>
@@ -16619,7 +16622,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ76">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR76">
         <v>1.84</v>
@@ -17440,7 +17443,7 @@
         <v>0.57</v>
       </c>
       <c r="AP80">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ80">
         <v>0.8</v>
@@ -17646,7 +17649,7 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ81">
         <v>1.2</v>
@@ -18061,7 +18064,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ83">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR83">
         <v>1.62</v>
@@ -19912,7 +19915,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ92">
         <v>2.1</v>
@@ -20533,7 +20536,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ95">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR95">
         <v>1.4</v>
@@ -21845,6 +21848,212 @@
       </c>
       <c r="BP101">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7776413</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45695.64583333334</v>
+      </c>
+      <c r="F102">
+        <v>21</v>
+      </c>
+      <c r="G102" t="s">
+        <v>76</v>
+      </c>
+      <c r="H102" t="s">
+        <v>71</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>1</v>
+      </c>
+      <c r="N102">
+        <v>1</v>
+      </c>
+      <c r="O102" t="s">
+        <v>84</v>
+      </c>
+      <c r="P102" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q102">
+        <v>2.97</v>
+      </c>
+      <c r="R102">
+        <v>2.09</v>
+      </c>
+      <c r="S102">
+        <v>3.32</v>
+      </c>
+      <c r="T102">
+        <v>1.38</v>
+      </c>
+      <c r="U102">
+        <v>2.9</v>
+      </c>
+      <c r="V102">
+        <v>2.66</v>
+      </c>
+      <c r="W102">
+        <v>1.44</v>
+      </c>
+      <c r="X102">
+        <v>6.6</v>
+      </c>
+      <c r="Y102">
+        <v>1.09</v>
+      </c>
+      <c r="Z102">
+        <v>2.42</v>
+      </c>
+      <c r="AA102">
+        <v>3.28</v>
+      </c>
+      <c r="AB102">
+        <v>2.69</v>
+      </c>
+      <c r="AC102">
+        <v>1.01</v>
+      </c>
+      <c r="AD102">
+        <v>9</v>
+      </c>
+      <c r="AE102">
+        <v>1.23</v>
+      </c>
+      <c r="AF102">
+        <v>3.42</v>
+      </c>
+      <c r="AG102">
+        <v>1.82</v>
+      </c>
+      <c r="AH102">
+        <v>1.92</v>
+      </c>
+      <c r="AI102">
+        <v>1.63</v>
+      </c>
+      <c r="AJ102">
+        <v>2.09</v>
+      </c>
+      <c r="AK102">
+        <v>1.4</v>
+      </c>
+      <c r="AL102">
+        <v>1.28</v>
+      </c>
+      <c r="AM102">
+        <v>1.48</v>
+      </c>
+      <c r="AN102">
+        <v>1</v>
+      </c>
+      <c r="AO102">
+        <v>1.1</v>
+      </c>
+      <c r="AP102">
+        <v>0.91</v>
+      </c>
+      <c r="AQ102">
+        <v>1.27</v>
+      </c>
+      <c r="AR102">
+        <v>1.56</v>
+      </c>
+      <c r="AS102">
+        <v>1.33</v>
+      </c>
+      <c r="AT102">
+        <v>2.89</v>
+      </c>
+      <c r="AU102">
+        <v>7</v>
+      </c>
+      <c r="AV102">
+        <v>2</v>
+      </c>
+      <c r="AW102">
+        <v>10</v>
+      </c>
+      <c r="AX102">
+        <v>2</v>
+      </c>
+      <c r="AY102">
+        <v>23</v>
+      </c>
+      <c r="AZ102">
+        <v>5</v>
+      </c>
+      <c r="BA102">
+        <v>12</v>
+      </c>
+      <c r="BB102">
+        <v>1</v>
+      </c>
+      <c r="BC102">
+        <v>13</v>
+      </c>
+      <c r="BD102">
+        <v>1.93</v>
+      </c>
+      <c r="BE102">
+        <v>6.35</v>
+      </c>
+      <c r="BF102">
+        <v>2.26</v>
+      </c>
+      <c r="BG102">
+        <v>1.18</v>
+      </c>
+      <c r="BH102">
+        <v>3.84</v>
+      </c>
+      <c r="BI102">
+        <v>1.37</v>
+      </c>
+      <c r="BJ102">
+        <v>2.66</v>
+      </c>
+      <c r="BK102">
+        <v>1.72</v>
+      </c>
+      <c r="BL102">
+        <v>2.08</v>
+      </c>
+      <c r="BM102">
+        <v>2.15</v>
+      </c>
+      <c r="BN102">
+        <v>1.68</v>
+      </c>
+      <c r="BO102">
+        <v>2.78</v>
+      </c>
+      <c r="BP102">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -481,6 +481,12 @@
     <t>['66', '82']</t>
   </si>
   <si>
+    <t>['36', '63']</t>
+  </si>
+  <si>
+    <t>['2', '10']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -680,6 +686,12 @@
   </si>
   <si>
     <t>['16']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['50', '57', '67', '72']</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP102"/>
+  <dimension ref="A1:BP104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1297,7 +1309,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1503,7 +1515,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1709,7 +1721,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2405,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ7">
         <v>1.27</v>
@@ -2533,7 +2545,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2817,10 +2829,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ9">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2945,7 +2957,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3026,7 +3038,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ10">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3357,7 +3369,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3563,7 +3575,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3769,7 +3781,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3850,7 +3862,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ14">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR14">
         <v>1.19</v>
@@ -3975,7 +3987,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4181,7 +4193,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4387,7 +4399,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4465,10 +4477,10 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ17">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR17">
         <v>1.81</v>
@@ -4593,7 +4605,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4671,7 +4683,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ18">
         <v>1.9</v>
@@ -4799,7 +4811,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5005,7 +5017,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5211,7 +5223,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5498,7 +5510,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ22">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR22">
         <v>1.91</v>
@@ -5623,7 +5635,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6035,7 +6047,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6241,7 +6253,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6447,7 +6459,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6653,7 +6665,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6937,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ29">
         <v>1.2</v>
@@ -7065,7 +7077,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7271,7 +7283,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7555,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ32">
         <v>1.2</v>
@@ -7683,7 +7695,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7889,7 +7901,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -7970,7 +7982,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ34">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR34">
         <v>1.52</v>
@@ -8095,7 +8107,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8301,7 +8313,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8382,7 +8394,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ36">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR36">
         <v>2.16</v>
@@ -8507,7 +8519,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8919,7 +8931,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9125,7 +9137,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9409,7 +9421,7 @@
         <v>0.33</v>
       </c>
       <c r="AP41">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ41">
         <v>0.8</v>
@@ -9537,7 +9549,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9615,7 +9627,7 @@
         <v>1.75</v>
       </c>
       <c r="AP42">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -9743,7 +9755,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9949,7 +9961,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10030,7 +10042,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ44">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -10236,7 +10248,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR45">
         <v>1.73</v>
@@ -10361,7 +10373,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10567,7 +10579,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10979,7 +10991,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11057,7 +11069,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ49">
         <v>0.9</v>
@@ -11391,7 +11403,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11597,7 +11609,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11803,7 +11815,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12009,7 +12021,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12090,7 +12102,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ54">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR54">
         <v>1.69</v>
@@ -12215,7 +12227,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12293,7 +12305,7 @@
         <v>1.4</v>
       </c>
       <c r="AP55">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ55">
         <v>1.2</v>
@@ -12627,7 +12639,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12705,7 +12717,7 @@
         <v>0.83</v>
       </c>
       <c r="AP57">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ57">
         <v>1.2</v>
@@ -13039,7 +13051,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13120,7 +13132,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ59">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR59">
         <v>1.44</v>
@@ -13451,7 +13463,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13657,7 +13669,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -14069,7 +14081,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14147,7 +14159,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ64">
         <v>0.8</v>
@@ -14353,10 +14365,10 @@
         <v>2.2</v>
       </c>
       <c r="AP65">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ65">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR65">
         <v>1.81</v>
@@ -14481,7 +14493,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14687,7 +14699,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14765,7 +14777,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ67">
         <v>0.9</v>
@@ -14893,7 +14905,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -14974,7 +14986,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ68">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15099,7 +15111,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15180,7 +15192,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR69">
         <v>1.4</v>
@@ -15305,7 +15317,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15511,7 +15523,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15717,7 +15729,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15795,7 +15807,7 @@
         <v>1.14</v>
       </c>
       <c r="AP72">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ72">
         <v>1.2</v>
@@ -15923,7 +15935,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16129,7 +16141,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16335,7 +16347,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16413,10 +16425,10 @@
         <v>1.29</v>
       </c>
       <c r="AP75">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ75">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR75">
         <v>1.68</v>
@@ -16541,7 +16553,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16747,7 +16759,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16828,7 +16840,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR77">
         <v>1.89</v>
@@ -16953,7 +16965,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17159,7 +17171,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17571,7 +17583,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q81">
         <v>3.6</v>
@@ -17652,7 +17664,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ81">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR81">
         <v>1.63</v>
@@ -17777,7 +17789,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18061,7 +18073,7 @@
         <v>1.38</v>
       </c>
       <c r="AP83">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ83">
         <v>1.27</v>
@@ -18395,7 +18407,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18807,7 +18819,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -18885,7 +18897,7 @@
         <v>1.88</v>
       </c>
       <c r="AP87">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ87">
         <v>1.9</v>
@@ -19013,7 +19025,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19094,7 +19106,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ88">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR88">
         <v>1.6</v>
@@ -19219,7 +19231,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19425,7 +19437,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19631,7 +19643,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19837,7 +19849,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -19918,7 +19930,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ92">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR92">
         <v>1.59</v>
@@ -20043,7 +20055,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20121,7 +20133,7 @@
         <v>1.22</v>
       </c>
       <c r="AP93">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ93">
         <v>1.2</v>
@@ -20249,7 +20261,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20661,7 +20673,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -20945,7 +20957,7 @@
         <v>1.11</v>
       </c>
       <c r="AP97">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21154,7 +21166,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ98">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR98">
         <v>1.61</v>
@@ -21485,7 +21497,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21897,7 +21909,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22054,6 +22066,418 @@
       </c>
       <c r="BP102">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7776414</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45695.67708333334</v>
+      </c>
+      <c r="F103">
+        <v>21</v>
+      </c>
+      <c r="G103" t="s">
+        <v>77</v>
+      </c>
+      <c r="H103" t="s">
+        <v>70</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
+      </c>
+      <c r="L103">
+        <v>2</v>
+      </c>
+      <c r="M103">
+        <v>1</v>
+      </c>
+      <c r="N103">
+        <v>3</v>
+      </c>
+      <c r="O103" t="s">
+        <v>155</v>
+      </c>
+      <c r="P103" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q103">
+        <v>2.36</v>
+      </c>
+      <c r="R103">
+        <v>2.36</v>
+      </c>
+      <c r="S103">
+        <v>3.9</v>
+      </c>
+      <c r="T103">
+        <v>1.28</v>
+      </c>
+      <c r="U103">
+        <v>3.46</v>
+      </c>
+      <c r="V103">
+        <v>2.29</v>
+      </c>
+      <c r="W103">
+        <v>1.56</v>
+      </c>
+      <c r="X103">
+        <v>5.8</v>
+      </c>
+      <c r="Y103">
+        <v>1.12</v>
+      </c>
+      <c r="Z103">
+        <v>1.89</v>
+      </c>
+      <c r="AA103">
+        <v>3.7</v>
+      </c>
+      <c r="AB103">
+        <v>3.7</v>
+      </c>
+      <c r="AC103">
+        <v>1.01</v>
+      </c>
+      <c r="AD103">
+        <v>13</v>
+      </c>
+      <c r="AE103">
+        <v>1.18</v>
+      </c>
+      <c r="AF103">
+        <v>4.4</v>
+      </c>
+      <c r="AG103">
+        <v>1.57</v>
+      </c>
+      <c r="AH103">
+        <v>2.23</v>
+      </c>
+      <c r="AI103">
+        <v>1.53</v>
+      </c>
+      <c r="AJ103">
+        <v>2.32</v>
+      </c>
+      <c r="AK103">
+        <v>1.27</v>
+      </c>
+      <c r="AL103">
+        <v>1.24</v>
+      </c>
+      <c r="AM103">
+        <v>1.81</v>
+      </c>
+      <c r="AN103">
+        <v>2.1</v>
+      </c>
+      <c r="AO103">
+        <v>1.2</v>
+      </c>
+      <c r="AP103">
+        <v>2.18</v>
+      </c>
+      <c r="AQ103">
+        <v>1.09</v>
+      </c>
+      <c r="AR103">
+        <v>1.61</v>
+      </c>
+      <c r="AS103">
+        <v>1.68</v>
+      </c>
+      <c r="AT103">
+        <v>3.29</v>
+      </c>
+      <c r="AU103">
+        <v>6</v>
+      </c>
+      <c r="AV103">
+        <v>6</v>
+      </c>
+      <c r="AW103">
+        <v>10</v>
+      </c>
+      <c r="AX103">
+        <v>11</v>
+      </c>
+      <c r="AY103">
+        <v>16</v>
+      </c>
+      <c r="AZ103">
+        <v>17</v>
+      </c>
+      <c r="BA103">
+        <v>5</v>
+      </c>
+      <c r="BB103">
+        <v>8</v>
+      </c>
+      <c r="BC103">
+        <v>13</v>
+      </c>
+      <c r="BD103">
+        <v>1.53</v>
+      </c>
+      <c r="BE103">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF103">
+        <v>2.9</v>
+      </c>
+      <c r="BG103">
+        <v>1.32</v>
+      </c>
+      <c r="BH103">
+        <v>2.88</v>
+      </c>
+      <c r="BI103">
+        <v>1.59</v>
+      </c>
+      <c r="BJ103">
+        <v>2.1</v>
+      </c>
+      <c r="BK103">
+        <v>2.04</v>
+      </c>
+      <c r="BL103">
+        <v>1.66</v>
+      </c>
+      <c r="BM103">
+        <v>2.66</v>
+      </c>
+      <c r="BN103">
+        <v>1.37</v>
+      </c>
+      <c r="BO103">
+        <v>3.74</v>
+      </c>
+      <c r="BP103">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7776416</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45695.67708333334</v>
+      </c>
+      <c r="F104">
+        <v>21</v>
+      </c>
+      <c r="G104" t="s">
+        <v>75</v>
+      </c>
+      <c r="H104" t="s">
+        <v>72</v>
+      </c>
+      <c r="I104">
+        <v>2</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>2</v>
+      </c>
+      <c r="L104">
+        <v>2</v>
+      </c>
+      <c r="M104">
+        <v>4</v>
+      </c>
+      <c r="N104">
+        <v>6</v>
+      </c>
+      <c r="O104" t="s">
+        <v>156</v>
+      </c>
+      <c r="P104" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q104">
+        <v>2.99</v>
+      </c>
+      <c r="R104">
+        <v>2.17</v>
+      </c>
+      <c r="S104">
+        <v>3.1</v>
+      </c>
+      <c r="T104">
+        <v>1.31</v>
+      </c>
+      <c r="U104">
+        <v>3.26</v>
+      </c>
+      <c r="V104">
+        <v>2.45</v>
+      </c>
+      <c r="W104">
+        <v>1.51</v>
+      </c>
+      <c r="X104">
+        <v>6.05</v>
+      </c>
+      <c r="Y104">
+        <v>1.11</v>
+      </c>
+      <c r="Z104">
+        <v>2.46</v>
+      </c>
+      <c r="AA104">
+        <v>3.44</v>
+      </c>
+      <c r="AB104">
+        <v>2.55</v>
+      </c>
+      <c r="AC104">
+        <v>1.01</v>
+      </c>
+      <c r="AD104">
+        <v>11</v>
+      </c>
+      <c r="AE104">
+        <v>1.15</v>
+      </c>
+      <c r="AF104">
+        <v>4.25</v>
+      </c>
+      <c r="AG104">
+        <v>1.63</v>
+      </c>
+      <c r="AH104">
+        <v>2.15</v>
+      </c>
+      <c r="AI104">
+        <v>1.51</v>
+      </c>
+      <c r="AJ104">
+        <v>2.32</v>
+      </c>
+      <c r="AK104">
+        <v>1.44</v>
+      </c>
+      <c r="AL104">
+        <v>1.26</v>
+      </c>
+      <c r="AM104">
+        <v>1.47</v>
+      </c>
+      <c r="AN104">
+        <v>1.4</v>
+      </c>
+      <c r="AO104">
+        <v>2.1</v>
+      </c>
+      <c r="AP104">
+        <v>1.27</v>
+      </c>
+      <c r="AQ104">
+        <v>2.18</v>
+      </c>
+      <c r="AR104">
+        <v>1.76</v>
+      </c>
+      <c r="AS104">
+        <v>1.84</v>
+      </c>
+      <c r="AT104">
+        <v>3.6</v>
+      </c>
+      <c r="AU104">
+        <v>6</v>
+      </c>
+      <c r="AV104">
+        <v>9</v>
+      </c>
+      <c r="AW104">
+        <v>7</v>
+      </c>
+      <c r="AX104">
+        <v>10</v>
+      </c>
+      <c r="AY104">
+        <v>13</v>
+      </c>
+      <c r="AZ104">
+        <v>19</v>
+      </c>
+      <c r="BA104">
+        <v>2</v>
+      </c>
+      <c r="BB104">
+        <v>5</v>
+      </c>
+      <c r="BC104">
+        <v>7</v>
+      </c>
+      <c r="BD104">
+        <v>1.69</v>
+      </c>
+      <c r="BE104">
+        <v>6.4</v>
+      </c>
+      <c r="BF104">
+        <v>2.7</v>
+      </c>
+      <c r="BG104">
+        <v>1.23</v>
+      </c>
+      <c r="BH104">
+        <v>3.42</v>
+      </c>
+      <c r="BI104">
+        <v>1.45</v>
+      </c>
+      <c r="BJ104">
+        <v>2.41</v>
+      </c>
+      <c r="BK104">
+        <v>1.81</v>
+      </c>
+      <c r="BL104">
+        <v>1.85</v>
+      </c>
+      <c r="BM104">
+        <v>2.3</v>
+      </c>
+      <c r="BN104">
+        <v>1.49</v>
+      </c>
+      <c r="BO104">
+        <v>3.08</v>
+      </c>
+      <c r="BP104">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="227">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -485,6 +485,9 @@
   </si>
   <si>
     <t>['2', '10']</t>
+  </si>
+  <si>
+    <t>['3']</t>
   </si>
   <si>
     <t>['25', '90+2']</t>
@@ -1053,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP104"/>
+  <dimension ref="A1:BP105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1309,7 +1312,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1515,7 +1518,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1721,7 +1724,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2008,7 +2011,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2211,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ6">
         <v>0.9</v>
@@ -2545,7 +2548,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2957,7 +2960,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3369,7 +3372,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3575,7 +3578,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3781,7 +3784,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3987,7 +3990,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4193,7 +4196,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4271,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ16">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR16">
         <v>1.95</v>
@@ -4399,7 +4402,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4605,7 +4608,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4811,7 +4814,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5017,7 +5020,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5223,7 +5226,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5635,7 +5638,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6047,7 +6050,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6125,7 +6128,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ25">
         <v>1.2</v>
@@ -6253,7 +6256,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6459,7 +6462,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6665,7 +6668,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6952,7 +6955,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ29">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR29">
         <v>1.46</v>
@@ -7077,7 +7080,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7283,7 +7286,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7570,7 +7573,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ32">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -7695,7 +7698,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7901,7 +7904,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8107,7 +8110,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8313,7 +8316,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8391,7 +8394,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ36">
         <v>2.18</v>
@@ -8519,7 +8522,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8931,7 +8934,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9137,7 +9140,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9549,7 +9552,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9755,7 +9758,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9836,7 +9839,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ43">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR43">
         <v>1.64</v>
@@ -9961,7 +9964,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10373,7 +10376,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10451,7 +10454,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ46">
         <v>1.2</v>
@@ -10579,7 +10582,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10991,7 +10994,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11403,7 +11406,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11609,7 +11612,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11815,7 +11818,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11896,7 +11899,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ53">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR53">
         <v>1.54</v>
@@ -12021,7 +12024,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12227,7 +12230,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12511,7 +12514,7 @@
         <v>1.8</v>
       </c>
       <c r="AP56">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ56">
         <v>1.9</v>
@@ -12639,7 +12642,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13051,7 +13054,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13463,7 +13466,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13669,7 +13672,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13750,7 +13753,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ62">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR62">
         <v>1.61</v>
@@ -14081,7 +14084,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14493,7 +14496,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14699,7 +14702,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14905,7 +14908,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -14983,7 +14986,7 @@
         <v>1.5</v>
       </c>
       <c r="AP68">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ68">
         <v>1.09</v>
@@ -15111,7 +15114,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15317,7 +15320,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15523,7 +15526,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15729,7 +15732,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15935,7 +15938,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16141,7 +16144,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16222,7 +16225,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ74">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR74">
         <v>1.53</v>
@@ -16347,7 +16350,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16553,7 +16556,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16631,7 +16634,7 @@
         <v>1.43</v>
       </c>
       <c r="AP76">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ76">
         <v>1.27</v>
@@ -16759,7 +16762,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16965,7 +16968,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17171,7 +17174,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17583,7 +17586,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q81">
         <v>3.6</v>
@@ -17789,7 +17792,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -17870,7 +17873,7 @@
         <v>2</v>
       </c>
       <c r="AQ82">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR82">
         <v>1.78</v>
@@ -18407,7 +18410,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18819,7 +18822,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19025,7 +19028,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19231,7 +19234,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19309,7 +19312,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -19437,7 +19440,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19643,7 +19646,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19849,7 +19852,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20055,7 +20058,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20136,7 +20139,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ93">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR93">
         <v>1.57</v>
@@ -20261,7 +20264,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20673,7 +20676,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21369,7 +21372,7 @@
         <v>0.89</v>
       </c>
       <c r="AP99">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ99">
         <v>0.9</v>
@@ -21497,7 +21500,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21909,7 +21912,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22115,7 +22118,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22321,7 +22324,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22478,6 +22481,212 @@
       </c>
       <c r="BP104">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7776417</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45697.42708333334</v>
+      </c>
+      <c r="F105">
+        <v>21</v>
+      </c>
+      <c r="G105" t="s">
+        <v>74</v>
+      </c>
+      <c r="H105" t="s">
+        <v>78</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>157</v>
+      </c>
+      <c r="P105" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q105">
+        <v>2.7</v>
+      </c>
+      <c r="R105">
+        <v>2.32</v>
+      </c>
+      <c r="S105">
+        <v>3.35</v>
+      </c>
+      <c r="T105">
+        <v>1.3</v>
+      </c>
+      <c r="U105">
+        <v>3.32</v>
+      </c>
+      <c r="V105">
+        <v>2.32</v>
+      </c>
+      <c r="W105">
+        <v>1.55</v>
+      </c>
+      <c r="X105">
+        <v>5.55</v>
+      </c>
+      <c r="Y105">
+        <v>1.12</v>
+      </c>
+      <c r="Z105">
+        <v>2.33</v>
+      </c>
+      <c r="AA105">
+        <v>3.45</v>
+      </c>
+      <c r="AB105">
+        <v>2.86</v>
+      </c>
+      <c r="AC105">
+        <v>1.01</v>
+      </c>
+      <c r="AD105">
+        <v>11</v>
+      </c>
+      <c r="AE105">
+        <v>1.19</v>
+      </c>
+      <c r="AF105">
+        <v>4.4</v>
+      </c>
+      <c r="AG105">
+        <v>1.57</v>
+      </c>
+      <c r="AH105">
+        <v>2.15</v>
+      </c>
+      <c r="AI105">
+        <v>1.51</v>
+      </c>
+      <c r="AJ105">
+        <v>2.39</v>
+      </c>
+      <c r="AK105">
+        <v>1.37</v>
+      </c>
+      <c r="AL105">
+        <v>1.27</v>
+      </c>
+      <c r="AM105">
+        <v>1.59</v>
+      </c>
+      <c r="AN105">
+        <v>2.1</v>
+      </c>
+      <c r="AO105">
+        <v>1.2</v>
+      </c>
+      <c r="AP105">
+        <v>2.18</v>
+      </c>
+      <c r="AQ105">
+        <v>1.09</v>
+      </c>
+      <c r="AR105">
+        <v>1.9</v>
+      </c>
+      <c r="AS105">
+        <v>1.27</v>
+      </c>
+      <c r="AT105">
+        <v>3.17</v>
+      </c>
+      <c r="AU105">
+        <v>8</v>
+      </c>
+      <c r="AV105">
+        <v>5</v>
+      </c>
+      <c r="AW105">
+        <v>11</v>
+      </c>
+      <c r="AX105">
+        <v>14</v>
+      </c>
+      <c r="AY105">
+        <v>19</v>
+      </c>
+      <c r="AZ105">
+        <v>19</v>
+      </c>
+      <c r="BA105">
+        <v>2</v>
+      </c>
+      <c r="BB105">
+        <v>3</v>
+      </c>
+      <c r="BC105">
+        <v>5</v>
+      </c>
+      <c r="BD105">
+        <v>2.06</v>
+      </c>
+      <c r="BE105">
+        <v>6.05</v>
+      </c>
+      <c r="BF105">
+        <v>2.14</v>
+      </c>
+      <c r="BG105">
+        <v>1.45</v>
+      </c>
+      <c r="BH105">
+        <v>2.62</v>
+      </c>
+      <c r="BI105">
+        <v>1.8</v>
+      </c>
+      <c r="BJ105">
+        <v>1.99</v>
+      </c>
+      <c r="BK105">
+        <v>2.26</v>
+      </c>
+      <c r="BL105">
+        <v>1.6</v>
+      </c>
+      <c r="BM105">
+        <v>3.05</v>
+      </c>
+      <c r="BN105">
+        <v>1.28</v>
+      </c>
+      <c r="BO105">
+        <v>4.1</v>
+      </c>
+      <c r="BP105">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="228">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -488,6 +488,9 @@
   </si>
   <si>
     <t>['3']</t>
+  </si>
+  <si>
+    <t>['42', '86']</t>
   </si>
   <si>
     <t>['25', '90+2']</t>
@@ -1056,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP105"/>
+  <dimension ref="A1:BP106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1312,7 +1315,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1518,7 +1521,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1724,7 +1727,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2548,7 +2551,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2629,7 +2632,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ8">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2960,7 +2963,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3244,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ11">
         <v>0.8</v>
@@ -3372,7 +3375,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3578,7 +3581,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3656,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ13">
         <v>1.2</v>
@@ -3784,7 +3787,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3990,7 +3993,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4196,7 +4199,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4402,7 +4405,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4608,7 +4611,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4814,7 +4817,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -4895,7 +4898,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ19">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR19">
         <v>1.52</v>
@@ -5020,7 +5023,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5226,7 +5229,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5638,7 +5641,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6050,7 +6053,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6256,7 +6259,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6334,7 +6337,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ26">
         <v>0.9</v>
@@ -6462,7 +6465,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6668,7 +6671,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7080,7 +7083,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7286,7 +7289,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7367,7 +7370,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ31">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR31">
         <v>1.17</v>
@@ -7698,7 +7701,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7904,7 +7907,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8110,7 +8113,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8188,10 +8191,10 @@
         <v>1.33</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ35">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR35">
         <v>1.63</v>
@@ -8316,7 +8319,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8522,7 +8525,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8934,7 +8937,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9140,7 +9143,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9552,7 +9555,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9758,7 +9761,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9964,7 +9967,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10248,7 +10251,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ45">
         <v>1.09</v>
@@ -10376,7 +10379,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10457,7 +10460,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ46">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR46">
         <v>2</v>
@@ -10582,7 +10585,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10994,7 +10997,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11406,7 +11409,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11612,7 +11615,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11818,7 +11821,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12024,7 +12027,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12230,7 +12233,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12311,7 +12314,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ55">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR55">
         <v>1.41</v>
@@ -12642,7 +12645,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13054,7 +13057,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13466,7 +13469,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13544,7 +13547,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ61">
         <v>1.27</v>
@@ -13672,7 +13675,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13959,7 +13962,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ63">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR63">
         <v>1.59</v>
@@ -14084,7 +14087,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14496,7 +14499,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14702,7 +14705,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14908,7 +14911,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15114,7 +15117,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15320,7 +15323,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15398,7 +15401,7 @@
         <v>1.67</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15526,7 +15529,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15732,7 +15735,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15813,7 +15816,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ72">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR72">
         <v>1.68</v>
@@ -15938,7 +15941,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16144,7 +16147,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16350,7 +16353,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16556,7 +16559,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16762,7 +16765,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16840,7 +16843,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ77">
         <v>2.18</v>
@@ -16968,7 +16971,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17174,7 +17177,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17586,7 +17589,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q81">
         <v>3.6</v>
@@ -17792,7 +17795,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -17870,7 +17873,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ82">
         <v>1.09</v>
@@ -18410,7 +18413,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18822,7 +18825,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19028,7 +19031,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19234,7 +19237,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19440,7 +19443,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19521,7 +19524,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ90">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -19646,7 +19649,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19852,7 +19855,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20058,7 +20061,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20264,7 +20267,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20342,7 +20345,7 @@
         <v>0.89</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ94">
         <v>0.8</v>
@@ -20676,7 +20679,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21500,7 +21503,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21581,7 +21584,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ100">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR100">
         <v>1.58</v>
@@ -21912,7 +21915,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22118,7 +22121,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22324,7 +22327,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22687,6 +22690,212 @@
       </c>
       <c r="BP105">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7776418</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45697.52083333334</v>
+      </c>
+      <c r="F106">
+        <v>21</v>
+      </c>
+      <c r="G106" t="s">
+        <v>79</v>
+      </c>
+      <c r="H106" t="s">
+        <v>73</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>1</v>
+      </c>
+      <c r="L106">
+        <v>2</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>2</v>
+      </c>
+      <c r="O106" t="s">
+        <v>158</v>
+      </c>
+      <c r="P106" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q106">
+        <v>2.13</v>
+      </c>
+      <c r="R106">
+        <v>2.34</v>
+      </c>
+      <c r="S106">
+        <v>4.9</v>
+      </c>
+      <c r="T106">
+        <v>1.33</v>
+      </c>
+      <c r="U106">
+        <v>3.14</v>
+      </c>
+      <c r="V106">
+        <v>2.4</v>
+      </c>
+      <c r="W106">
+        <v>1.5</v>
+      </c>
+      <c r="X106">
+        <v>6.05</v>
+      </c>
+      <c r="Y106">
+        <v>1.1</v>
+      </c>
+      <c r="Z106">
+        <v>1.6</v>
+      </c>
+      <c r="AA106">
+        <v>4.1</v>
+      </c>
+      <c r="AB106">
+        <v>5</v>
+      </c>
+      <c r="AC106">
+        <v>1.01</v>
+      </c>
+      <c r="AD106">
+        <v>11</v>
+      </c>
+      <c r="AE106">
+        <v>1.22</v>
+      </c>
+      <c r="AF106">
+        <v>3.95</v>
+      </c>
+      <c r="AG106">
+        <v>1.7</v>
+      </c>
+      <c r="AH106">
+        <v>1.95</v>
+      </c>
+      <c r="AI106">
+        <v>1.7</v>
+      </c>
+      <c r="AJ106">
+        <v>2.02</v>
+      </c>
+      <c r="AK106">
+        <v>1.18</v>
+      </c>
+      <c r="AL106">
+        <v>1.22</v>
+      </c>
+      <c r="AM106">
+        <v>2.09</v>
+      </c>
+      <c r="AN106">
+        <v>2</v>
+      </c>
+      <c r="AO106">
+        <v>1.2</v>
+      </c>
+      <c r="AP106">
+        <v>2.09</v>
+      </c>
+      <c r="AQ106">
+        <v>1.09</v>
+      </c>
+      <c r="AR106">
+        <v>1.72</v>
+      </c>
+      <c r="AS106">
+        <v>1.57</v>
+      </c>
+      <c r="AT106">
+        <v>3.29</v>
+      </c>
+      <c r="AU106">
+        <v>7</v>
+      </c>
+      <c r="AV106">
+        <v>3</v>
+      </c>
+      <c r="AW106">
+        <v>7</v>
+      </c>
+      <c r="AX106">
+        <v>11</v>
+      </c>
+      <c r="AY106">
+        <v>14</v>
+      </c>
+      <c r="AZ106">
+        <v>14</v>
+      </c>
+      <c r="BA106">
+        <v>4</v>
+      </c>
+      <c r="BB106">
+        <v>5</v>
+      </c>
+      <c r="BC106">
+        <v>9</v>
+      </c>
+      <c r="BD106">
+        <v>1.35</v>
+      </c>
+      <c r="BE106">
+        <v>7.4</v>
+      </c>
+      <c r="BF106">
+        <v>4.15</v>
+      </c>
+      <c r="BG106">
+        <v>1.22</v>
+      </c>
+      <c r="BH106">
+        <v>3.5</v>
+      </c>
+      <c r="BI106">
+        <v>1.47</v>
+      </c>
+      <c r="BJ106">
+        <v>2.56</v>
+      </c>
+      <c r="BK106">
+        <v>1.81</v>
+      </c>
+      <c r="BL106">
+        <v>1.98</v>
+      </c>
+      <c r="BM106">
+        <v>2.26</v>
+      </c>
+      <c r="BN106">
+        <v>1.59</v>
+      </c>
+      <c r="BO106">
+        <v>2.97</v>
+      </c>
+      <c r="BP106">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="228">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -493,6 +493,9 @@
     <t>['42', '86']</t>
   </si>
   <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -656,9 +659,6 @@
   </si>
   <si>
     <t>['40']</t>
-  </si>
-  <si>
-    <t>['45+3']</t>
   </si>
   <si>
     <t>['11', '76']</t>
@@ -1059,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP106"/>
+  <dimension ref="A1:BP109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1315,7 +1315,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ2">
         <v>1.2</v>
@@ -1521,7 +1521,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -1727,7 +1727,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -1805,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ4">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2551,7 +2551,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2963,7 +2963,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3250,7 +3250,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ11">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3375,7 +3375,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3581,7 +3581,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3787,7 +3787,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ14">
         <v>1.09</v>
@@ -3993,7 +3993,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4199,7 +4199,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4405,7 +4405,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4611,7 +4611,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4692,7 +4692,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ18">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR18">
         <v>1.54</v>
@@ -4817,7 +4817,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ19">
         <v>1.09</v>
@@ -5023,7 +5023,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5229,7 +5229,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5307,10 +5307,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ21">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR21">
         <v>1.63</v>
@@ -5641,7 +5641,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5925,7 +5925,7 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6053,7 +6053,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6259,7 +6259,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6465,7 +6465,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6543,10 +6543,10 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ27">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR27">
         <v>1.47</v>
@@ -6671,7 +6671,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7083,7 +7083,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7161,10 +7161,10 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ30">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR30">
         <v>1.62</v>
@@ -7289,7 +7289,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7367,7 +7367,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ31">
         <v>1.09</v>
@@ -7701,7 +7701,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7907,7 +7907,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -7985,7 +7985,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ34">
         <v>1.09</v>
@@ -8113,7 +8113,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8319,7 +8319,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8525,7 +8525,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8603,7 +8603,7 @@
         <v>1.33</v>
       </c>
       <c r="AP37">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ37">
         <v>0.9</v>
@@ -8812,7 +8812,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ38">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR38">
         <v>2.02</v>
@@ -8937,7 +8937,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9015,7 +9015,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ39">
         <v>1.27</v>
@@ -9143,7 +9143,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9430,7 +9430,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ41">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR41">
         <v>1.58</v>
@@ -9555,7 +9555,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9761,7 +9761,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9839,7 +9839,7 @@
         <v>0.25</v>
       </c>
       <c r="AP43">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ43">
         <v>1.09</v>
@@ -9967,7 +9967,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10379,7 +10379,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10585,7 +10585,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10663,7 +10663,7 @@
         <v>2.25</v>
       </c>
       <c r="AP47">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ47">
         <v>1.27</v>
@@ -10872,7 +10872,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ48">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR48">
         <v>1.41</v>
@@ -10997,7 +10997,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11281,10 +11281,10 @@
         <v>0.25</v>
       </c>
       <c r="AP50">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ50">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR50">
         <v>1.24</v>
@@ -11409,7 +11409,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11615,7 +11615,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11693,7 +11693,7 @@
         <v>1.4</v>
       </c>
       <c r="AP52">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ52">
         <v>1</v>
@@ -11821,7 +11821,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12027,7 +12027,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12105,7 +12105,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ54">
         <v>2.18</v>
@@ -12233,7 +12233,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12520,7 +12520,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ56">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR56">
         <v>1.95</v>
@@ -12645,7 +12645,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12929,7 +12929,7 @@
         <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ58">
         <v>0.9</v>
@@ -13057,7 +13057,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13344,7 +13344,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ60">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR60">
         <v>1.75</v>
@@ -13469,7 +13469,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13675,7 +13675,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13753,7 +13753,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ62">
         <v>1.09</v>
@@ -13959,7 +13959,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ63">
         <v>1.09</v>
@@ -14087,7 +14087,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14168,7 +14168,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ64">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR64">
         <v>1.41</v>
@@ -14499,7 +14499,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14580,7 +14580,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ66">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR66">
         <v>1.6</v>
@@ -14705,7 +14705,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14911,7 +14911,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15117,7 +15117,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15323,7 +15323,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15529,7 +15529,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15735,7 +15735,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15941,7 +15941,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16019,10 +16019,10 @@
         <v>1.71</v>
       </c>
       <c r="AP73">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ73">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR73">
         <v>1.6</v>
@@ -16147,7 +16147,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16225,7 +16225,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ74">
         <v>1.09</v>
@@ -16353,7 +16353,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16559,7 +16559,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16765,7 +16765,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16971,7 +16971,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17177,7 +17177,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17464,7 +17464,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ80">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR80">
         <v>1.62</v>
@@ -17589,7 +17589,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="Q81">
         <v>3.6</v>
@@ -18285,7 +18285,7 @@
         <v>0.86</v>
       </c>
       <c r="AP84">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ84">
         <v>1.2</v>
@@ -18494,7 +18494,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ85">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18697,7 +18697,7 @@
         <v>0.63</v>
       </c>
       <c r="AP86">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ86">
         <v>0.9</v>
@@ -18906,7 +18906,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ87">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR87">
         <v>1.73</v>
@@ -19109,7 +19109,7 @@
         <v>1.88</v>
       </c>
       <c r="AP88">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ88">
         <v>2.18</v>
@@ -19727,7 +19727,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ91">
         <v>1.2</v>
@@ -20061,7 +20061,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20348,7 +20348,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ94">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR94">
         <v>1.69</v>
@@ -20757,10 +20757,10 @@
         <v>1.78</v>
       </c>
       <c r="AP96">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ96">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR96">
         <v>1.68</v>
@@ -21503,7 +21503,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21581,7 +21581,7 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ100">
         <v>1.09</v>
@@ -21787,7 +21787,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ101">
         <v>1.2</v>
@@ -22896,6 +22896,624 @@
       </c>
       <c r="BP106">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7776419</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45702.64583333334</v>
+      </c>
+      <c r="F107">
+        <v>22</v>
+      </c>
+      <c r="G107" t="s">
+        <v>70</v>
+      </c>
+      <c r="H107" t="s">
+        <v>74</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107" t="s">
+        <v>84</v>
+      </c>
+      <c r="P107" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q107">
+        <v>2.55</v>
+      </c>
+      <c r="R107">
+        <v>2.36</v>
+      </c>
+      <c r="S107">
+        <v>3.45</v>
+      </c>
+      <c r="T107">
+        <v>1.27</v>
+      </c>
+      <c r="U107">
+        <v>3.54</v>
+      </c>
+      <c r="V107">
+        <v>2.25</v>
+      </c>
+      <c r="W107">
+        <v>1.58</v>
+      </c>
+      <c r="X107">
+        <v>5.5</v>
+      </c>
+      <c r="Y107">
+        <v>1.13</v>
+      </c>
+      <c r="Z107">
+        <v>2.12</v>
+      </c>
+      <c r="AA107">
+        <v>3.69</v>
+      </c>
+      <c r="AB107">
+        <v>3.07</v>
+      </c>
+      <c r="AC107">
+        <v>1.01</v>
+      </c>
+      <c r="AD107">
+        <v>13</v>
+      </c>
+      <c r="AE107">
+        <v>1.17</v>
+      </c>
+      <c r="AF107">
+        <v>4.6</v>
+      </c>
+      <c r="AG107">
+        <v>1.53</v>
+      </c>
+      <c r="AH107">
+        <v>2.2</v>
+      </c>
+      <c r="AI107">
+        <v>1.48</v>
+      </c>
+      <c r="AJ107">
+        <v>2.46</v>
+      </c>
+      <c r="AK107">
+        <v>1.34</v>
+      </c>
+      <c r="AL107">
+        <v>1.26</v>
+      </c>
+      <c r="AM107">
+        <v>1.64</v>
+      </c>
+      <c r="AN107">
+        <v>1.3</v>
+      </c>
+      <c r="AO107">
+        <v>0.8</v>
+      </c>
+      <c r="AP107">
+        <v>1.27</v>
+      </c>
+      <c r="AQ107">
+        <v>0.82</v>
+      </c>
+      <c r="AR107">
+        <v>1.57</v>
+      </c>
+      <c r="AS107">
+        <v>1.24</v>
+      </c>
+      <c r="AT107">
+        <v>2.81</v>
+      </c>
+      <c r="AU107">
+        <v>0</v>
+      </c>
+      <c r="AV107">
+        <v>2</v>
+      </c>
+      <c r="AW107">
+        <v>5</v>
+      </c>
+      <c r="AX107">
+        <v>4</v>
+      </c>
+      <c r="AY107">
+        <v>5</v>
+      </c>
+      <c r="AZ107">
+        <v>6</v>
+      </c>
+      <c r="BA107">
+        <v>2</v>
+      </c>
+      <c r="BB107">
+        <v>2</v>
+      </c>
+      <c r="BC107">
+        <v>4</v>
+      </c>
+      <c r="BD107">
+        <v>1.66</v>
+      </c>
+      <c r="BE107">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF107">
+        <v>2.53</v>
+      </c>
+      <c r="BG107">
+        <v>1.22</v>
+      </c>
+      <c r="BH107">
+        <v>3.5</v>
+      </c>
+      <c r="BI107">
+        <v>1.49</v>
+      </c>
+      <c r="BJ107">
+        <v>2.53</v>
+      </c>
+      <c r="BK107">
+        <v>1.83</v>
+      </c>
+      <c r="BL107">
+        <v>1.96</v>
+      </c>
+      <c r="BM107">
+        <v>2.3</v>
+      </c>
+      <c r="BN107">
+        <v>1.59</v>
+      </c>
+      <c r="BO107">
+        <v>3.04</v>
+      </c>
+      <c r="BP107">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7776420</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45702.64583333334</v>
+      </c>
+      <c r="F108">
+        <v>22</v>
+      </c>
+      <c r="G108" t="s">
+        <v>71</v>
+      </c>
+      <c r="H108" t="s">
+        <v>77</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108" t="s">
+        <v>84</v>
+      </c>
+      <c r="P108" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q108">
+        <v>3.8</v>
+      </c>
+      <c r="R108">
+        <v>2.18</v>
+      </c>
+      <c r="S108">
+        <v>2.6</v>
+      </c>
+      <c r="T108">
+        <v>1.36</v>
+      </c>
+      <c r="U108">
+        <v>2.97</v>
+      </c>
+      <c r="V108">
+        <v>2.6</v>
+      </c>
+      <c r="W108">
+        <v>1.44</v>
+      </c>
+      <c r="X108">
+        <v>6.7</v>
+      </c>
+      <c r="Y108">
+        <v>1.09</v>
+      </c>
+      <c r="Z108">
+        <v>3.41</v>
+      </c>
+      <c r="AA108">
+        <v>3.41</v>
+      </c>
+      <c r="AB108">
+        <v>2.06</v>
+      </c>
+      <c r="AC108">
+        <v>1</v>
+      </c>
+      <c r="AD108">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE108">
+        <v>1.26</v>
+      </c>
+      <c r="AF108">
+        <v>3.6</v>
+      </c>
+      <c r="AG108">
+        <v>1.83</v>
+      </c>
+      <c r="AH108">
+        <v>1.91</v>
+      </c>
+      <c r="AI108">
+        <v>1.67</v>
+      </c>
+      <c r="AJ108">
+        <v>2.07</v>
+      </c>
+      <c r="AK108">
+        <v>1.67</v>
+      </c>
+      <c r="AL108">
+        <v>1.28</v>
+      </c>
+      <c r="AM108">
+        <v>1.31</v>
+      </c>
+      <c r="AN108">
+        <v>0.5</v>
+      </c>
+      <c r="AO108">
+        <v>1</v>
+      </c>
+      <c r="AP108">
+        <v>0.55</v>
+      </c>
+      <c r="AQ108">
+        <v>1</v>
+      </c>
+      <c r="AR108">
+        <v>1.58</v>
+      </c>
+      <c r="AS108">
+        <v>1.65</v>
+      </c>
+      <c r="AT108">
+        <v>3.23</v>
+      </c>
+      <c r="AU108">
+        <v>0</v>
+      </c>
+      <c r="AV108">
+        <v>4</v>
+      </c>
+      <c r="AW108">
+        <v>7</v>
+      </c>
+      <c r="AX108">
+        <v>0</v>
+      </c>
+      <c r="AY108">
+        <v>7</v>
+      </c>
+      <c r="AZ108">
+        <v>4</v>
+      </c>
+      <c r="BA108">
+        <v>4</v>
+      </c>
+      <c r="BB108">
+        <v>4</v>
+      </c>
+      <c r="BC108">
+        <v>8</v>
+      </c>
+      <c r="BD108">
+        <v>2.39</v>
+      </c>
+      <c r="BE108">
+        <v>8</v>
+      </c>
+      <c r="BF108">
+        <v>1.74</v>
+      </c>
+      <c r="BG108">
+        <v>1.26</v>
+      </c>
+      <c r="BH108">
+        <v>3.22</v>
+      </c>
+      <c r="BI108">
+        <v>1.58</v>
+      </c>
+      <c r="BJ108">
+        <v>2.32</v>
+      </c>
+      <c r="BK108">
+        <v>1.95</v>
+      </c>
+      <c r="BL108">
+        <v>1.84</v>
+      </c>
+      <c r="BM108">
+        <v>2.47</v>
+      </c>
+      <c r="BN108">
+        <v>1.51</v>
+      </c>
+      <c r="BO108">
+        <v>3.28</v>
+      </c>
+      <c r="BP108">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7776421</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45702.67708333334</v>
+      </c>
+      <c r="F109">
+        <v>22</v>
+      </c>
+      <c r="G109" t="s">
+        <v>72</v>
+      </c>
+      <c r="H109" t="s">
+        <v>79</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>1</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>1</v>
+      </c>
+      <c r="O109" t="s">
+        <v>159</v>
+      </c>
+      <c r="P109" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q109">
+        <v>2.8</v>
+      </c>
+      <c r="R109">
+        <v>2.29</v>
+      </c>
+      <c r="S109">
+        <v>3.2</v>
+      </c>
+      <c r="T109">
+        <v>1.28</v>
+      </c>
+      <c r="U109">
+        <v>3.36</v>
+      </c>
+      <c r="V109">
+        <v>2.36</v>
+      </c>
+      <c r="W109">
+        <v>1.54</v>
+      </c>
+      <c r="X109">
+        <v>6</v>
+      </c>
+      <c r="Y109">
+        <v>1.07</v>
+      </c>
+      <c r="Z109">
+        <v>2.35</v>
+      </c>
+      <c r="AA109">
+        <v>3.39</v>
+      </c>
+      <c r="AB109">
+        <v>2.86</v>
+      </c>
+      <c r="AC109">
+        <v>1.01</v>
+      </c>
+      <c r="AD109">
+        <v>11</v>
+      </c>
+      <c r="AE109">
+        <v>1.2</v>
+      </c>
+      <c r="AF109">
+        <v>4.3</v>
+      </c>
+      <c r="AG109">
+        <v>1.61</v>
+      </c>
+      <c r="AH109">
+        <v>2.1</v>
+      </c>
+      <c r="AI109">
+        <v>1.52</v>
+      </c>
+      <c r="AJ109">
+        <v>2.36</v>
+      </c>
+      <c r="AK109">
+        <v>1.41</v>
+      </c>
+      <c r="AL109">
+        <v>1.27</v>
+      </c>
+      <c r="AM109">
+        <v>1.53</v>
+      </c>
+      <c r="AN109">
+        <v>1.4</v>
+      </c>
+      <c r="AO109">
+        <v>1.9</v>
+      </c>
+      <c r="AP109">
+        <v>1.55</v>
+      </c>
+      <c r="AQ109">
+        <v>1.73</v>
+      </c>
+      <c r="AR109">
+        <v>1.53</v>
+      </c>
+      <c r="AS109">
+        <v>1.81</v>
+      </c>
+      <c r="AT109">
+        <v>3.34</v>
+      </c>
+      <c r="AU109">
+        <v>3</v>
+      </c>
+      <c r="AV109">
+        <v>4</v>
+      </c>
+      <c r="AW109">
+        <v>9</v>
+      </c>
+      <c r="AX109">
+        <v>12</v>
+      </c>
+      <c r="AY109">
+        <v>12</v>
+      </c>
+      <c r="AZ109">
+        <v>16</v>
+      </c>
+      <c r="BA109">
+        <v>2</v>
+      </c>
+      <c r="BB109">
+        <v>3</v>
+      </c>
+      <c r="BC109">
+        <v>5</v>
+      </c>
+      <c r="BD109">
+        <v>1.88</v>
+      </c>
+      <c r="BE109">
+        <v>6.45</v>
+      </c>
+      <c r="BF109">
+        <v>2.32</v>
+      </c>
+      <c r="BG109">
+        <v>1.19</v>
+      </c>
+      <c r="BH109">
+        <v>4</v>
+      </c>
+      <c r="BI109">
+        <v>1.33</v>
+      </c>
+      <c r="BJ109">
+        <v>2.83</v>
+      </c>
+      <c r="BK109">
+        <v>1.67</v>
+      </c>
+      <c r="BL109">
+        <v>2.16</v>
+      </c>
+      <c r="BM109">
+        <v>2.07</v>
+      </c>
+      <c r="BN109">
+        <v>1.74</v>
+      </c>
+      <c r="BO109">
+        <v>2.59</v>
+      </c>
+      <c r="BP109">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="231">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -496,6 +496,9 @@
     <t>['45+3']</t>
   </si>
   <si>
+    <t>['21', '50']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -698,6 +701,12 @@
   </si>
   <si>
     <t>['50', '57', '67', '72']</t>
+  </si>
+  <si>
+    <t>['90+7']</t>
+  </si>
+  <si>
+    <t>['13']</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP109"/>
+  <dimension ref="A1:BP111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1315,7 +1324,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1396,7 +1405,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ2">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1521,7 +1530,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1727,7 +1736,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2011,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ5">
         <v>1.09</v>
@@ -2220,7 +2229,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ6">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2551,7 +2560,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2963,7 +2972,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3041,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ10">
         <v>2.18</v>
@@ -3375,7 +3384,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3581,7 +3590,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3662,7 +3671,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ13">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR13">
         <v>1.92</v>
@@ -3787,7 +3796,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3993,7 +4002,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4071,7 +4080,7 @@
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4199,7 +4208,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4405,7 +4414,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4611,7 +4620,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4817,7 +4826,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5023,7 +5032,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5101,10 +5110,10 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ20">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR20">
         <v>1.99</v>
@@ -5229,7 +5238,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5513,7 +5522,7 @@
         <v>1.5</v>
       </c>
       <c r="AP22">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ22">
         <v>1.09</v>
@@ -5641,7 +5650,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5719,7 +5728,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ23">
         <v>1.27</v>
@@ -6053,7 +6062,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6134,7 +6143,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ25">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR25">
         <v>1.92</v>
@@ -6259,7 +6268,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6340,7 +6349,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ26">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR26">
         <v>1.45</v>
@@ -6465,7 +6474,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6671,7 +6680,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6752,7 +6761,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ28">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR28">
         <v>1.43</v>
@@ -7083,7 +7092,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7289,7 +7298,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7701,7 +7710,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7907,7 +7916,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8113,7 +8122,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8319,7 +8328,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8525,7 +8534,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8606,7 +8615,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ37">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -8809,7 +8818,7 @@
         <v>2.33</v>
       </c>
       <c r="AP38">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ38">
         <v>1.73</v>
@@ -8937,7 +8946,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9143,7 +9152,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9221,10 +9230,10 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ40">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR40">
         <v>1.35</v>
@@ -9555,7 +9564,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9761,7 +9770,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9967,7 +9976,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10379,7 +10388,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10585,7 +10594,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10869,7 +10878,7 @@
         <v>2</v>
       </c>
       <c r="AP48">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ48">
         <v>1.73</v>
@@ -10997,7 +11006,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11078,7 +11087,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ49">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR49">
         <v>1.57</v>
@@ -11409,7 +11418,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11487,10 +11496,10 @@
         <v>0.8</v>
       </c>
       <c r="AP51">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ51">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR51">
         <v>1.86</v>
@@ -11615,7 +11624,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11821,7 +11830,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12027,7 +12036,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12233,7 +12242,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12645,7 +12654,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12726,7 +12735,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ57">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR57">
         <v>1.74</v>
@@ -12932,7 +12941,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ58">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR58">
         <v>1.33</v>
@@ -13057,7 +13066,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13135,7 +13144,7 @@
         <v>1.2</v>
       </c>
       <c r="AP59">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ59">
         <v>1.09</v>
@@ -13341,7 +13350,7 @@
         <v>0.4</v>
       </c>
       <c r="AP60">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ60">
         <v>0.82</v>
@@ -13469,7 +13478,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13675,7 +13684,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -14087,7 +14096,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14499,7 +14508,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14705,7 +14714,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14786,7 +14795,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ67">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR67">
         <v>1.46</v>
@@ -14911,7 +14920,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15117,7 +15126,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15195,7 +15204,7 @@
         <v>1.83</v>
       </c>
       <c r="AP69">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ69">
         <v>2.18</v>
@@ -15323,7 +15332,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15529,7 +15538,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15607,7 +15616,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ71">
         <v>1.27</v>
@@ -15735,7 +15744,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15941,7 +15950,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16147,7 +16156,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16353,7 +16362,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16559,7 +16568,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16765,7 +16774,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16971,7 +16980,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17049,10 +17058,10 @@
         <v>0.57</v>
       </c>
       <c r="AP78">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ78">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR78">
         <v>1.35</v>
@@ -17177,7 +17186,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17255,7 +17264,7 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17795,7 +17804,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18288,7 +18297,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ84">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR84">
         <v>1.62</v>
@@ -18413,7 +18422,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18491,7 +18500,7 @@
         <v>0.63</v>
       </c>
       <c r="AP85">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ85">
         <v>0.82</v>
@@ -18700,7 +18709,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ86">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR86">
         <v>1.62</v>
@@ -18825,7 +18834,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19031,7 +19040,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19237,7 +19246,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19443,7 +19452,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19521,7 +19530,7 @@
         <v>1.13</v>
       </c>
       <c r="AP90">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ90">
         <v>1.09</v>
@@ -19649,7 +19658,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19730,7 +19739,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ91">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR91">
         <v>1.62</v>
@@ -19855,7 +19864,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20061,7 +20070,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20267,7 +20276,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20551,7 +20560,7 @@
         <v>1.22</v>
       </c>
       <c r="AP95">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ95">
         <v>1.27</v>
@@ -20679,7 +20688,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21169,7 +21178,7 @@
         <v>1.33</v>
       </c>
       <c r="AP98">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ98">
         <v>1.09</v>
@@ -21378,7 +21387,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ99">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR99">
         <v>1.93</v>
@@ -21503,7 +21512,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21790,7 +21799,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ101">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR101">
         <v>1.64</v>
@@ -21915,7 +21924,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22121,7 +22130,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22327,7 +22336,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -23514,6 +23523,418 @@
       </c>
       <c r="BP109">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7776422</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45703.58333333334</v>
+      </c>
+      <c r="F110">
+        <v>22</v>
+      </c>
+      <c r="G110" t="s">
+        <v>73</v>
+      </c>
+      <c r="H110" t="s">
+        <v>75</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>84</v>
+      </c>
+      <c r="P110" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q110">
+        <v>3.3</v>
+      </c>
+      <c r="R110">
+        <v>2.15</v>
+      </c>
+      <c r="S110">
+        <v>2.95</v>
+      </c>
+      <c r="T110">
+        <v>1.36</v>
+      </c>
+      <c r="U110">
+        <v>2.94</v>
+      </c>
+      <c r="V110">
+        <v>2.65</v>
+      </c>
+      <c r="W110">
+        <v>1.42</v>
+      </c>
+      <c r="X110">
+        <v>7.1</v>
+      </c>
+      <c r="Y110">
+        <v>1.04</v>
+      </c>
+      <c r="Z110">
+        <v>2.77</v>
+      </c>
+      <c r="AA110">
+        <v>3.25</v>
+      </c>
+      <c r="AB110">
+        <v>2.49</v>
+      </c>
+      <c r="AC110">
+        <v>1.01</v>
+      </c>
+      <c r="AD110">
+        <v>9</v>
+      </c>
+      <c r="AE110">
+        <v>1.28</v>
+      </c>
+      <c r="AF110">
+        <v>3.5</v>
+      </c>
+      <c r="AG110">
+        <v>1.87</v>
+      </c>
+      <c r="AH110">
+        <v>1.87</v>
+      </c>
+      <c r="AI110">
+        <v>1.67</v>
+      </c>
+      <c r="AJ110">
+        <v>2.07</v>
+      </c>
+      <c r="AK110">
+        <v>1.51</v>
+      </c>
+      <c r="AL110">
+        <v>1.29</v>
+      </c>
+      <c r="AM110">
+        <v>1.41</v>
+      </c>
+      <c r="AN110">
+        <v>1.5</v>
+      </c>
+      <c r="AO110">
+        <v>1.2</v>
+      </c>
+      <c r="AP110">
+        <v>1.36</v>
+      </c>
+      <c r="AQ110">
+        <v>1.36</v>
+      </c>
+      <c r="AR110">
+        <v>1.42</v>
+      </c>
+      <c r="AS110">
+        <v>1.66</v>
+      </c>
+      <c r="AT110">
+        <v>3.08</v>
+      </c>
+      <c r="AU110">
+        <v>4</v>
+      </c>
+      <c r="AV110">
+        <v>6</v>
+      </c>
+      <c r="AW110">
+        <v>10</v>
+      </c>
+      <c r="AX110">
+        <v>14</v>
+      </c>
+      <c r="AY110">
+        <v>14</v>
+      </c>
+      <c r="AZ110">
+        <v>20</v>
+      </c>
+      <c r="BA110">
+        <v>4</v>
+      </c>
+      <c r="BB110">
+        <v>10</v>
+      </c>
+      <c r="BC110">
+        <v>14</v>
+      </c>
+      <c r="BD110">
+        <v>2.14</v>
+      </c>
+      <c r="BE110">
+        <v>6.15</v>
+      </c>
+      <c r="BF110">
+        <v>2.05</v>
+      </c>
+      <c r="BG110">
+        <v>1.31</v>
+      </c>
+      <c r="BH110">
+        <v>2.92</v>
+      </c>
+      <c r="BI110">
+        <v>1.65</v>
+      </c>
+      <c r="BJ110">
+        <v>2.19</v>
+      </c>
+      <c r="BK110">
+        <v>2.06</v>
+      </c>
+      <c r="BL110">
+        <v>1.74</v>
+      </c>
+      <c r="BM110">
+        <v>2.66</v>
+      </c>
+      <c r="BN110">
+        <v>1.37</v>
+      </c>
+      <c r="BO110">
+        <v>3.7</v>
+      </c>
+      <c r="BP110">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7776423</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45703.58333333334</v>
+      </c>
+      <c r="F111">
+        <v>22</v>
+      </c>
+      <c r="G111" t="s">
+        <v>78</v>
+      </c>
+      <c r="H111" t="s">
+        <v>76</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>2</v>
+      </c>
+      <c r="L111">
+        <v>2</v>
+      </c>
+      <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
+        <v>3</v>
+      </c>
+      <c r="O111" t="s">
+        <v>160</v>
+      </c>
+      <c r="P111" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q111">
+        <v>2.32</v>
+      </c>
+      <c r="R111">
+        <v>2.29</v>
+      </c>
+      <c r="S111">
+        <v>4.3</v>
+      </c>
+      <c r="T111">
+        <v>1.31</v>
+      </c>
+      <c r="U111">
+        <v>3.2</v>
+      </c>
+      <c r="V111">
+        <v>2.4</v>
+      </c>
+      <c r="W111">
+        <v>1.5</v>
+      </c>
+      <c r="X111">
+        <v>6.15</v>
+      </c>
+      <c r="Y111">
+        <v>1.07</v>
+      </c>
+      <c r="Z111">
+        <v>1.74</v>
+      </c>
+      <c r="AA111">
+        <v>3.83</v>
+      </c>
+      <c r="AB111">
+        <v>4.3</v>
+      </c>
+      <c r="AC111">
+        <v>1.01</v>
+      </c>
+      <c r="AD111">
+        <v>11</v>
+      </c>
+      <c r="AE111">
+        <v>1.22</v>
+      </c>
+      <c r="AF111">
+        <v>4</v>
+      </c>
+      <c r="AG111">
+        <v>1.65</v>
+      </c>
+      <c r="AH111">
+        <v>2</v>
+      </c>
+      <c r="AI111">
+        <v>1.63</v>
+      </c>
+      <c r="AJ111">
+        <v>2.14</v>
+      </c>
+      <c r="AK111">
+        <v>1.24</v>
+      </c>
+      <c r="AL111">
+        <v>1.24</v>
+      </c>
+      <c r="AM111">
+        <v>1.87</v>
+      </c>
+      <c r="AN111">
+        <v>1.4</v>
+      </c>
+      <c r="AO111">
+        <v>0.9</v>
+      </c>
+      <c r="AP111">
+        <v>1.55</v>
+      </c>
+      <c r="AQ111">
+        <v>0.82</v>
+      </c>
+      <c r="AR111">
+        <v>1.61</v>
+      </c>
+      <c r="AS111">
+        <v>1.41</v>
+      </c>
+      <c r="AT111">
+        <v>3.02</v>
+      </c>
+      <c r="AU111">
+        <v>5</v>
+      </c>
+      <c r="AV111">
+        <v>4</v>
+      </c>
+      <c r="AW111">
+        <v>4</v>
+      </c>
+      <c r="AX111">
+        <v>4</v>
+      </c>
+      <c r="AY111">
+        <v>9</v>
+      </c>
+      <c r="AZ111">
+        <v>8</v>
+      </c>
+      <c r="BA111">
+        <v>3</v>
+      </c>
+      <c r="BB111">
+        <v>2</v>
+      </c>
+      <c r="BC111">
+        <v>5</v>
+      </c>
+      <c r="BD111">
+        <v>1.48</v>
+      </c>
+      <c r="BE111">
+        <v>6.65</v>
+      </c>
+      <c r="BF111">
+        <v>3.42</v>
+      </c>
+      <c r="BG111">
+        <v>1.33</v>
+      </c>
+      <c r="BH111">
+        <v>2.83</v>
+      </c>
+      <c r="BI111">
+        <v>1.67</v>
+      </c>
+      <c r="BJ111">
+        <v>2.14</v>
+      </c>
+      <c r="BK111">
+        <v>2.1</v>
+      </c>
+      <c r="BL111">
+        <v>1.7</v>
+      </c>
+      <c r="BM111">
+        <v>2.7</v>
+      </c>
+      <c r="BN111">
+        <v>1.36</v>
+      </c>
+      <c r="BO111">
+        <v>3.8</v>
+      </c>
+      <c r="BP111">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="234">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -499,6 +499,12 @@
     <t>['21', '50']</t>
   </si>
   <si>
+    <t>['46', '64', '72']</t>
+  </si>
+  <si>
+    <t>['12', '90+2']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -707,6 +713,9 @@
   </si>
   <si>
     <t>['13']</t>
+  </si>
+  <si>
+    <t>['9', '63', '66', '79']</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP111"/>
+  <dimension ref="A1:BP113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1324,7 +1333,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1405,7 +1414,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ2">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1530,7 +1539,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1608,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -1736,7 +1745,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2560,7 +2569,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2638,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8">
         <v>1.09</v>
@@ -2847,7 +2856,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ9">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2972,7 +2981,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3384,7 +3393,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3462,7 +3471,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12">
         <v>1.27</v>
@@ -3590,7 +3599,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3671,7 +3680,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ13">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR13">
         <v>1.92</v>
@@ -3796,7 +3805,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3877,7 +3886,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ14">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR14">
         <v>1.19</v>
@@ -4002,7 +4011,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4208,7 +4217,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4414,7 +4423,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4620,7 +4629,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4826,7 +4835,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5032,7 +5041,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5238,7 +5247,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5316,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ21">
         <v>0.82</v>
@@ -5525,7 +5534,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ22">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR22">
         <v>1.91</v>
@@ -5650,7 +5659,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6062,7 +6071,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6143,7 +6152,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ25">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR25">
         <v>1.92</v>
@@ -6268,7 +6277,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6474,7 +6483,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6680,7 +6689,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6758,10 +6767,10 @@
         <v>0.33</v>
       </c>
       <c r="AP28">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ28">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
         <v>1.43</v>
@@ -7092,7 +7101,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7170,7 +7179,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ30">
         <v>1.73</v>
@@ -7298,7 +7307,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7710,7 +7719,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7788,7 +7797,7 @@
         <v>1.33</v>
       </c>
       <c r="AP33">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -7916,7 +7925,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -7994,10 +8003,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ34">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR34">
         <v>1.52</v>
@@ -8122,7 +8131,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8328,7 +8337,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8534,7 +8543,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8946,7 +8955,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9152,7 +9161,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9233,7 +9242,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ40">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR40">
         <v>1.35</v>
@@ -9564,7 +9573,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9770,7 +9779,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9848,7 +9857,7 @@
         <v>0.25</v>
       </c>
       <c r="AP43">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ43">
         <v>1.09</v>
@@ -9976,7 +9985,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10054,7 +10063,7 @@
         <v>1.67</v>
       </c>
       <c r="AP44">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ44">
         <v>2.18</v>
@@ -10263,7 +10272,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ45">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR45">
         <v>1.73</v>
@@ -10388,7 +10397,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10594,7 +10603,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11006,7 +11015,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11418,7 +11427,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11499,7 +11508,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ51">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR51">
         <v>1.86</v>
@@ -11624,7 +11633,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11830,7 +11839,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11908,7 +11917,7 @@
         <v>0.8</v>
       </c>
       <c r="AP53">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ53">
         <v>1.09</v>
@@ -12036,7 +12045,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12114,7 +12123,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ54">
         <v>2.18</v>
@@ -12242,7 +12251,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12654,7 +12663,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12735,7 +12744,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ57">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR57">
         <v>1.74</v>
@@ -13066,7 +13075,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13147,7 +13156,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ59">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR59">
         <v>1.44</v>
@@ -13478,7 +13487,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13684,7 +13693,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13968,7 +13977,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ63">
         <v>1.09</v>
@@ -14096,7 +14105,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14508,7 +14517,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14586,7 +14595,7 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ66">
         <v>1.73</v>
@@ -14714,7 +14723,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14920,7 +14929,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15001,7 +15010,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ68">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15126,7 +15135,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15332,7 +15341,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15538,7 +15547,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15744,7 +15753,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15950,7 +15959,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16156,7 +16165,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16362,7 +16371,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16443,7 +16452,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ75">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR75">
         <v>1.68</v>
@@ -16568,7 +16577,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16774,7 +16783,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16980,7 +16989,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17186,7 +17195,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17470,7 +17479,7 @@
         <v>0.57</v>
       </c>
       <c r="AP80">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ80">
         <v>0.82</v>
@@ -17676,10 +17685,10 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ81">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR81">
         <v>1.63</v>
@@ -17804,7 +17813,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18297,7 +18306,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ84">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR84">
         <v>1.62</v>
@@ -18422,7 +18431,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18706,7 +18715,7 @@
         <v>0.63</v>
       </c>
       <c r="AP86">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ86">
         <v>0.82</v>
@@ -18834,7 +18843,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19040,7 +19049,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19246,7 +19255,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19452,7 +19461,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19658,7 +19667,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19739,7 +19748,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ91">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR91">
         <v>1.62</v>
@@ -19864,7 +19873,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -19942,7 +19951,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ92">
         <v>2.18</v>
@@ -20070,7 +20079,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20276,7 +20285,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20688,7 +20697,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -20766,7 +20775,7 @@
         <v>1.78</v>
       </c>
       <c r="AP96">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ96">
         <v>1.73</v>
@@ -21181,7 +21190,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ98">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR98">
         <v>1.61</v>
@@ -21512,7 +21521,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21796,10 +21805,10 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ101">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR101">
         <v>1.64</v>
@@ -21924,7 +21933,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22002,7 +22011,7 @@
         <v>1.1</v>
       </c>
       <c r="AP102">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ102">
         <v>1.27</v>
@@ -22130,7 +22139,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22211,7 +22220,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ103">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR103">
         <v>1.61</v>
@@ -22336,7 +22345,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -23238,7 +23247,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23572,7 +23581,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23653,7 +23662,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ110">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -23778,7 +23787,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -23935,6 +23944,418 @@
       </c>
       <c r="BP111">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7776424</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45709.64583333334</v>
+      </c>
+      <c r="F112">
+        <v>23</v>
+      </c>
+      <c r="G112" t="s">
+        <v>76</v>
+      </c>
+      <c r="H112" t="s">
+        <v>75</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>3</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>3</v>
+      </c>
+      <c r="O112" t="s">
+        <v>161</v>
+      </c>
+      <c r="P112" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q112">
+        <v>3.84</v>
+      </c>
+      <c r="R112">
+        <v>2.23</v>
+      </c>
+      <c r="S112">
+        <v>2.45</v>
+      </c>
+      <c r="T112">
+        <v>1.3</v>
+      </c>
+      <c r="U112">
+        <v>3.26</v>
+      </c>
+      <c r="V112">
+        <v>2.47</v>
+      </c>
+      <c r="W112">
+        <v>1.49</v>
+      </c>
+      <c r="X112">
+        <v>5.9</v>
+      </c>
+      <c r="Y112">
+        <v>1.08</v>
+      </c>
+      <c r="Z112">
+        <v>3.84</v>
+      </c>
+      <c r="AA112">
+        <v>3.74</v>
+      </c>
+      <c r="AB112">
+        <v>1.84</v>
+      </c>
+      <c r="AC112">
+        <v>1.01</v>
+      </c>
+      <c r="AD112">
+        <v>11</v>
+      </c>
+      <c r="AE112">
+        <v>1.16</v>
+      </c>
+      <c r="AF112">
+        <v>4.15</v>
+      </c>
+      <c r="AG112">
+        <v>1.65</v>
+      </c>
+      <c r="AH112">
+        <v>2.13</v>
+      </c>
+      <c r="AI112">
+        <v>1.56</v>
+      </c>
+      <c r="AJ112">
+        <v>2.21</v>
+      </c>
+      <c r="AK112">
+        <v>1.76</v>
+      </c>
+      <c r="AL112">
+        <v>1.23</v>
+      </c>
+      <c r="AM112">
+        <v>1.26</v>
+      </c>
+      <c r="AN112">
+        <v>0.91</v>
+      </c>
+      <c r="AO112">
+        <v>1.36</v>
+      </c>
+      <c r="AP112">
+        <v>1.08</v>
+      </c>
+      <c r="AQ112">
+        <v>1.25</v>
+      </c>
+      <c r="AR112">
+        <v>1.63</v>
+      </c>
+      <c r="AS112">
+        <v>1.69</v>
+      </c>
+      <c r="AT112">
+        <v>3.32</v>
+      </c>
+      <c r="AU112">
+        <v>10</v>
+      </c>
+      <c r="AV112">
+        <v>5</v>
+      </c>
+      <c r="AW112">
+        <v>4</v>
+      </c>
+      <c r="AX112">
+        <v>7</v>
+      </c>
+      <c r="AY112">
+        <v>14</v>
+      </c>
+      <c r="AZ112">
+        <v>12</v>
+      </c>
+      <c r="BA112">
+        <v>10</v>
+      </c>
+      <c r="BB112">
+        <v>7</v>
+      </c>
+      <c r="BC112">
+        <v>17</v>
+      </c>
+      <c r="BD112">
+        <v>3.18</v>
+      </c>
+      <c r="BE112">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF112">
+        <v>1.45</v>
+      </c>
+      <c r="BG112">
+        <v>1.19</v>
+      </c>
+      <c r="BH112">
+        <v>3.8</v>
+      </c>
+      <c r="BI112">
+        <v>1.38</v>
+      </c>
+      <c r="BJ112">
+        <v>2.62</v>
+      </c>
+      <c r="BK112">
+        <v>1.69</v>
+      </c>
+      <c r="BL112">
+        <v>2</v>
+      </c>
+      <c r="BM112">
+        <v>2.1</v>
+      </c>
+      <c r="BN112">
+        <v>1.59</v>
+      </c>
+      <c r="BO112">
+        <v>2.78</v>
+      </c>
+      <c r="BP112">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7776426</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45709.67708333334</v>
+      </c>
+      <c r="F113">
+        <v>23</v>
+      </c>
+      <c r="G113" t="s">
+        <v>71</v>
+      </c>
+      <c r="H113" t="s">
+        <v>70</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>2</v>
+      </c>
+      <c r="L113">
+        <v>2</v>
+      </c>
+      <c r="M113">
+        <v>4</v>
+      </c>
+      <c r="N113">
+        <v>6</v>
+      </c>
+      <c r="O113" t="s">
+        <v>162</v>
+      </c>
+      <c r="P113" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q113">
+        <v>3.2</v>
+      </c>
+      <c r="R113">
+        <v>2.19</v>
+      </c>
+      <c r="S113">
+        <v>3</v>
+      </c>
+      <c r="T113">
+        <v>1.34</v>
+      </c>
+      <c r="U113">
+        <v>3.04</v>
+      </c>
+      <c r="V113">
+        <v>2.55</v>
+      </c>
+      <c r="W113">
+        <v>1.45</v>
+      </c>
+      <c r="X113">
+        <v>6.65</v>
+      </c>
+      <c r="Y113">
+        <v>1.05</v>
+      </c>
+      <c r="Z113">
+        <v>2.77</v>
+      </c>
+      <c r="AA113">
+        <v>3.35</v>
+      </c>
+      <c r="AB113">
+        <v>2.43</v>
+      </c>
+      <c r="AC113">
+        <v>1.02</v>
+      </c>
+      <c r="AD113">
+        <v>10</v>
+      </c>
+      <c r="AE113">
+        <v>1.25</v>
+      </c>
+      <c r="AF113">
+        <v>3.7</v>
+      </c>
+      <c r="AG113">
+        <v>1.85</v>
+      </c>
+      <c r="AH113">
+        <v>1.89</v>
+      </c>
+      <c r="AI113">
+        <v>1.62</v>
+      </c>
+      <c r="AJ113">
+        <v>2.15</v>
+      </c>
+      <c r="AK113">
+        <v>1.49</v>
+      </c>
+      <c r="AL113">
+        <v>1.29</v>
+      </c>
+      <c r="AM113">
+        <v>1.43</v>
+      </c>
+      <c r="AN113">
+        <v>0.55</v>
+      </c>
+      <c r="AO113">
+        <v>1.09</v>
+      </c>
+      <c r="AP113">
+        <v>0.5</v>
+      </c>
+      <c r="AQ113">
+        <v>1.25</v>
+      </c>
+      <c r="AR113">
+        <v>1.52</v>
+      </c>
+      <c r="AS113">
+        <v>1.71</v>
+      </c>
+      <c r="AT113">
+        <v>3.23</v>
+      </c>
+      <c r="AU113">
+        <v>3</v>
+      </c>
+      <c r="AV113">
+        <v>8</v>
+      </c>
+      <c r="AW113">
+        <v>5</v>
+      </c>
+      <c r="AX113">
+        <v>7</v>
+      </c>
+      <c r="AY113">
+        <v>8</v>
+      </c>
+      <c r="AZ113">
+        <v>15</v>
+      </c>
+      <c r="BA113">
+        <v>4</v>
+      </c>
+      <c r="BB113">
+        <v>5</v>
+      </c>
+      <c r="BC113">
+        <v>9</v>
+      </c>
+      <c r="BD113">
+        <v>1.97</v>
+      </c>
+      <c r="BE113">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF113">
+        <v>2.05</v>
+      </c>
+      <c r="BG113">
+        <v>1.19</v>
+      </c>
+      <c r="BH113">
+        <v>3.78</v>
+      </c>
+      <c r="BI113">
+        <v>1.38</v>
+      </c>
+      <c r="BJ113">
+        <v>2.62</v>
+      </c>
+      <c r="BK113">
+        <v>1.69</v>
+      </c>
+      <c r="BL113">
+        <v>2</v>
+      </c>
+      <c r="BM113">
+        <v>2.12</v>
+      </c>
+      <c r="BN113">
+        <v>1.58</v>
+      </c>
+      <c r="BO113">
+        <v>2.81</v>
+      </c>
+      <c r="BP113">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="234">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1077,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP113"/>
+  <dimension ref="A1:BP114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5">
         <v>1.09</v>
@@ -4089,7 +4089,7 @@
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -5737,7 +5737,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ23">
         <v>1.27</v>
@@ -9239,7 +9239,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ40">
         <v>1.25</v>
@@ -10887,7 +10887,7 @@
         <v>2</v>
       </c>
       <c r="AP48">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ48">
         <v>1.73</v>
@@ -13153,7 +13153,7 @@
         <v>1.2</v>
       </c>
       <c r="AP59">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ59">
         <v>1.25</v>
@@ -15213,7 +15213,7 @@
         <v>1.83</v>
       </c>
       <c r="AP69">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ69">
         <v>2.18</v>
@@ -17067,7 +17067,7 @@
         <v>0.57</v>
       </c>
       <c r="AP78">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ78">
         <v>0.82</v>
@@ -18509,7 +18509,7 @@
         <v>0.63</v>
       </c>
       <c r="AP85">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ85">
         <v>0.82</v>
@@ -20569,7 +20569,7 @@
         <v>1.22</v>
       </c>
       <c r="AP95">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ95">
         <v>1.27</v>
@@ -23659,7 +23659,7 @@
         <v>1.2</v>
       </c>
       <c r="AP110">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ110">
         <v>1.25</v>
@@ -24356,6 +24356,212 @@
       </c>
       <c r="BP113">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7776427</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45710.58333333334</v>
+      </c>
+      <c r="F114">
+        <v>23</v>
+      </c>
+      <c r="G114" t="s">
+        <v>73</v>
+      </c>
+      <c r="H114" t="s">
+        <v>77</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114" t="s">
+        <v>84</v>
+      </c>
+      <c r="P114" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q114">
+        <v>3</v>
+      </c>
+      <c r="R114">
+        <v>2.17</v>
+      </c>
+      <c r="S114">
+        <v>3.2</v>
+      </c>
+      <c r="T114">
+        <v>1.35</v>
+      </c>
+      <c r="U114">
+        <v>2.98</v>
+      </c>
+      <c r="V114">
+        <v>2.6</v>
+      </c>
+      <c r="W114">
+        <v>1.44</v>
+      </c>
+      <c r="X114">
+        <v>7.2</v>
+      </c>
+      <c r="Y114">
+        <v>1.04</v>
+      </c>
+      <c r="Z114">
+        <v>2.71</v>
+      </c>
+      <c r="AA114">
+        <v>3.26</v>
+      </c>
+      <c r="AB114">
+        <v>2.54</v>
+      </c>
+      <c r="AC114">
+        <v>1.01</v>
+      </c>
+      <c r="AD114">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE114">
+        <v>1.26</v>
+      </c>
+      <c r="AF114">
+        <v>3.6</v>
+      </c>
+      <c r="AG114">
+        <v>1.91</v>
+      </c>
+      <c r="AH114">
+        <v>1.83</v>
+      </c>
+      <c r="AI114">
+        <v>1.64</v>
+      </c>
+      <c r="AJ114">
+        <v>2.12</v>
+      </c>
+      <c r="AK114">
+        <v>1.44</v>
+      </c>
+      <c r="AL114">
+        <v>1.29</v>
+      </c>
+      <c r="AM114">
+        <v>1.48</v>
+      </c>
+      <c r="AN114">
+        <v>1.36</v>
+      </c>
+      <c r="AO114">
+        <v>1</v>
+      </c>
+      <c r="AP114">
+        <v>1.33</v>
+      </c>
+      <c r="AQ114">
+        <v>1</v>
+      </c>
+      <c r="AR114">
+        <v>1.42</v>
+      </c>
+      <c r="AS114">
+        <v>1.59</v>
+      </c>
+      <c r="AT114">
+        <v>3.01</v>
+      </c>
+      <c r="AU114">
+        <v>5</v>
+      </c>
+      <c r="AV114">
+        <v>0</v>
+      </c>
+      <c r="AW114">
+        <v>12</v>
+      </c>
+      <c r="AX114">
+        <v>5</v>
+      </c>
+      <c r="AY114">
+        <v>17</v>
+      </c>
+      <c r="AZ114">
+        <v>5</v>
+      </c>
+      <c r="BA114">
+        <v>6</v>
+      </c>
+      <c r="BB114">
+        <v>1</v>
+      </c>
+      <c r="BC114">
+        <v>7</v>
+      </c>
+      <c r="BD114">
+        <v>2.01</v>
+      </c>
+      <c r="BE114">
+        <v>5.95</v>
+      </c>
+      <c r="BF114">
+        <v>2.21</v>
+      </c>
+      <c r="BG114">
+        <v>1.5</v>
+      </c>
+      <c r="BH114">
+        <v>2.47</v>
+      </c>
+      <c r="BI114">
+        <v>1.89</v>
+      </c>
+      <c r="BJ114">
+        <v>1.91</v>
+      </c>
+      <c r="BK114">
+        <v>2.36</v>
+      </c>
+      <c r="BL114">
+        <v>1.54</v>
+      </c>
+      <c r="BM114">
+        <v>3.28</v>
+      </c>
+      <c r="BN114">
+        <v>1.25</v>
+      </c>
+      <c r="BO114">
+        <v>4.25</v>
+      </c>
+      <c r="BP114">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="236">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -505,6 +505,9 @@
     <t>['12', '90+2']</t>
   </si>
   <si>
+    <t>['68', '90+3']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -716,6 +719,9 @@
   </si>
   <si>
     <t>['9', '63', '66', '79']</t>
+  </si>
+  <si>
+    <t>['38', '60', '73']</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP114"/>
+  <dimension ref="A1:BP116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1333,7 +1339,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1539,7 +1545,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1745,7 +1751,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -1826,7 +1832,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ4">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2235,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>0.82</v>
@@ -2569,7 +2575,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2981,7 +2987,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3059,10 +3065,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ10">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3393,7 +3399,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3599,7 +3605,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3805,7 +3811,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4011,7 +4017,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4217,7 +4223,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4295,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.09</v>
@@ -4423,7 +4429,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4504,7 +4510,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ17">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR17">
         <v>1.81</v>
@@ -4629,7 +4635,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4710,7 +4716,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ18">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR18">
         <v>1.54</v>
@@ -4835,7 +4841,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5041,7 +5047,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5119,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ20">
         <v>0.82</v>
@@ -5247,7 +5253,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5531,7 +5537,7 @@
         <v>1.5</v>
       </c>
       <c r="AP22">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ22">
         <v>1.25</v>
@@ -5659,7 +5665,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6071,7 +6077,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6149,7 +6155,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>1.25</v>
@@ -6277,7 +6283,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6483,7 +6489,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6689,7 +6695,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7101,7 +7107,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7182,7 +7188,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ30">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR30">
         <v>1.62</v>
@@ -7307,7 +7313,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7719,7 +7725,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7925,7 +7931,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8131,7 +8137,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8337,7 +8343,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8415,10 +8421,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR36">
         <v>2.16</v>
@@ -8543,7 +8549,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8827,10 +8833,10 @@
         <v>2.33</v>
       </c>
       <c r="AP38">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ38">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR38">
         <v>2.02</v>
@@ -8955,7 +8961,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9161,7 +9167,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9573,7 +9579,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9779,7 +9785,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9985,7 +9991,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10066,7 +10072,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ44">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -10397,7 +10403,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10475,7 +10481,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>1.09</v>
@@ -10603,7 +10609,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10890,7 +10896,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ48">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR48">
         <v>1.41</v>
@@ -11015,7 +11021,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11427,7 +11433,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11505,7 +11511,7 @@
         <v>0.8</v>
       </c>
       <c r="AP51">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ51">
         <v>1.25</v>
@@ -11633,7 +11639,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11839,7 +11845,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12045,7 +12051,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12126,7 +12132,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ54">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR54">
         <v>1.69</v>
@@ -12251,7 +12257,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12535,10 +12541,10 @@
         <v>1.8</v>
       </c>
       <c r="AP56">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR56">
         <v>1.95</v>
@@ -12663,7 +12669,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13075,7 +13081,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13359,7 +13365,7 @@
         <v>0.4</v>
       </c>
       <c r="AP60">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ60">
         <v>0.82</v>
@@ -13487,7 +13493,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13693,7 +13699,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -14105,7 +14111,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14392,7 +14398,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ65">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR65">
         <v>1.81</v>
@@ -14517,7 +14523,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14598,7 +14604,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ66">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR66">
         <v>1.6</v>
@@ -14723,7 +14729,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14929,7 +14935,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15007,7 +15013,7 @@
         <v>1.5</v>
       </c>
       <c r="AP68">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
         <v>1.25</v>
@@ -15135,7 +15141,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15216,7 +15222,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ69">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR69">
         <v>1.4</v>
@@ -15341,7 +15347,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15547,7 +15553,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15625,7 +15631,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ71">
         <v>1.27</v>
@@ -15753,7 +15759,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15959,7 +15965,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16040,7 +16046,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ73">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR73">
         <v>1.6</v>
@@ -16165,7 +16171,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16371,7 +16377,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16577,7 +16583,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16655,7 +16661,7 @@
         <v>1.43</v>
       </c>
       <c r="AP76">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ76">
         <v>1.27</v>
@@ -16783,7 +16789,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16864,7 +16870,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ77">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR77">
         <v>1.89</v>
@@ -16989,7 +16995,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17195,7 +17201,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17273,7 +17279,7 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17813,7 +17819,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18431,7 +18437,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18843,7 +18849,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -18924,7 +18930,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ87">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR87">
         <v>1.73</v>
@@ -19049,7 +19055,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19130,7 +19136,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ88">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR88">
         <v>1.6</v>
@@ -19255,7 +19261,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19333,7 +19339,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -19461,7 +19467,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19539,7 +19545,7 @@
         <v>1.13</v>
       </c>
       <c r="AP90">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ90">
         <v>1.09</v>
@@ -19667,7 +19673,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19873,7 +19879,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -19954,7 +19960,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ92">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR92">
         <v>1.59</v>
@@ -20079,7 +20085,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20285,7 +20291,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20697,7 +20703,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -20778,7 +20784,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ96">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR96">
         <v>1.68</v>
@@ -21187,7 +21193,7 @@
         <v>1.33</v>
       </c>
       <c r="AP98">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ98">
         <v>1.25</v>
@@ -21393,7 +21399,7 @@
         <v>0.89</v>
       </c>
       <c r="AP99">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ99">
         <v>0.82</v>
@@ -21521,7 +21527,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21933,7 +21939,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22139,7 +22145,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22345,7 +22351,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22426,7 +22432,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ104">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR104">
         <v>1.76</v>
@@ -22629,7 +22635,7 @@
         <v>1.2</v>
       </c>
       <c r="AP105">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ105">
         <v>1.09</v>
@@ -23456,7 +23462,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ109">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR109">
         <v>1.53</v>
@@ -23581,7 +23587,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23787,7 +23793,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -23865,7 +23871,7 @@
         <v>0.9</v>
       </c>
       <c r="AP111">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ111">
         <v>0.82</v>
@@ -24199,7 +24205,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24562,6 +24568,418 @@
       </c>
       <c r="BP114">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7776428</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45711.42708333334</v>
+      </c>
+      <c r="F115">
+        <v>23</v>
+      </c>
+      <c r="G115" t="s">
+        <v>74</v>
+      </c>
+      <c r="H115" t="s">
+        <v>72</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
+        <v>1</v>
+      </c>
+      <c r="O115" t="s">
+        <v>84</v>
+      </c>
+      <c r="P115" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q115">
+        <v>3.45</v>
+      </c>
+      <c r="R115">
+        <v>2.34</v>
+      </c>
+      <c r="S115">
+        <v>2.6</v>
+      </c>
+      <c r="T115">
+        <v>1.28</v>
+      </c>
+      <c r="U115">
+        <v>3.4</v>
+      </c>
+      <c r="V115">
+        <v>2.29</v>
+      </c>
+      <c r="W115">
+        <v>1.56</v>
+      </c>
+      <c r="X115">
+        <v>5.85</v>
+      </c>
+      <c r="Y115">
+        <v>1.08</v>
+      </c>
+      <c r="Z115">
+        <v>3.2</v>
+      </c>
+      <c r="AA115">
+        <v>3.58</v>
+      </c>
+      <c r="AB115">
+        <v>2.09</v>
+      </c>
+      <c r="AC115">
+        <v>1.01</v>
+      </c>
+      <c r="AD115">
+        <v>11</v>
+      </c>
+      <c r="AE115">
+        <v>1.18</v>
+      </c>
+      <c r="AF115">
+        <v>4.5</v>
+      </c>
+      <c r="AG115">
+        <v>1.6</v>
+      </c>
+      <c r="AH115">
+        <v>2.1</v>
+      </c>
+      <c r="AI115">
+        <v>1.5</v>
+      </c>
+      <c r="AJ115">
+        <v>2.41</v>
+      </c>
+      <c r="AK115">
+        <v>1.63</v>
+      </c>
+      <c r="AL115">
+        <v>1.27</v>
+      </c>
+      <c r="AM115">
+        <v>1.35</v>
+      </c>
+      <c r="AN115">
+        <v>2.18</v>
+      </c>
+      <c r="AO115">
+        <v>2.18</v>
+      </c>
+      <c r="AP115">
+        <v>2</v>
+      </c>
+      <c r="AQ115">
+        <v>2.25</v>
+      </c>
+      <c r="AR115">
+        <v>1.93</v>
+      </c>
+      <c r="AS115">
+        <v>1.88</v>
+      </c>
+      <c r="AT115">
+        <v>3.81</v>
+      </c>
+      <c r="AU115">
+        <v>2</v>
+      </c>
+      <c r="AV115">
+        <v>6</v>
+      </c>
+      <c r="AW115">
+        <v>7</v>
+      </c>
+      <c r="AX115">
+        <v>5</v>
+      </c>
+      <c r="AY115">
+        <v>9</v>
+      </c>
+      <c r="AZ115">
+        <v>11</v>
+      </c>
+      <c r="BA115">
+        <v>6</v>
+      </c>
+      <c r="BB115">
+        <v>4</v>
+      </c>
+      <c r="BC115">
+        <v>10</v>
+      </c>
+      <c r="BD115">
+        <v>2.3</v>
+      </c>
+      <c r="BE115">
+        <v>6.3</v>
+      </c>
+      <c r="BF115">
+        <v>1.91</v>
+      </c>
+      <c r="BG115">
+        <v>1.22</v>
+      </c>
+      <c r="BH115">
+        <v>3.5</v>
+      </c>
+      <c r="BI115">
+        <v>1.48</v>
+      </c>
+      <c r="BJ115">
+        <v>2.53</v>
+      </c>
+      <c r="BK115">
+        <v>1.81</v>
+      </c>
+      <c r="BL115">
+        <v>1.98</v>
+      </c>
+      <c r="BM115">
+        <v>2.25</v>
+      </c>
+      <c r="BN115">
+        <v>1.6</v>
+      </c>
+      <c r="BO115">
+        <v>2.97</v>
+      </c>
+      <c r="BP115">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7776429</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45711.42708333334</v>
+      </c>
+      <c r="F116">
+        <v>23</v>
+      </c>
+      <c r="G116" t="s">
+        <v>78</v>
+      </c>
+      <c r="H116" t="s">
+        <v>79</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>1</v>
+      </c>
+      <c r="K116">
+        <v>1</v>
+      </c>
+      <c r="L116">
+        <v>2</v>
+      </c>
+      <c r="M116">
+        <v>3</v>
+      </c>
+      <c r="N116">
+        <v>5</v>
+      </c>
+      <c r="O116" t="s">
+        <v>163</v>
+      </c>
+      <c r="P116" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q116">
+        <v>3.6</v>
+      </c>
+      <c r="R116">
+        <v>2.2</v>
+      </c>
+      <c r="S116">
+        <v>2.7</v>
+      </c>
+      <c r="T116">
+        <v>1.33</v>
+      </c>
+      <c r="U116">
+        <v>3.08</v>
+      </c>
+      <c r="V116">
+        <v>2.55</v>
+      </c>
+      <c r="W116">
+        <v>1.45</v>
+      </c>
+      <c r="X116">
+        <v>6.55</v>
+      </c>
+      <c r="Y116">
+        <v>1.06</v>
+      </c>
+      <c r="Z116">
+        <v>3.33</v>
+      </c>
+      <c r="AA116">
+        <v>3.45</v>
+      </c>
+      <c r="AB116">
+        <v>2.08</v>
+      </c>
+      <c r="AC116">
+        <v>1.01</v>
+      </c>
+      <c r="AD116">
+        <v>11</v>
+      </c>
+      <c r="AE116">
+        <v>1.25</v>
+      </c>
+      <c r="AF116">
+        <v>3.7</v>
+      </c>
+      <c r="AG116">
+        <v>1.77</v>
+      </c>
+      <c r="AH116">
+        <v>1.98</v>
+      </c>
+      <c r="AI116">
+        <v>1.63</v>
+      </c>
+      <c r="AJ116">
+        <v>2.14</v>
+      </c>
+      <c r="AK116">
+        <v>1.61</v>
+      </c>
+      <c r="AL116">
+        <v>1.28</v>
+      </c>
+      <c r="AM116">
+        <v>1.34</v>
+      </c>
+      <c r="AN116">
+        <v>1.55</v>
+      </c>
+      <c r="AO116">
+        <v>1.73</v>
+      </c>
+      <c r="AP116">
+        <v>1.42</v>
+      </c>
+      <c r="AQ116">
+        <v>1.83</v>
+      </c>
+      <c r="AR116">
+        <v>1.59</v>
+      </c>
+      <c r="AS116">
+        <v>1.79</v>
+      </c>
+      <c r="AT116">
+        <v>3.38</v>
+      </c>
+      <c r="AU116">
+        <v>3</v>
+      </c>
+      <c r="AV116">
+        <v>6</v>
+      </c>
+      <c r="AW116">
+        <v>14</v>
+      </c>
+      <c r="AX116">
+        <v>10</v>
+      </c>
+      <c r="AY116">
+        <v>17</v>
+      </c>
+      <c r="AZ116">
+        <v>16</v>
+      </c>
+      <c r="BA116">
+        <v>2</v>
+      </c>
+      <c r="BB116">
+        <v>1</v>
+      </c>
+      <c r="BC116">
+        <v>3</v>
+      </c>
+      <c r="BD116">
+        <v>2.8</v>
+      </c>
+      <c r="BE116">
+        <v>6.3</v>
+      </c>
+      <c r="BF116">
+        <v>1.66</v>
+      </c>
+      <c r="BG116">
+        <v>1.36</v>
+      </c>
+      <c r="BH116">
+        <v>2.7</v>
+      </c>
+      <c r="BI116">
+        <v>1.76</v>
+      </c>
+      <c r="BJ116">
+        <v>2.02</v>
+      </c>
+      <c r="BK116">
+        <v>2.22</v>
+      </c>
+      <c r="BL116">
+        <v>1.62</v>
+      </c>
+      <c r="BM116">
+        <v>2.88</v>
+      </c>
+      <c r="BN116">
+        <v>1.32</v>
+      </c>
+      <c r="BO116">
+        <v>4.05</v>
+      </c>
+      <c r="BP116">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="240">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,12 @@
     <t>['68', '90+3']</t>
   </si>
   <si>
+    <t>['31', '37']</t>
+  </si>
+  <si>
+    <t>['41', '88']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -722,6 +728,12 @@
   </si>
   <si>
     <t>['38', '60', '73']</t>
+  </si>
+  <si>
+    <t>['41']</t>
+  </si>
+  <si>
+    <t>['23', '45+1']</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP116"/>
+  <dimension ref="A1:BP118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1339,7 +1351,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1545,7 +1557,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1751,7 +1763,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2038,7 +2050,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ5">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2244,7 +2256,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2447,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ7">
         <v>1.27</v>
@@ -2575,7 +2587,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2987,7 +2999,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3271,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>0.82</v>
@@ -3399,7 +3411,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3605,7 +3617,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3683,7 +3695,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>1.25</v>
@@ -3811,7 +3823,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4017,7 +4029,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4223,7 +4235,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4304,7 +4316,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>1.95</v>
@@ -4429,7 +4441,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4507,7 +4519,7 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ17">
         <v>2.25</v>
@@ -4635,7 +4647,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4841,7 +4853,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5047,7 +5059,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5128,7 +5140,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ20">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR20">
         <v>1.99</v>
@@ -5253,7 +5265,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5665,7 +5677,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6077,7 +6089,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6283,7 +6295,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6361,10 +6373,10 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR26">
         <v>1.45</v>
@@ -6489,7 +6501,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6695,7 +6707,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6982,7 +6994,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ29">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>1.46</v>
@@ -7107,7 +7119,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7313,7 +7325,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7597,10 +7609,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ32">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -7725,7 +7737,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7931,7 +7943,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8137,7 +8149,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8215,7 +8227,7 @@
         <v>1.33</v>
       </c>
       <c r="AP35">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
         <v>1.09</v>
@@ -8343,7 +8355,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8549,7 +8561,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8630,7 +8642,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ37">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -8961,7 +8973,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9167,7 +9179,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9579,7 +9591,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9657,7 +9669,7 @@
         <v>1.75</v>
       </c>
       <c r="AP42">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -9785,7 +9797,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9866,7 +9878,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ43">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR43">
         <v>1.64</v>
@@ -9991,7 +10003,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10275,7 +10287,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>1.25</v>
@@ -10403,7 +10415,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10609,7 +10621,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11021,7 +11033,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11102,7 +11114,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ49">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR49">
         <v>1.57</v>
@@ -11433,7 +11445,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11639,7 +11651,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11845,7 +11857,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11926,7 +11938,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ53">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR53">
         <v>1.54</v>
@@ -12051,7 +12063,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12257,7 +12269,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12335,7 +12347,7 @@
         <v>1.4</v>
       </c>
       <c r="AP55">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ55">
         <v>1.09</v>
@@ -12669,7 +12681,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12956,7 +12968,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ58">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR58">
         <v>1.33</v>
@@ -13081,7 +13093,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13493,7 +13505,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13571,7 +13583,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ61">
         <v>1.27</v>
@@ -13699,7 +13711,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13780,7 +13792,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ62">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.61</v>
@@ -14111,7 +14123,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14189,7 +14201,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ64">
         <v>0.82</v>
@@ -14523,7 +14535,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14729,7 +14741,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14807,10 +14819,10 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ67">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR67">
         <v>1.46</v>
@@ -14935,7 +14947,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15141,7 +15153,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15347,7 +15359,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15425,7 +15437,7 @@
         <v>1.67</v>
       </c>
       <c r="AP70">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15553,7 +15565,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15759,7 +15771,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15965,7 +15977,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16171,7 +16183,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16252,7 +16264,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ74">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR74">
         <v>1.53</v>
@@ -16377,7 +16389,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16455,7 +16467,7 @@
         <v>1.29</v>
       </c>
       <c r="AP75">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ75">
         <v>1.25</v>
@@ -16583,7 +16595,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16789,7 +16801,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16867,7 +16879,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>2.25</v>
@@ -16995,7 +17007,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17076,7 +17088,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ78">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR78">
         <v>1.35</v>
@@ -17201,7 +17213,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17819,7 +17831,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -17897,10 +17909,10 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR82">
         <v>1.78</v>
@@ -18437,7 +18449,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18724,7 +18736,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ86">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR86">
         <v>1.62</v>
@@ -18849,7 +18861,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -18927,7 +18939,7 @@
         <v>1.88</v>
       </c>
       <c r="AP87">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ87">
         <v>1.83</v>
@@ -19055,7 +19067,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19261,7 +19273,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19467,7 +19479,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19673,7 +19685,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19879,7 +19891,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20085,7 +20097,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20166,7 +20178,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ93">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.57</v>
@@ -20291,7 +20303,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20369,7 +20381,7 @@
         <v>0.89</v>
       </c>
       <c r="AP94">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>0.82</v>
@@ -20703,7 +20715,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -20987,7 +20999,7 @@
         <v>1.11</v>
       </c>
       <c r="AP97">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21402,7 +21414,7 @@
         <v>2</v>
       </c>
       <c r="AQ99">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR99">
         <v>1.93</v>
@@ -21527,7 +21539,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21939,7 +21951,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22145,7 +22157,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22351,7 +22363,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22429,7 +22441,7 @@
         <v>2.1</v>
       </c>
       <c r="AP104">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ104">
         <v>2.25</v>
@@ -22638,7 +22650,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR105">
         <v>1.9</v>
@@ -22841,7 +22853,7 @@
         <v>1.2</v>
       </c>
       <c r="AP106">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
         <v>1.09</v>
@@ -23587,7 +23599,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23793,7 +23805,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -23874,7 +23886,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ111">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR111">
         <v>1.61</v>
@@ -24205,7 +24217,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24823,7 +24835,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -24980,6 +24992,418 @@
       </c>
       <c r="BP116">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7776430</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45716.64583333334</v>
+      </c>
+      <c r="F117">
+        <v>24</v>
+      </c>
+      <c r="G117" t="s">
+        <v>75</v>
+      </c>
+      <c r="H117" t="s">
+        <v>78</v>
+      </c>
+      <c r="I117">
+        <v>2</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117">
+        <v>3</v>
+      </c>
+      <c r="L117">
+        <v>2</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="N117">
+        <v>3</v>
+      </c>
+      <c r="O117" t="s">
+        <v>164</v>
+      </c>
+      <c r="P117" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q117">
+        <v>2.42</v>
+      </c>
+      <c r="R117">
+        <v>2.18</v>
+      </c>
+      <c r="S117">
+        <v>4.1</v>
+      </c>
+      <c r="T117">
+        <v>1.33</v>
+      </c>
+      <c r="U117">
+        <v>3.1</v>
+      </c>
+      <c r="V117">
+        <v>2.61</v>
+      </c>
+      <c r="W117">
+        <v>1.44</v>
+      </c>
+      <c r="X117">
+        <v>6.35</v>
+      </c>
+      <c r="Y117">
+        <v>1.06</v>
+      </c>
+      <c r="Z117">
+        <v>1.92</v>
+      </c>
+      <c r="AA117">
+        <v>3.59</v>
+      </c>
+      <c r="AB117">
+        <v>3.68</v>
+      </c>
+      <c r="AC117">
+        <v>1.02</v>
+      </c>
+      <c r="AD117">
+        <v>10</v>
+      </c>
+      <c r="AE117">
+        <v>1.19</v>
+      </c>
+      <c r="AF117">
+        <v>3.8</v>
+      </c>
+      <c r="AG117">
+        <v>1.7</v>
+      </c>
+      <c r="AH117">
+        <v>1.95</v>
+      </c>
+      <c r="AI117">
+        <v>1.63</v>
+      </c>
+      <c r="AJ117">
+        <v>2.09</v>
+      </c>
+      <c r="AK117">
+        <v>1.24</v>
+      </c>
+      <c r="AL117">
+        <v>1.24</v>
+      </c>
+      <c r="AM117">
+        <v>1.8</v>
+      </c>
+      <c r="AN117">
+        <v>1.27</v>
+      </c>
+      <c r="AO117">
+        <v>1.09</v>
+      </c>
+      <c r="AP117">
+        <v>1.42</v>
+      </c>
+      <c r="AQ117">
+        <v>1</v>
+      </c>
+      <c r="AR117">
+        <v>1.73</v>
+      </c>
+      <c r="AS117">
+        <v>1.34</v>
+      </c>
+      <c r="AT117">
+        <v>3.07</v>
+      </c>
+      <c r="AU117">
+        <v>8</v>
+      </c>
+      <c r="AV117">
+        <v>10</v>
+      </c>
+      <c r="AW117">
+        <v>8</v>
+      </c>
+      <c r="AX117">
+        <v>7</v>
+      </c>
+      <c r="AY117">
+        <v>16</v>
+      </c>
+      <c r="AZ117">
+        <v>17</v>
+      </c>
+      <c r="BA117">
+        <v>3</v>
+      </c>
+      <c r="BB117">
+        <v>4</v>
+      </c>
+      <c r="BC117">
+        <v>7</v>
+      </c>
+      <c r="BD117">
+        <v>1.48</v>
+      </c>
+      <c r="BE117">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF117">
+        <v>3.12</v>
+      </c>
+      <c r="BG117">
+        <v>1.36</v>
+      </c>
+      <c r="BH117">
+        <v>2.7</v>
+      </c>
+      <c r="BI117">
+        <v>1.75</v>
+      </c>
+      <c r="BJ117">
+        <v>2.03</v>
+      </c>
+      <c r="BK117">
+        <v>2.2</v>
+      </c>
+      <c r="BL117">
+        <v>1.64</v>
+      </c>
+      <c r="BM117">
+        <v>2.88</v>
+      </c>
+      <c r="BN117">
+        <v>1.32</v>
+      </c>
+      <c r="BO117">
+        <v>4.6</v>
+      </c>
+      <c r="BP117">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7776431</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45716.67708333334</v>
+      </c>
+      <c r="F118">
+        <v>24</v>
+      </c>
+      <c r="G118" t="s">
+        <v>79</v>
+      </c>
+      <c r="H118" t="s">
+        <v>76</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>2</v>
+      </c>
+      <c r="K118">
+        <v>3</v>
+      </c>
+      <c r="L118">
+        <v>2</v>
+      </c>
+      <c r="M118">
+        <v>2</v>
+      </c>
+      <c r="N118">
+        <v>4</v>
+      </c>
+      <c r="O118" t="s">
+        <v>165</v>
+      </c>
+      <c r="P118" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q118">
+        <v>1.82</v>
+      </c>
+      <c r="R118">
+        <v>2.5</v>
+      </c>
+      <c r="S118">
+        <v>5.95</v>
+      </c>
+      <c r="T118">
+        <v>1.23</v>
+      </c>
+      <c r="U118">
+        <v>3.64</v>
+      </c>
+      <c r="V118">
+        <v>2.25</v>
+      </c>
+      <c r="W118">
+        <v>1.6</v>
+      </c>
+      <c r="X118">
+        <v>5.1</v>
+      </c>
+      <c r="Y118">
+        <v>1.12</v>
+      </c>
+      <c r="Z118">
+        <v>1.4</v>
+      </c>
+      <c r="AA118">
+        <v>4.8</v>
+      </c>
+      <c r="AB118">
+        <v>6.6</v>
+      </c>
+      <c r="AC118">
+        <v>1.01</v>
+      </c>
+      <c r="AD118">
+        <v>13</v>
+      </c>
+      <c r="AE118">
+        <v>1.11</v>
+      </c>
+      <c r="AF118">
+        <v>4.95</v>
+      </c>
+      <c r="AG118">
+        <v>1.48</v>
+      </c>
+      <c r="AH118">
+        <v>2.46</v>
+      </c>
+      <c r="AI118">
+        <v>1.67</v>
+      </c>
+      <c r="AJ118">
+        <v>2.03</v>
+      </c>
+      <c r="AK118">
+        <v>1.07</v>
+      </c>
+      <c r="AL118">
+        <v>1.14</v>
+      </c>
+      <c r="AM118">
+        <v>2.75</v>
+      </c>
+      <c r="AN118">
+        <v>2.09</v>
+      </c>
+      <c r="AO118">
+        <v>0.82</v>
+      </c>
+      <c r="AP118">
+        <v>2</v>
+      </c>
+      <c r="AQ118">
+        <v>0.83</v>
+      </c>
+      <c r="AR118">
+        <v>1.72</v>
+      </c>
+      <c r="AS118">
+        <v>1.39</v>
+      </c>
+      <c r="AT118">
+        <v>3.11</v>
+      </c>
+      <c r="AU118">
+        <v>5</v>
+      </c>
+      <c r="AV118">
+        <v>4</v>
+      </c>
+      <c r="AW118">
+        <v>11</v>
+      </c>
+      <c r="AX118">
+        <v>2</v>
+      </c>
+      <c r="AY118">
+        <v>16</v>
+      </c>
+      <c r="AZ118">
+        <v>6</v>
+      </c>
+      <c r="BA118">
+        <v>5</v>
+      </c>
+      <c r="BB118">
+        <v>0</v>
+      </c>
+      <c r="BC118">
+        <v>5</v>
+      </c>
+      <c r="BD118">
+        <v>1.19</v>
+      </c>
+      <c r="BE118">
+        <v>11</v>
+      </c>
+      <c r="BF118">
+        <v>5.35</v>
+      </c>
+      <c r="BG118">
+        <v>1.2</v>
+      </c>
+      <c r="BH118">
+        <v>3.82</v>
+      </c>
+      <c r="BI118">
+        <v>1.35</v>
+      </c>
+      <c r="BJ118">
+        <v>2.74</v>
+      </c>
+      <c r="BK118">
+        <v>1.68</v>
+      </c>
+      <c r="BL118">
+        <v>2.14</v>
+      </c>
+      <c r="BM118">
+        <v>2.11</v>
+      </c>
+      <c r="BN118">
+        <v>1.7</v>
+      </c>
+      <c r="BO118">
+        <v>2.66</v>
+      </c>
+      <c r="BP118">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="241">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -512,6 +512,9 @@
   </si>
   <si>
     <t>['41', '88']</t>
+  </si>
+  <si>
+    <t>['5', '43', '65']</t>
   </si>
   <si>
     <t>['25', '90+2']</t>
@@ -1095,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP118"/>
+  <dimension ref="A1:BP119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1351,7 +1354,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1557,7 +1560,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1763,7 +1766,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -1841,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4">
         <v>1.83</v>
@@ -2462,7 +2465,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ7">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2587,7 +2590,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2999,7 +3002,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3411,7 +3414,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3492,7 +3495,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ12">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR12">
         <v>1.34</v>
@@ -3617,7 +3620,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3823,7 +3826,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3901,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14">
         <v>1.25</v>
@@ -4029,7 +4032,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4235,7 +4238,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4441,7 +4444,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4647,7 +4650,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4853,7 +4856,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5059,7 +5062,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5265,7 +5268,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5677,7 +5680,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5758,7 +5761,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ23">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR23">
         <v>1.3</v>
@@ -5961,7 +5964,7 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6089,7 +6092,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6295,7 +6298,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6501,7 +6504,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6707,7 +6710,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7119,7 +7122,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7325,7 +7328,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7403,7 +7406,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ31">
         <v>1.09</v>
@@ -7737,7 +7740,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7943,7 +7946,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8149,7 +8152,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8355,7 +8358,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8561,7 +8564,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8973,7 +8976,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9051,10 +9054,10 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ39">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR39">
         <v>1.16</v>
@@ -9179,7 +9182,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9591,7 +9594,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9797,7 +9800,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10003,7 +10006,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10415,7 +10418,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10621,7 +10624,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10702,7 +10705,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ47">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR47">
         <v>1.79</v>
@@ -11033,7 +11036,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11317,7 +11320,7 @@
         <v>0.25</v>
       </c>
       <c r="AP50">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ50">
         <v>0.82</v>
@@ -11445,7 +11448,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11651,7 +11654,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11857,7 +11860,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12063,7 +12066,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12269,7 +12272,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12681,7 +12684,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12965,7 +12968,7 @@
         <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58">
         <v>0.83</v>
@@ -13093,7 +13096,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13505,7 +13508,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13586,7 +13589,7 @@
         <v>2</v>
       </c>
       <c r="AQ61">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -13711,7 +13714,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -14123,7 +14126,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14535,7 +14538,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14741,7 +14744,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14947,7 +14950,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15153,7 +15156,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15359,7 +15362,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15565,7 +15568,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15646,7 +15649,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ71">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR71">
         <v>1.83</v>
@@ -15771,7 +15774,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15977,7 +15980,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16183,7 +16186,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16261,7 +16264,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ74">
         <v>1</v>
@@ -16389,7 +16392,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16595,7 +16598,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16676,7 +16679,7 @@
         <v>2</v>
       </c>
       <c r="AQ76">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR76">
         <v>1.84</v>
@@ -16801,7 +16804,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17007,7 +17010,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17213,7 +17216,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17831,7 +17834,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18118,7 +18121,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ83">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR83">
         <v>1.62</v>
@@ -18321,7 +18324,7 @@
         <v>0.86</v>
       </c>
       <c r="AP84">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84">
         <v>1.25</v>
@@ -18449,7 +18452,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18861,7 +18864,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19067,7 +19070,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19273,7 +19276,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19479,7 +19482,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19685,7 +19688,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19891,7 +19894,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20097,7 +20100,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20303,7 +20306,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20590,7 +20593,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ95">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR95">
         <v>1.4</v>
@@ -20715,7 +20718,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21539,7 +21542,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21617,7 +21620,7 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ100">
         <v>1.09</v>
@@ -21951,7 +21954,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22032,7 +22035,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ102">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR102">
         <v>1.56</v>
@@ -22157,7 +22160,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22363,7 +22366,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -23471,7 +23474,7 @@
         <v>1.9</v>
       </c>
       <c r="AP109">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ109">
         <v>1.83</v>
@@ -23599,7 +23602,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23805,7 +23808,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -24217,7 +24220,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24835,7 +24838,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -25041,7 +25044,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q117">
         <v>2.42</v>
@@ -25247,7 +25250,7 @@
         <v>165</v>
       </c>
       <c r="P118" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q118">
         <v>1.82</v>
@@ -25404,6 +25407,212 @@
       </c>
       <c r="BP118">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7776432</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45717.58333333334</v>
+      </c>
+      <c r="F119">
+        <v>24</v>
+      </c>
+      <c r="G119" t="s">
+        <v>72</v>
+      </c>
+      <c r="H119" t="s">
+        <v>71</v>
+      </c>
+      <c r="I119">
+        <v>2</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>2</v>
+      </c>
+      <c r="L119">
+        <v>3</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>3</v>
+      </c>
+      <c r="O119" t="s">
+        <v>166</v>
+      </c>
+      <c r="P119" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q119">
+        <v>1.98</v>
+      </c>
+      <c r="R119">
+        <v>2.42</v>
+      </c>
+      <c r="S119">
+        <v>5.6</v>
+      </c>
+      <c r="T119">
+        <v>1.3</v>
+      </c>
+      <c r="U119">
+        <v>3.26</v>
+      </c>
+      <c r="V119">
+        <v>2.38</v>
+      </c>
+      <c r="W119">
+        <v>1.53</v>
+      </c>
+      <c r="X119">
+        <v>6</v>
+      </c>
+      <c r="Y119">
+        <v>1.07</v>
+      </c>
+      <c r="Z119">
+        <v>1.47</v>
+      </c>
+      <c r="AA119">
+        <v>4.4</v>
+      </c>
+      <c r="AB119">
+        <v>6.2</v>
+      </c>
+      <c r="AC119">
+        <v>1.01</v>
+      </c>
+      <c r="AD119">
+        <v>11</v>
+      </c>
+      <c r="AE119">
+        <v>1.21</v>
+      </c>
+      <c r="AF119">
+        <v>4.1</v>
+      </c>
+      <c r="AG119">
+        <v>1.8</v>
+      </c>
+      <c r="AH119">
+        <v>1.94</v>
+      </c>
+      <c r="AI119">
+        <v>1.75</v>
+      </c>
+      <c r="AJ119">
+        <v>1.96</v>
+      </c>
+      <c r="AK119">
+        <v>1.14</v>
+      </c>
+      <c r="AL119">
+        <v>1.19</v>
+      </c>
+      <c r="AM119">
+        <v>2.34</v>
+      </c>
+      <c r="AN119">
+        <v>1.55</v>
+      </c>
+      <c r="AO119">
+        <v>1.27</v>
+      </c>
+      <c r="AP119">
+        <v>1.67</v>
+      </c>
+      <c r="AQ119">
+        <v>1.17</v>
+      </c>
+      <c r="AR119">
+        <v>1.51</v>
+      </c>
+      <c r="AS119">
+        <v>1.28</v>
+      </c>
+      <c r="AT119">
+        <v>2.79</v>
+      </c>
+      <c r="AU119">
+        <v>7</v>
+      </c>
+      <c r="AV119">
+        <v>2</v>
+      </c>
+      <c r="AW119">
+        <v>8</v>
+      </c>
+      <c r="AX119">
+        <v>10</v>
+      </c>
+      <c r="AY119">
+        <v>15</v>
+      </c>
+      <c r="AZ119">
+        <v>12</v>
+      </c>
+      <c r="BA119">
+        <v>2</v>
+      </c>
+      <c r="BB119">
+        <v>2</v>
+      </c>
+      <c r="BC119">
+        <v>4</v>
+      </c>
+      <c r="BD119">
+        <v>1.24</v>
+      </c>
+      <c r="BE119">
+        <v>8.4</v>
+      </c>
+      <c r="BF119">
+        <v>5.2</v>
+      </c>
+      <c r="BG119">
+        <v>1.18</v>
+      </c>
+      <c r="BH119">
+        <v>4.1</v>
+      </c>
+      <c r="BI119">
+        <v>1.3</v>
+      </c>
+      <c r="BJ119">
+        <v>2.97</v>
+      </c>
+      <c r="BK119">
+        <v>1.6</v>
+      </c>
+      <c r="BL119">
+        <v>2.25</v>
+      </c>
+      <c r="BM119">
+        <v>2</v>
+      </c>
+      <c r="BN119">
+        <v>1.79</v>
+      </c>
+      <c r="BO119">
+        <v>2.54</v>
+      </c>
+      <c r="BP119">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="242">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -515,6 +515,9 @@
   </si>
   <si>
     <t>['5', '43', '65']</t>
+  </si>
+  <si>
+    <t>['53']</t>
   </si>
   <si>
     <t>['25', '90+2']</t>
@@ -1098,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1354,7 +1357,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1432,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ2">
         <v>1.25</v>
@@ -1560,7 +1563,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1766,7 +1769,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2590,7 +2593,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2671,7 +2674,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3002,7 +3005,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3414,7 +3417,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3620,7 +3623,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3826,7 +3829,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4032,7 +4035,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4238,7 +4241,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4444,7 +4447,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4650,7 +4653,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4856,7 +4859,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -4934,10 +4937,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ19">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR19">
         <v>1.52</v>
@@ -5062,7 +5065,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5268,7 +5271,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5680,7 +5683,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6092,7 +6095,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6298,7 +6301,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6504,7 +6507,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6582,7 +6585,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ27">
         <v>0.82</v>
@@ -6710,7 +6713,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7122,7 +7125,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7328,7 +7331,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7409,7 +7412,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ31">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR31">
         <v>1.17</v>
@@ -7740,7 +7743,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7946,7 +7949,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8152,7 +8155,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8233,7 +8236,7 @@
         <v>2</v>
       </c>
       <c r="AQ35">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR35">
         <v>1.63</v>
@@ -8358,7 +8361,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8564,7 +8567,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8642,7 +8645,7 @@
         <v>1.33</v>
       </c>
       <c r="AP37">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37">
         <v>0.83</v>
@@ -8976,7 +8979,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9182,7 +9185,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9594,7 +9597,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9800,7 +9803,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10006,7 +10009,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10418,7 +10421,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10499,7 +10502,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR46">
         <v>2</v>
@@ -10624,7 +10627,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10702,7 +10705,7 @@
         <v>2.25</v>
       </c>
       <c r="AP47">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ47">
         <v>1.17</v>
@@ -11036,7 +11039,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11448,7 +11451,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11654,7 +11657,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11732,7 +11735,7 @@
         <v>1.4</v>
       </c>
       <c r="AP52">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ52">
         <v>1</v>
@@ -11860,7 +11863,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12066,7 +12069,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12272,7 +12275,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12353,7 +12356,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ55">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR55">
         <v>1.41</v>
@@ -12684,7 +12687,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13096,7 +13099,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13508,7 +13511,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13714,7 +13717,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13792,7 +13795,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14001,7 +14004,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ63">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR63">
         <v>1.59</v>
@@ -14126,7 +14129,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14538,7 +14541,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14744,7 +14747,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14950,7 +14953,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15156,7 +15159,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15362,7 +15365,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15568,7 +15571,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15774,7 +15777,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15855,7 +15858,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ72">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR72">
         <v>1.68</v>
@@ -15980,7 +15983,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16058,7 +16061,7 @@
         <v>1.71</v>
       </c>
       <c r="AP73">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ73">
         <v>1.83</v>
@@ -16186,7 +16189,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16392,7 +16395,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16598,7 +16601,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16804,7 +16807,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17010,7 +17013,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17216,7 +17219,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17834,7 +17837,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18452,7 +18455,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18864,7 +18867,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19070,7 +19073,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19148,7 +19151,7 @@
         <v>1.88</v>
       </c>
       <c r="AP88">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ88">
         <v>2.25</v>
@@ -19276,7 +19279,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19482,7 +19485,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19563,7 +19566,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ90">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -19688,7 +19691,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19766,7 +19769,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ91">
         <v>1.25</v>
@@ -19894,7 +19897,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20100,7 +20103,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20306,7 +20309,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20718,7 +20721,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21542,7 +21545,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21623,7 +21626,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ100">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR100">
         <v>1.58</v>
@@ -21954,7 +21957,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22160,7 +22163,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22366,7 +22369,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22859,7 +22862,7 @@
         <v>2</v>
       </c>
       <c r="AQ106">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR106">
         <v>1.72</v>
@@ -23062,7 +23065,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ107">
         <v>0.82</v>
@@ -23602,7 +23605,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23808,7 +23811,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -24220,7 +24223,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24838,7 +24841,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -25044,7 +25047,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q117">
         <v>2.42</v>
@@ -25250,7 +25253,7 @@
         <v>165</v>
       </c>
       <c r="P118" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q118">
         <v>1.82</v>
@@ -25613,6 +25616,212 @@
       </c>
       <c r="BP119">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7776433</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45718.42708333334</v>
+      </c>
+      <c r="F120">
+        <v>24</v>
+      </c>
+      <c r="G120" t="s">
+        <v>70</v>
+      </c>
+      <c r="H120" t="s">
+        <v>73</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120">
+        <v>1</v>
+      </c>
+      <c r="N120">
+        <v>2</v>
+      </c>
+      <c r="O120" t="s">
+        <v>167</v>
+      </c>
+      <c r="P120" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q120">
+        <v>2.9</v>
+      </c>
+      <c r="R120">
+        <v>2.15</v>
+      </c>
+      <c r="S120">
+        <v>3.35</v>
+      </c>
+      <c r="T120">
+        <v>1.35</v>
+      </c>
+      <c r="U120">
+        <v>2.98</v>
+      </c>
+      <c r="V120">
+        <v>2.65</v>
+      </c>
+      <c r="W120">
+        <v>1.42</v>
+      </c>
+      <c r="X120">
+        <v>6.85</v>
+      </c>
+      <c r="Y120">
+        <v>1.05</v>
+      </c>
+      <c r="Z120">
+        <v>2.39</v>
+      </c>
+      <c r="AA120">
+        <v>3.36</v>
+      </c>
+      <c r="AB120">
+        <v>2.82</v>
+      </c>
+      <c r="AC120">
+        <v>1</v>
+      </c>
+      <c r="AD120">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE120">
+        <v>1.27</v>
+      </c>
+      <c r="AF120">
+        <v>3.5</v>
+      </c>
+      <c r="AG120">
+        <v>1.83</v>
+      </c>
+      <c r="AH120">
+        <v>1.91</v>
+      </c>
+      <c r="AI120">
+        <v>1.67</v>
+      </c>
+      <c r="AJ120">
+        <v>2.08</v>
+      </c>
+      <c r="AK120">
+        <v>1.4</v>
+      </c>
+      <c r="AL120">
+        <v>1.28</v>
+      </c>
+      <c r="AM120">
+        <v>1.53</v>
+      </c>
+      <c r="AN120">
+        <v>1.27</v>
+      </c>
+      <c r="AO120">
+        <v>1.09</v>
+      </c>
+      <c r="AP120">
+        <v>1.25</v>
+      </c>
+      <c r="AQ120">
+        <v>1.08</v>
+      </c>
+      <c r="AR120">
+        <v>1.5</v>
+      </c>
+      <c r="AS120">
+        <v>1.56</v>
+      </c>
+      <c r="AT120">
+        <v>3.06</v>
+      </c>
+      <c r="AU120">
+        <v>6</v>
+      </c>
+      <c r="AV120">
+        <v>3</v>
+      </c>
+      <c r="AW120">
+        <v>5</v>
+      </c>
+      <c r="AX120">
+        <v>7</v>
+      </c>
+      <c r="AY120">
+        <v>11</v>
+      </c>
+      <c r="AZ120">
+        <v>10</v>
+      </c>
+      <c r="BA120">
+        <v>2</v>
+      </c>
+      <c r="BB120">
+        <v>4</v>
+      </c>
+      <c r="BC120">
+        <v>6</v>
+      </c>
+      <c r="BD120">
+        <v>2.1</v>
+      </c>
+      <c r="BE120">
+        <v>6.2</v>
+      </c>
+      <c r="BF120">
+        <v>2.08</v>
+      </c>
+      <c r="BG120">
+        <v>1.26</v>
+      </c>
+      <c r="BH120">
+        <v>3.22</v>
+      </c>
+      <c r="BI120">
+        <v>1.55</v>
+      </c>
+      <c r="BJ120">
+        <v>2.34</v>
+      </c>
+      <c r="BK120">
+        <v>1.94</v>
+      </c>
+      <c r="BL120">
+        <v>1.85</v>
+      </c>
+      <c r="BM120">
+        <v>2.44</v>
+      </c>
+      <c r="BN120">
+        <v>1.51</v>
+      </c>
+      <c r="BO120">
+        <v>3.28</v>
+      </c>
+      <c r="BP120">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="244">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -520,6 +520,9 @@
     <t>['53']</t>
   </si>
   <si>
+    <t>['14', '34', '87']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -740,6 +743,9 @@
   </si>
   <si>
     <t>['23', '45+1']</t>
+  </si>
+  <si>
+    <t>['70', '79']</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1357,7 +1363,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1563,7 +1569,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1769,7 +1775,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2593,7 +2599,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2877,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ9">
         <v>1.25</v>
@@ -3005,7 +3011,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3292,7 +3298,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3417,7 +3423,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3623,7 +3629,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3829,7 +3835,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4035,7 +4041,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4241,7 +4247,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4447,7 +4453,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4653,7 +4659,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4731,7 +4737,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ18">
         <v>1.83</v>
@@ -4859,7 +4865,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5065,7 +5071,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5271,7 +5277,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5352,7 +5358,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ21">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR21">
         <v>1.63</v>
@@ -5683,7 +5689,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6095,7 +6101,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6301,7 +6307,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6507,7 +6513,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6588,7 +6594,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ27">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR27">
         <v>1.47</v>
@@ -6713,7 +6719,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6997,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7125,7 +7131,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7331,7 +7337,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7743,7 +7749,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7949,7 +7955,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8155,7 +8161,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8361,7 +8367,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8567,7 +8573,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8979,7 +8985,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9185,7 +9191,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9469,10 +9475,10 @@
         <v>0.33</v>
       </c>
       <c r="AP41">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ41">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR41">
         <v>1.58</v>
@@ -9597,7 +9603,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9803,7 +9809,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10009,7 +10015,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10421,7 +10427,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10627,7 +10633,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11039,7 +11045,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11117,7 +11123,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ49">
         <v>0.83</v>
@@ -11326,7 +11332,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ50">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR50">
         <v>1.24</v>
@@ -11451,7 +11457,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11657,7 +11663,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11863,7 +11869,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12069,7 +12075,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12275,7 +12281,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12687,7 +12693,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12765,7 +12771,7 @@
         <v>0.83</v>
       </c>
       <c r="AP57">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ57">
         <v>1.25</v>
@@ -13099,7 +13105,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13386,7 +13392,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ60">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR60">
         <v>1.75</v>
@@ -13511,7 +13517,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13717,7 +13723,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -14129,7 +14135,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14210,7 +14216,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ64">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR64">
         <v>1.41</v>
@@ -14413,7 +14419,7 @@
         <v>2.2</v>
       </c>
       <c r="AP65">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ65">
         <v>2.25</v>
@@ -14541,7 +14547,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14747,7 +14753,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14953,7 +14959,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15159,7 +15165,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15365,7 +15371,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15571,7 +15577,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15777,7 +15783,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15855,7 +15861,7 @@
         <v>1.14</v>
       </c>
       <c r="AP72">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ72">
         <v>1.08</v>
@@ -15983,7 +15989,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16189,7 +16195,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16395,7 +16401,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16601,7 +16607,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16807,7 +16813,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17013,7 +17019,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17219,7 +17225,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17506,7 +17512,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ80">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR80">
         <v>1.62</v>
@@ -17837,7 +17843,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18121,7 +18127,7 @@
         <v>1.38</v>
       </c>
       <c r="AP83">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ83">
         <v>1.17</v>
@@ -18455,7 +18461,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18536,7 +18542,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ85">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18867,7 +18873,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19073,7 +19079,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19279,7 +19285,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19485,7 +19491,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19691,7 +19697,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19897,7 +19903,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20103,7 +20109,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20181,7 +20187,7 @@
         <v>1.22</v>
       </c>
       <c r="AP93">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -20309,7 +20315,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20390,7 +20396,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR94">
         <v>1.69</v>
@@ -20721,7 +20727,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21545,7 +21551,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21957,7 +21963,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22163,7 +22169,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22241,7 +22247,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ103">
         <v>1.25</v>
@@ -22369,7 +22375,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -23068,7 +23074,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ107">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR107">
         <v>1.57</v>
@@ -23605,7 +23611,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23811,7 +23817,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -24223,7 +24229,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24841,7 +24847,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -25047,7 +25053,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q117">
         <v>2.42</v>
@@ -25253,7 +25259,7 @@
         <v>165</v>
       </c>
       <c r="P118" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q118">
         <v>1.82</v>
@@ -25665,7 +25671,7 @@
         <v>167</v>
       </c>
       <c r="P120" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q120">
         <v>2.9</v>
@@ -25822,6 +25828,212 @@
       </c>
       <c r="BP120">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7776434</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45718.52083333334</v>
+      </c>
+      <c r="F121">
+        <v>24</v>
+      </c>
+      <c r="G121" t="s">
+        <v>77</v>
+      </c>
+      <c r="H121" t="s">
+        <v>74</v>
+      </c>
+      <c r="I121">
+        <v>2</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>2</v>
+      </c>
+      <c r="L121">
+        <v>3</v>
+      </c>
+      <c r="M121">
+        <v>2</v>
+      </c>
+      <c r="N121">
+        <v>5</v>
+      </c>
+      <c r="O121" t="s">
+        <v>168</v>
+      </c>
+      <c r="P121" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q121">
+        <v>2.6</v>
+      </c>
+      <c r="R121">
+        <v>2.25</v>
+      </c>
+      <c r="S121">
+        <v>3.7</v>
+      </c>
+      <c r="T121">
+        <v>1.32</v>
+      </c>
+      <c r="U121">
+        <v>3.14</v>
+      </c>
+      <c r="V121">
+        <v>2.45</v>
+      </c>
+      <c r="W121">
+        <v>1.49</v>
+      </c>
+      <c r="X121">
+        <v>5.65</v>
+      </c>
+      <c r="Y121">
+        <v>1.08</v>
+      </c>
+      <c r="Z121">
+        <v>2.1</v>
+      </c>
+      <c r="AA121">
+        <v>3.81</v>
+      </c>
+      <c r="AB121">
+        <v>3.01</v>
+      </c>
+      <c r="AC121">
+        <v>1.01</v>
+      </c>
+      <c r="AD121">
+        <v>11</v>
+      </c>
+      <c r="AE121">
+        <v>1.22</v>
+      </c>
+      <c r="AF121">
+        <v>3.95</v>
+      </c>
+      <c r="AG121">
+        <v>1.67</v>
+      </c>
+      <c r="AH121">
+        <v>2</v>
+      </c>
+      <c r="AI121">
+        <v>1.6</v>
+      </c>
+      <c r="AJ121">
+        <v>2.2</v>
+      </c>
+      <c r="AK121">
+        <v>1.32</v>
+      </c>
+      <c r="AL121">
+        <v>1.26</v>
+      </c>
+      <c r="AM121">
+        <v>1.67</v>
+      </c>
+      <c r="AN121">
+        <v>2.18</v>
+      </c>
+      <c r="AO121">
+        <v>0.82</v>
+      </c>
+      <c r="AP121">
+        <v>2.25</v>
+      </c>
+      <c r="AQ121">
+        <v>0.75</v>
+      </c>
+      <c r="AR121">
+        <v>1.63</v>
+      </c>
+      <c r="AS121">
+        <v>1.22</v>
+      </c>
+      <c r="AT121">
+        <v>2.85</v>
+      </c>
+      <c r="AU121">
+        <v>6</v>
+      </c>
+      <c r="AV121">
+        <v>3</v>
+      </c>
+      <c r="AW121">
+        <v>7</v>
+      </c>
+      <c r="AX121">
+        <v>5</v>
+      </c>
+      <c r="AY121">
+        <v>13</v>
+      </c>
+      <c r="AZ121">
+        <v>8</v>
+      </c>
+      <c r="BA121">
+        <v>2</v>
+      </c>
+      <c r="BB121">
+        <v>4</v>
+      </c>
+      <c r="BC121">
+        <v>6</v>
+      </c>
+      <c r="BD121">
+        <v>1.47</v>
+      </c>
+      <c r="BE121">
+        <v>6.7</v>
+      </c>
+      <c r="BF121">
+        <v>3.46</v>
+      </c>
+      <c r="BG121">
+        <v>1.33</v>
+      </c>
+      <c r="BH121">
+        <v>2.83</v>
+      </c>
+      <c r="BI121">
+        <v>1.68</v>
+      </c>
+      <c r="BJ121">
+        <v>2.14</v>
+      </c>
+      <c r="BK121">
+        <v>2.11</v>
+      </c>
+      <c r="BL121">
+        <v>1.69</v>
+      </c>
+      <c r="BM121">
+        <v>2.74</v>
+      </c>
+      <c r="BN121">
+        <v>1.35</v>
+      </c>
+      <c r="BO121">
+        <v>3.82</v>
+      </c>
+      <c r="BP121">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="247">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -523,6 +523,9 @@
     <t>['14', '34', '87']</t>
   </si>
   <si>
+    <t>['22', '84']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -746,6 +749,12 @@
   </si>
   <si>
     <t>['70', '79']</t>
+  </si>
+  <si>
+    <t>['26', '40', '41']</t>
+  </si>
+  <si>
+    <t>['10', '31', '82']</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1363,7 +1372,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1569,7 +1578,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1647,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1775,7 +1784,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -1853,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ4">
         <v>1.83</v>
@@ -2059,10 +2068,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2599,7 +2608,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2677,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
         <v>1.08</v>
@@ -2886,7 +2895,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ9">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3011,7 +3020,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3298,7 +3307,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3423,7 +3432,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3501,7 +3510,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ12">
         <v>1.17</v>
@@ -3629,7 +3638,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3835,7 +3844,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3913,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ14">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR14">
         <v>1.19</v>
@@ -4041,7 +4050,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4119,10 +4128,10 @@
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR15">
         <v>1.72</v>
@@ -4247,7 +4256,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4328,7 +4337,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR16">
         <v>1.95</v>
@@ -4453,7 +4462,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4659,7 +4668,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4865,7 +4874,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5071,7 +5080,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5277,7 +5286,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5355,10 +5364,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ21">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR21">
         <v>1.63</v>
@@ -5564,7 +5573,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ22">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR22">
         <v>1.91</v>
@@ -5689,7 +5698,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5767,7 +5776,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ23">
         <v>1.17</v>
@@ -5973,10 +5982,10 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR24">
         <v>1.47</v>
@@ -6101,7 +6110,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6307,7 +6316,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6513,7 +6522,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6594,7 +6603,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ27">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR27">
         <v>1.47</v>
@@ -6719,7 +6728,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6797,7 +6806,7 @@
         <v>0.33</v>
       </c>
       <c r="AP28">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
         <v>1.25</v>
@@ -7006,7 +7015,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR29">
         <v>1.46</v>
@@ -7131,7 +7140,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7209,7 +7218,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ30">
         <v>1.83</v>
@@ -7337,7 +7346,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7415,7 +7424,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ31">
         <v>1.08</v>
@@ -7624,7 +7633,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -7749,7 +7758,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7827,10 +7836,10 @@
         <v>1.33</v>
       </c>
       <c r="AP33">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR33">
         <v>1.62</v>
@@ -7955,7 +7964,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8033,10 +8042,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ34">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR34">
         <v>1.52</v>
@@ -8161,7 +8170,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8367,7 +8376,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8573,7 +8582,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8985,7 +8994,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9063,7 +9072,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ39">
         <v>1.17</v>
@@ -9191,7 +9200,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9269,7 +9278,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ40">
         <v>1.25</v>
@@ -9478,7 +9487,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ41">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR41">
         <v>1.58</v>
@@ -9603,7 +9612,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9684,7 +9693,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR42">
         <v>1.36</v>
@@ -9809,7 +9818,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9887,10 +9896,10 @@
         <v>0.25</v>
       </c>
       <c r="AP43">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR43">
         <v>1.64</v>
@@ -10015,7 +10024,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10093,7 +10102,7 @@
         <v>1.67</v>
       </c>
       <c r="AP44">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
         <v>2.25</v>
@@ -10302,7 +10311,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR45">
         <v>1.73</v>
@@ -10427,7 +10436,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10633,7 +10642,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10917,7 +10926,7 @@
         <v>2</v>
       </c>
       <c r="AP48">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ48">
         <v>1.83</v>
@@ -11045,7 +11054,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11329,10 +11338,10 @@
         <v>0.25</v>
       </c>
       <c r="AP50">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ50">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR50">
         <v>1.24</v>
@@ -11457,7 +11466,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11663,7 +11672,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11744,7 +11753,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR52">
         <v>1.69</v>
@@ -11869,7 +11878,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11947,10 +11956,10 @@
         <v>0.8</v>
       </c>
       <c r="AP53">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR53">
         <v>1.54</v>
@@ -12075,7 +12084,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12153,7 +12162,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ54">
         <v>2.25</v>
@@ -12281,7 +12290,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12693,7 +12702,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12977,7 +12986,7 @@
         <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ58">
         <v>0.83</v>
@@ -13105,7 +13114,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13183,10 +13192,10 @@
         <v>1.2</v>
       </c>
       <c r="AP59">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ59">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR59">
         <v>1.44</v>
@@ -13392,7 +13401,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ60">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR60">
         <v>1.75</v>
@@ -13517,7 +13526,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13723,7 +13732,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13804,7 +13813,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR62">
         <v>1.61</v>
@@ -14007,7 +14016,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ63">
         <v>1.08</v>
@@ -14135,7 +14144,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14216,7 +14225,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ64">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR64">
         <v>1.41</v>
@@ -14547,7 +14556,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14625,7 +14634,7 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
         <v>1.83</v>
@@ -14753,7 +14762,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14959,7 +14968,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15040,7 +15049,7 @@
         <v>2</v>
       </c>
       <c r="AQ68">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15165,7 +15174,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15243,7 +15252,7 @@
         <v>1.83</v>
       </c>
       <c r="AP69">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ69">
         <v>2.25</v>
@@ -15371,7 +15380,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15452,7 +15461,7 @@
         <v>2</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR70">
         <v>1.92</v>
@@ -15577,7 +15586,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15783,7 +15792,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15989,7 +15998,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16195,7 +16204,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16273,10 +16282,10 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ74">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR74">
         <v>1.53</v>
@@ -16401,7 +16410,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16482,7 +16491,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ75">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR75">
         <v>1.68</v>
@@ -16607,7 +16616,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16813,7 +16822,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17019,7 +17028,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17097,7 +17106,7 @@
         <v>0.57</v>
       </c>
       <c r="AP78">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ78">
         <v>0.83</v>
@@ -17225,7 +17234,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17306,7 +17315,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR79">
         <v>1.71</v>
@@ -17509,10 +17518,10 @@
         <v>0.57</v>
       </c>
       <c r="AP80">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ80">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR80">
         <v>1.62</v>
@@ -17715,10 +17724,10 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ81">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR81">
         <v>1.63</v>
@@ -17843,7 +17852,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -17924,7 +17933,7 @@
         <v>2</v>
       </c>
       <c r="AQ82">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR82">
         <v>1.78</v>
@@ -18333,7 +18342,7 @@
         <v>0.86</v>
       </c>
       <c r="AP84">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ84">
         <v>1.25</v>
@@ -18461,7 +18470,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18539,10 +18548,10 @@
         <v>0.63</v>
       </c>
       <c r="AP85">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ85">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18745,7 +18754,7 @@
         <v>0.63</v>
       </c>
       <c r="AP86">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ86">
         <v>0.83</v>
@@ -18873,7 +18882,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19079,7 +19088,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19285,7 +19294,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19366,7 +19375,7 @@
         <v>2</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR89">
         <v>1.97</v>
@@ -19491,7 +19500,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19697,7 +19706,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19903,7 +19912,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -19981,7 +19990,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ92">
         <v>2.25</v>
@@ -20109,7 +20118,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20190,7 +20199,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR93">
         <v>1.57</v>
@@ -20315,7 +20324,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20396,7 +20405,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR94">
         <v>1.69</v>
@@ -20599,7 +20608,7 @@
         <v>1.22</v>
       </c>
       <c r="AP95">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ95">
         <v>1.17</v>
@@ -20727,7 +20736,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -20805,7 +20814,7 @@
         <v>1.78</v>
       </c>
       <c r="AP96">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ96">
         <v>1.83</v>
@@ -21014,7 +21023,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR97">
         <v>1.69</v>
@@ -21220,7 +21229,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ98">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR98">
         <v>1.61</v>
@@ -21551,7 +21560,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21629,7 +21638,7 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ100">
         <v>1.08</v>
@@ -21835,7 +21844,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ101">
         <v>1.25</v>
@@ -21963,7 +21972,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22041,7 +22050,7 @@
         <v>1.1</v>
       </c>
       <c r="AP102">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ102">
         <v>1.17</v>
@@ -22169,7 +22178,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22250,7 +22259,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ103">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR103">
         <v>1.61</v>
@@ -22375,7 +22384,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22662,7 +22671,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR105">
         <v>1.9</v>
@@ -23074,7 +23083,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ107">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR107">
         <v>1.57</v>
@@ -23277,10 +23286,10 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR108">
         <v>1.58</v>
@@ -23483,7 +23492,7 @@
         <v>1.9</v>
       </c>
       <c r="AP109">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ109">
         <v>1.83</v>
@@ -23611,7 +23620,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23689,7 +23698,7 @@
         <v>1.2</v>
       </c>
       <c r="AP110">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ110">
         <v>1.25</v>
@@ -23817,7 +23826,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -24101,7 +24110,7 @@
         <v>1.36</v>
       </c>
       <c r="AP112">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ112">
         <v>1.25</v>
@@ -24229,7 +24238,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24307,10 +24316,10 @@
         <v>1.09</v>
       </c>
       <c r="AP113">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ113">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24513,10 +24522,10 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ114">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR114">
         <v>1.42</v>
@@ -24847,7 +24856,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -25053,7 +25062,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q117">
         <v>2.42</v>
@@ -25134,7 +25143,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ117">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR117">
         <v>1.73</v>
@@ -25259,7 +25268,7 @@
         <v>165</v>
       </c>
       <c r="P118" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q118">
         <v>1.82</v>
@@ -25543,7 +25552,7 @@
         <v>1.27</v>
       </c>
       <c r="AP119">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ119">
         <v>1.17</v>
@@ -25671,7 +25680,7 @@
         <v>167</v>
       </c>
       <c r="P120" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q120">
         <v>2.9</v>
@@ -25877,7 +25886,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -25958,7 +25967,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ121">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR121">
         <v>1.63</v>
@@ -26034,6 +26043,830 @@
       </c>
       <c r="BP121">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7776437</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45723.64583333334</v>
+      </c>
+      <c r="F122">
+        <v>25</v>
+      </c>
+      <c r="G122" t="s">
+        <v>76</v>
+      </c>
+      <c r="H122" t="s">
+        <v>77</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>3</v>
+      </c>
+      <c r="K122">
+        <v>3</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>3</v>
+      </c>
+      <c r="N122">
+        <v>3</v>
+      </c>
+      <c r="O122" t="s">
+        <v>84</v>
+      </c>
+      <c r="P122" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q122">
+        <v>4.14</v>
+      </c>
+      <c r="R122">
+        <v>2.35</v>
+      </c>
+      <c r="S122">
+        <v>2.4</v>
+      </c>
+      <c r="T122">
+        <v>1.32</v>
+      </c>
+      <c r="U122">
+        <v>3.1</v>
+      </c>
+      <c r="V122">
+        <v>2.4</v>
+      </c>
+      <c r="W122">
+        <v>1.5</v>
+      </c>
+      <c r="X122">
+        <v>5.3</v>
+      </c>
+      <c r="Y122">
+        <v>1.12</v>
+      </c>
+      <c r="Z122">
+        <v>3.57</v>
+      </c>
+      <c r="AA122">
+        <v>3.65</v>
+      </c>
+      <c r="AB122">
+        <v>1.94</v>
+      </c>
+      <c r="AC122">
+        <v>1.04</v>
+      </c>
+      <c r="AD122">
+        <v>8.5</v>
+      </c>
+      <c r="AE122">
+        <v>1.21</v>
+      </c>
+      <c r="AF122">
+        <v>3.78</v>
+      </c>
+      <c r="AG122">
+        <v>1.79</v>
+      </c>
+      <c r="AH122">
+        <v>1.95</v>
+      </c>
+      <c r="AI122">
+        <v>1.6</v>
+      </c>
+      <c r="AJ122">
+        <v>2.2</v>
+      </c>
+      <c r="AK122">
+        <v>1.27</v>
+      </c>
+      <c r="AL122">
+        <v>1.24</v>
+      </c>
+      <c r="AM122">
+        <v>1.27</v>
+      </c>
+      <c r="AN122">
+        <v>1.08</v>
+      </c>
+      <c r="AO122">
+        <v>1</v>
+      </c>
+      <c r="AP122">
+        <v>1</v>
+      </c>
+      <c r="AQ122">
+        <v>1.15</v>
+      </c>
+      <c r="AR122">
+        <v>1.65</v>
+      </c>
+      <c r="AS122">
+        <v>1.5</v>
+      </c>
+      <c r="AT122">
+        <v>3.15</v>
+      </c>
+      <c r="AU122">
+        <v>3</v>
+      </c>
+      <c r="AV122">
+        <v>9</v>
+      </c>
+      <c r="AW122">
+        <v>4</v>
+      </c>
+      <c r="AX122">
+        <v>3</v>
+      </c>
+      <c r="AY122">
+        <v>7</v>
+      </c>
+      <c r="AZ122">
+        <v>12</v>
+      </c>
+      <c r="BA122">
+        <v>2</v>
+      </c>
+      <c r="BB122">
+        <v>1</v>
+      </c>
+      <c r="BC122">
+        <v>3</v>
+      </c>
+      <c r="BD122">
+        <v>2.71</v>
+      </c>
+      <c r="BE122">
+        <v>6.2</v>
+      </c>
+      <c r="BF122">
+        <v>1.7</v>
+      </c>
+      <c r="BG122">
+        <v>1.35</v>
+      </c>
+      <c r="BH122">
+        <v>2.74</v>
+      </c>
+      <c r="BI122">
+        <v>1.67</v>
+      </c>
+      <c r="BJ122">
+        <v>2.03</v>
+      </c>
+      <c r="BK122">
+        <v>2.1</v>
+      </c>
+      <c r="BL122">
+        <v>1.59</v>
+      </c>
+      <c r="BM122">
+        <v>2.83</v>
+      </c>
+      <c r="BN122">
+        <v>1.33</v>
+      </c>
+      <c r="BO122">
+        <v>0</v>
+      </c>
+      <c r="BP122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7776435</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45723.64583333334</v>
+      </c>
+      <c r="F123">
+        <v>25</v>
+      </c>
+      <c r="G123" t="s">
+        <v>71</v>
+      </c>
+      <c r="H123" t="s">
+        <v>74</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
+        <v>2</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>1</v>
+      </c>
+      <c r="N123">
+        <v>2</v>
+      </c>
+      <c r="O123" t="s">
+        <v>146</v>
+      </c>
+      <c r="P123" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q123">
+        <v>3.5</v>
+      </c>
+      <c r="R123">
+        <v>2.25</v>
+      </c>
+      <c r="S123">
+        <v>2.85</v>
+      </c>
+      <c r="T123">
+        <v>1.34</v>
+      </c>
+      <c r="U123">
+        <v>3.2</v>
+      </c>
+      <c r="V123">
+        <v>2.62</v>
+      </c>
+      <c r="W123">
+        <v>1.43</v>
+      </c>
+      <c r="X123">
+        <v>6.4</v>
+      </c>
+      <c r="Y123">
+        <v>1.05</v>
+      </c>
+      <c r="Z123">
+        <v>3.09</v>
+      </c>
+      <c r="AA123">
+        <v>3.45</v>
+      </c>
+      <c r="AB123">
+        <v>2.19</v>
+      </c>
+      <c r="AC123">
+        <v>1.02</v>
+      </c>
+      <c r="AD123">
+        <v>8.5</v>
+      </c>
+      <c r="AE123">
+        <v>1.22</v>
+      </c>
+      <c r="AF123">
+        <v>3.74</v>
+      </c>
+      <c r="AG123">
+        <v>1.87</v>
+      </c>
+      <c r="AH123">
+        <v>1.87</v>
+      </c>
+      <c r="AI123">
+        <v>1.57</v>
+      </c>
+      <c r="AJ123">
+        <v>2.25</v>
+      </c>
+      <c r="AK123">
+        <v>1.3</v>
+      </c>
+      <c r="AL123">
+        <v>1.26</v>
+      </c>
+      <c r="AM123">
+        <v>1.33</v>
+      </c>
+      <c r="AN123">
+        <v>0.5</v>
+      </c>
+      <c r="AO123">
+        <v>0.75</v>
+      </c>
+      <c r="AP123">
+        <v>0.54</v>
+      </c>
+      <c r="AQ123">
+        <v>0.77</v>
+      </c>
+      <c r="AR123">
+        <v>1.49</v>
+      </c>
+      <c r="AS123">
+        <v>1.21</v>
+      </c>
+      <c r="AT123">
+        <v>2.7</v>
+      </c>
+      <c r="AU123">
+        <v>6</v>
+      </c>
+      <c r="AV123">
+        <v>6</v>
+      </c>
+      <c r="AW123">
+        <v>9</v>
+      </c>
+      <c r="AX123">
+        <v>12</v>
+      </c>
+      <c r="AY123">
+        <v>15</v>
+      </c>
+      <c r="AZ123">
+        <v>18</v>
+      </c>
+      <c r="BA123">
+        <v>4</v>
+      </c>
+      <c r="BB123">
+        <v>8</v>
+      </c>
+      <c r="BC123">
+        <v>12</v>
+      </c>
+      <c r="BD123">
+        <v>2.07</v>
+      </c>
+      <c r="BE123">
+        <v>6.2</v>
+      </c>
+      <c r="BF123">
+        <v>2.11</v>
+      </c>
+      <c r="BG123">
+        <v>1.22</v>
+      </c>
+      <c r="BH123">
+        <v>3.48</v>
+      </c>
+      <c r="BI123">
+        <v>1.44</v>
+      </c>
+      <c r="BJ123">
+        <v>2.43</v>
+      </c>
+      <c r="BK123">
+        <v>1.78</v>
+      </c>
+      <c r="BL123">
+        <v>1.88</v>
+      </c>
+      <c r="BM123">
+        <v>2.26</v>
+      </c>
+      <c r="BN123">
+        <v>1.51</v>
+      </c>
+      <c r="BO123">
+        <v>3.05</v>
+      </c>
+      <c r="BP123">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7776438</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45723.67708333334</v>
+      </c>
+      <c r="F124">
+        <v>25</v>
+      </c>
+      <c r="G124" t="s">
+        <v>72</v>
+      </c>
+      <c r="H124" t="s">
+        <v>70</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>2</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>2</v>
+      </c>
+      <c r="O124" t="s">
+        <v>169</v>
+      </c>
+      <c r="P124" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q124">
+        <v>2.1</v>
+      </c>
+      <c r="R124">
+        <v>2.45</v>
+      </c>
+      <c r="S124">
+        <v>4.1</v>
+      </c>
+      <c r="T124">
+        <v>1.29</v>
+      </c>
+      <c r="U124">
+        <v>3.4</v>
+      </c>
+      <c r="V124">
+        <v>2.25</v>
+      </c>
+      <c r="W124">
+        <v>1.55</v>
+      </c>
+      <c r="X124">
+        <v>5</v>
+      </c>
+      <c r="Y124">
+        <v>1.13</v>
+      </c>
+      <c r="Z124">
+        <v>1.79</v>
+      </c>
+      <c r="AA124">
+        <v>3.92</v>
+      </c>
+      <c r="AB124">
+        <v>3.91</v>
+      </c>
+      <c r="AC124">
+        <v>1.02</v>
+      </c>
+      <c r="AD124">
+        <v>10</v>
+      </c>
+      <c r="AE124">
+        <v>1.14</v>
+      </c>
+      <c r="AF124">
+        <v>4.7</v>
+      </c>
+      <c r="AG124">
+        <v>1.53</v>
+      </c>
+      <c r="AH124">
+        <v>2.25</v>
+      </c>
+      <c r="AI124">
+        <v>1.52</v>
+      </c>
+      <c r="AJ124">
+        <v>2.35</v>
+      </c>
+      <c r="AK124">
+        <v>1.22</v>
+      </c>
+      <c r="AL124">
+        <v>1.19</v>
+      </c>
+      <c r="AM124">
+        <v>2.15</v>
+      </c>
+      <c r="AN124">
+        <v>1.67</v>
+      </c>
+      <c r="AO124">
+        <v>1.25</v>
+      </c>
+      <c r="AP124">
+        <v>1.77</v>
+      </c>
+      <c r="AQ124">
+        <v>1.15</v>
+      </c>
+      <c r="AR124">
+        <v>1.52</v>
+      </c>
+      <c r="AS124">
+        <v>1.74</v>
+      </c>
+      <c r="AT124">
+        <v>3.26</v>
+      </c>
+      <c r="AU124">
+        <v>5</v>
+      </c>
+      <c r="AV124">
+        <v>0</v>
+      </c>
+      <c r="AW124">
+        <v>7</v>
+      </c>
+      <c r="AX124">
+        <v>5</v>
+      </c>
+      <c r="AY124">
+        <v>12</v>
+      </c>
+      <c r="AZ124">
+        <v>5</v>
+      </c>
+      <c r="BA124">
+        <v>3</v>
+      </c>
+      <c r="BB124">
+        <v>8</v>
+      </c>
+      <c r="BC124">
+        <v>11</v>
+      </c>
+      <c r="BD124">
+        <v>1.39</v>
+      </c>
+      <c r="BE124">
+        <v>7.3</v>
+      </c>
+      <c r="BF124">
+        <v>3.84</v>
+      </c>
+      <c r="BG124">
+        <v>1.2</v>
+      </c>
+      <c r="BH124">
+        <v>3.72</v>
+      </c>
+      <c r="BI124">
+        <v>1.39</v>
+      </c>
+      <c r="BJ124">
+        <v>2.59</v>
+      </c>
+      <c r="BK124">
+        <v>1.71</v>
+      </c>
+      <c r="BL124">
+        <v>1.97</v>
+      </c>
+      <c r="BM124">
+        <v>2.15</v>
+      </c>
+      <c r="BN124">
+        <v>1.56</v>
+      </c>
+      <c r="BO124">
+        <v>2.88</v>
+      </c>
+      <c r="BP124">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7776439</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45724.58333333334</v>
+      </c>
+      <c r="F125">
+        <v>25</v>
+      </c>
+      <c r="G125" t="s">
+        <v>73</v>
+      </c>
+      <c r="H125" t="s">
+        <v>78</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>2</v>
+      </c>
+      <c r="K125">
+        <v>2</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>3</v>
+      </c>
+      <c r="N125">
+        <v>3</v>
+      </c>
+      <c r="O125" t="s">
+        <v>84</v>
+      </c>
+      <c r="P125" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q125">
+        <v>2.88</v>
+      </c>
+      <c r="R125">
+        <v>2.05</v>
+      </c>
+      <c r="S125">
+        <v>3.56</v>
+      </c>
+      <c r="T125">
+        <v>1.37</v>
+      </c>
+      <c r="U125">
+        <v>2.84</v>
+      </c>
+      <c r="V125">
+        <v>2.89</v>
+      </c>
+      <c r="W125">
+        <v>1.36</v>
+      </c>
+      <c r="X125">
+        <v>7.9</v>
+      </c>
+      <c r="Y125">
+        <v>1.02</v>
+      </c>
+      <c r="Z125">
+        <v>2.35</v>
+      </c>
+      <c r="AA125">
+        <v>3.25</v>
+      </c>
+      <c r="AB125">
+        <v>2.97</v>
+      </c>
+      <c r="AC125">
+        <v>1.01</v>
+      </c>
+      <c r="AD125">
+        <v>8.6</v>
+      </c>
+      <c r="AE125">
+        <v>1.25</v>
+      </c>
+      <c r="AF125">
+        <v>3.28</v>
+      </c>
+      <c r="AG125">
+        <v>1.92</v>
+      </c>
+      <c r="AH125">
+        <v>1.82</v>
+      </c>
+      <c r="AI125">
+        <v>1.72</v>
+      </c>
+      <c r="AJ125">
+        <v>1.95</v>
+      </c>
+      <c r="AK125">
+        <v>1.34</v>
+      </c>
+      <c r="AL125">
+        <v>1.27</v>
+      </c>
+      <c r="AM125">
+        <v>1.56</v>
+      </c>
+      <c r="AN125">
+        <v>1.33</v>
+      </c>
+      <c r="AO125">
+        <v>1</v>
+      </c>
+      <c r="AP125">
+        <v>1.23</v>
+      </c>
+      <c r="AQ125">
+        <v>1.15</v>
+      </c>
+      <c r="AR125">
+        <v>1.44</v>
+      </c>
+      <c r="AS125">
+        <v>1.42</v>
+      </c>
+      <c r="AT125">
+        <v>2.86</v>
+      </c>
+      <c r="AU125">
+        <v>6</v>
+      </c>
+      <c r="AV125">
+        <v>5</v>
+      </c>
+      <c r="AW125">
+        <v>9</v>
+      </c>
+      <c r="AX125">
+        <v>4</v>
+      </c>
+      <c r="AY125">
+        <v>15</v>
+      </c>
+      <c r="AZ125">
+        <v>9</v>
+      </c>
+      <c r="BA125">
+        <v>3</v>
+      </c>
+      <c r="BB125">
+        <v>1</v>
+      </c>
+      <c r="BC125">
+        <v>4</v>
+      </c>
+      <c r="BD125">
+        <v>1.57</v>
+      </c>
+      <c r="BE125">
+        <v>7.9</v>
+      </c>
+      <c r="BF125">
+        <v>2.82</v>
+      </c>
+      <c r="BG125">
+        <v>1.42</v>
+      </c>
+      <c r="BH125">
+        <v>2.49</v>
+      </c>
+      <c r="BI125">
+        <v>1.79</v>
+      </c>
+      <c r="BJ125">
+        <v>1.87</v>
+      </c>
+      <c r="BK125">
+        <v>2.3</v>
+      </c>
+      <c r="BL125">
+        <v>1.49</v>
+      </c>
+      <c r="BM125">
+        <v>3.14</v>
+      </c>
+      <c r="BN125">
+        <v>1.27</v>
+      </c>
+      <c r="BO125">
+        <v>0</v>
+      </c>
+      <c r="BP125">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="248">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -524,6 +524,9 @@
   </si>
   <si>
     <t>['22', '84']</t>
+  </si>
+  <si>
+    <t>['52', '61']</t>
   </si>
   <si>
     <t>['25', '90+2']</t>
@@ -1116,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP125"/>
+  <dimension ref="A1:BP126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1372,7 +1375,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1453,7 +1456,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ2">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1578,7 +1581,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1784,7 +1787,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2608,7 +2611,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -3020,7 +3023,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3304,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ11">
         <v>0.77</v>
@@ -3432,7 +3435,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3638,7 +3641,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3716,10 +3719,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ13">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR13">
         <v>1.92</v>
@@ -3844,7 +3847,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4050,7 +4053,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4256,7 +4259,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4462,7 +4465,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4668,7 +4671,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4874,7 +4877,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5080,7 +5083,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5286,7 +5289,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5698,7 +5701,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6110,7 +6113,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6191,7 +6194,7 @@
         <v>2</v>
       </c>
       <c r="AQ25">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR25">
         <v>1.92</v>
@@ -6316,7 +6319,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6394,7 +6397,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ26">
         <v>0.83</v>
@@ -6522,7 +6525,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6728,7 +6731,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6809,7 +6812,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR28">
         <v>1.43</v>
@@ -7140,7 +7143,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7346,7 +7349,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7758,7 +7761,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7964,7 +7967,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8170,7 +8173,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8248,7 +8251,7 @@
         <v>1.33</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ35">
         <v>1.08</v>
@@ -8376,7 +8379,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8582,7 +8585,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8994,7 +8997,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9200,7 +9203,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9281,7 +9284,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ40">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR40">
         <v>1.35</v>
@@ -9612,7 +9615,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9818,7 +9821,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10024,7 +10027,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10308,7 +10311,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ45">
         <v>1.15</v>
@@ -10436,7 +10439,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10642,7 +10645,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11054,7 +11057,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11466,7 +11469,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11547,7 +11550,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ51">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR51">
         <v>1.86</v>
@@ -11672,7 +11675,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11878,7 +11881,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12084,7 +12087,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12290,7 +12293,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12702,7 +12705,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12783,7 +12786,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ57">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR57">
         <v>1.74</v>
@@ -13114,7 +13117,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13526,7 +13529,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13604,7 +13607,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ61">
         <v>1.17</v>
@@ -13732,7 +13735,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -14144,7 +14147,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14556,7 +14559,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14762,7 +14765,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14968,7 +14971,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15174,7 +15177,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15380,7 +15383,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15458,7 +15461,7 @@
         <v>1.67</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ70">
         <v>1.15</v>
@@ -15586,7 +15589,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15792,7 +15795,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15998,7 +16001,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16204,7 +16207,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16410,7 +16413,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16616,7 +16619,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16822,7 +16825,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16900,7 +16903,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ77">
         <v>2.25</v>
@@ -17028,7 +17031,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17234,7 +17237,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17852,7 +17855,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -17930,7 +17933,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ82">
         <v>1.15</v>
@@ -18345,7 +18348,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ84">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR84">
         <v>1.62</v>
@@ -18470,7 +18473,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18882,7 +18885,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19088,7 +19091,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19294,7 +19297,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19500,7 +19503,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19706,7 +19709,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19787,7 +19790,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ91">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR91">
         <v>1.62</v>
@@ -19912,7 +19915,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20118,7 +20121,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20324,7 +20327,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20402,7 +20405,7 @@
         <v>0.89</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ94">
         <v>0.77</v>
@@ -20736,7 +20739,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21560,7 +21563,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21847,7 +21850,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ101">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR101">
         <v>1.64</v>
@@ -21972,7 +21975,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22178,7 +22181,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22384,7 +22387,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22874,7 +22877,7 @@
         <v>1.2</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ106">
         <v>1.08</v>
@@ -23620,7 +23623,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23701,7 +23704,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ110">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -23826,7 +23829,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -24113,7 +24116,7 @@
         <v>1</v>
       </c>
       <c r="AQ112">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR112">
         <v>1.63</v>
@@ -24238,7 +24241,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24856,7 +24859,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -25062,7 +25065,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q117">
         <v>2.42</v>
@@ -25268,7 +25271,7 @@
         <v>165</v>
       </c>
       <c r="P118" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q118">
         <v>1.82</v>
@@ -25346,7 +25349,7 @@
         <v>0.82</v>
       </c>
       <c r="AP118">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ118">
         <v>0.83</v>
@@ -25680,7 +25683,7 @@
         <v>167</v>
       </c>
       <c r="P120" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q120">
         <v>2.9</v>
@@ -25886,7 +25889,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -26092,7 +26095,7 @@
         <v>84</v>
       </c>
       <c r="P122" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q122">
         <v>4.14</v>
@@ -26710,7 +26713,7 @@
         <v>84</v>
       </c>
       <c r="P125" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q125">
         <v>2.88</v>
@@ -26867,6 +26870,212 @@
       </c>
       <c r="BP125">
         <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7776440</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45725.52083333334</v>
+      </c>
+      <c r="F126">
+        <v>25</v>
+      </c>
+      <c r="G126" t="s">
+        <v>79</v>
+      </c>
+      <c r="H126" t="s">
+        <v>75</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>2</v>
+      </c>
+      <c r="M126">
+        <v>1</v>
+      </c>
+      <c r="N126">
+        <v>3</v>
+      </c>
+      <c r="O126" t="s">
+        <v>170</v>
+      </c>
+      <c r="P126" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q126">
+        <v>2.26</v>
+      </c>
+      <c r="R126">
+        <v>2.26</v>
+      </c>
+      <c r="S126">
+        <v>4.3</v>
+      </c>
+      <c r="T126">
+        <v>1.3</v>
+      </c>
+      <c r="U126">
+        <v>3.2</v>
+      </c>
+      <c r="V126">
+        <v>2.41</v>
+      </c>
+      <c r="W126">
+        <v>1.5</v>
+      </c>
+      <c r="X126">
+        <v>5.3</v>
+      </c>
+      <c r="Y126">
+        <v>1.09</v>
+      </c>
+      <c r="Z126">
+        <v>1.8</v>
+      </c>
+      <c r="AA126">
+        <v>3.79</v>
+      </c>
+      <c r="AB126">
+        <v>3.98</v>
+      </c>
+      <c r="AC126">
+        <v>1.01</v>
+      </c>
+      <c r="AD126">
+        <v>11</v>
+      </c>
+      <c r="AE126">
+        <v>1.17</v>
+      </c>
+      <c r="AF126">
+        <v>4.05</v>
+      </c>
+      <c r="AG126">
+        <v>1.61</v>
+      </c>
+      <c r="AH126">
+        <v>2.05</v>
+      </c>
+      <c r="AI126">
+        <v>1.59</v>
+      </c>
+      <c r="AJ126">
+        <v>2.15</v>
+      </c>
+      <c r="AK126">
+        <v>1.21</v>
+      </c>
+      <c r="AL126">
+        <v>1.22</v>
+      </c>
+      <c r="AM126">
+        <v>1.91</v>
+      </c>
+      <c r="AN126">
+        <v>2</v>
+      </c>
+      <c r="AO126">
+        <v>1.25</v>
+      </c>
+      <c r="AP126">
+        <v>2.08</v>
+      </c>
+      <c r="AQ126">
+        <v>1.15</v>
+      </c>
+      <c r="AR126">
+        <v>1.75</v>
+      </c>
+      <c r="AS126">
+        <v>1.68</v>
+      </c>
+      <c r="AT126">
+        <v>3.43</v>
+      </c>
+      <c r="AU126">
+        <v>5</v>
+      </c>
+      <c r="AV126">
+        <v>2</v>
+      </c>
+      <c r="AW126">
+        <v>6</v>
+      </c>
+      <c r="AX126">
+        <v>8</v>
+      </c>
+      <c r="AY126">
+        <v>11</v>
+      </c>
+      <c r="AZ126">
+        <v>10</v>
+      </c>
+      <c r="BA126">
+        <v>6</v>
+      </c>
+      <c r="BB126">
+        <v>4</v>
+      </c>
+      <c r="BC126">
+        <v>10</v>
+      </c>
+      <c r="BD126">
+        <v>1.54</v>
+      </c>
+      <c r="BE126">
+        <v>8.4</v>
+      </c>
+      <c r="BF126">
+        <v>2.86</v>
+      </c>
+      <c r="BG126">
+        <v>1.25</v>
+      </c>
+      <c r="BH126">
+        <v>3.28</v>
+      </c>
+      <c r="BI126">
+        <v>1.48</v>
+      </c>
+      <c r="BJ126">
+        <v>2.33</v>
+      </c>
+      <c r="BK126">
+        <v>1.85</v>
+      </c>
+      <c r="BL126">
+        <v>1.81</v>
+      </c>
+      <c r="BM126">
+        <v>2.38</v>
+      </c>
+      <c r="BN126">
+        <v>1.46</v>
+      </c>
+      <c r="BO126">
+        <v>3.2</v>
+      </c>
+      <c r="BP126">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="248">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1119,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1868,7 +1868,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ4">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ9">
         <v>1.15</v>
@@ -4749,10 +4749,10 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ18">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR18">
         <v>1.54</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ29">
         <v>1.15</v>
@@ -7224,7 +7224,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ30">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR30">
         <v>1.62</v>
@@ -8872,7 +8872,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ38">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR38">
         <v>2.02</v>
@@ -9487,7 +9487,7 @@
         <v>0.33</v>
       </c>
       <c r="AP41">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ41">
         <v>0.77</v>
@@ -10932,7 +10932,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ48">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR48">
         <v>1.41</v>
@@ -11135,7 +11135,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ49">
         <v>0.83</v>
@@ -12580,7 +12580,7 @@
         <v>2</v>
       </c>
       <c r="AQ56">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR56">
         <v>1.95</v>
@@ -12783,7 +12783,7 @@
         <v>0.83</v>
       </c>
       <c r="AP57">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ57">
         <v>1.15</v>
@@ -14431,7 +14431,7 @@
         <v>2.2</v>
       </c>
       <c r="AP65">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ65">
         <v>2.25</v>
@@ -14640,7 +14640,7 @@
         <v>1</v>
       </c>
       <c r="AQ66">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR66">
         <v>1.6</v>
@@ -15873,7 +15873,7 @@
         <v>1.14</v>
       </c>
       <c r="AP72">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ72">
         <v>1.08</v>
@@ -16082,7 +16082,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ73">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR73">
         <v>1.6</v>
@@ -18139,7 +18139,7 @@
         <v>1.38</v>
       </c>
       <c r="AP83">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ83">
         <v>1.17</v>
@@ -18966,7 +18966,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ87">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR87">
         <v>1.73</v>
@@ -20199,7 +20199,7 @@
         <v>1.22</v>
       </c>
       <c r="AP93">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ93">
         <v>1.15</v>
@@ -20820,7 +20820,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ96">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR96">
         <v>1.68</v>
@@ -22259,7 +22259,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ103">
         <v>1.15</v>
@@ -23498,7 +23498,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ109">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR109">
         <v>1.53</v>
@@ -24940,7 +24940,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ116">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR116">
         <v>1.59</v>
@@ -25967,7 +25967,7 @@
         <v>0.82</v>
       </c>
       <c r="AP121">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ121">
         <v>0.77</v>
@@ -27076,6 +27076,212 @@
       </c>
       <c r="BP126">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7776441</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45730.67708333334</v>
+      </c>
+      <c r="F127">
+        <v>26</v>
+      </c>
+      <c r="G127" t="s">
+        <v>77</v>
+      </c>
+      <c r="H127" t="s">
+        <v>79</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127" t="s">
+        <v>84</v>
+      </c>
+      <c r="P127" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q127">
+        <v>3.38</v>
+      </c>
+      <c r="R127">
+        <v>2.08</v>
+      </c>
+      <c r="S127">
+        <v>2.94</v>
+      </c>
+      <c r="T127">
+        <v>1.35</v>
+      </c>
+      <c r="U127">
+        <v>2.93</v>
+      </c>
+      <c r="V127">
+        <v>2.62</v>
+      </c>
+      <c r="W127">
+        <v>1.43</v>
+      </c>
+      <c r="X127">
+        <v>6.55</v>
+      </c>
+      <c r="Y127">
+        <v>1.05</v>
+      </c>
+      <c r="Z127">
+        <v>2.91</v>
+      </c>
+      <c r="AA127">
+        <v>3.36</v>
+      </c>
+      <c r="AB127">
+        <v>2.33</v>
+      </c>
+      <c r="AC127">
+        <v>1.02</v>
+      </c>
+      <c r="AD127">
+        <v>10</v>
+      </c>
+      <c r="AE127">
+        <v>1.2</v>
+      </c>
+      <c r="AF127">
+        <v>3.68</v>
+      </c>
+      <c r="AG127">
+        <v>1.77</v>
+      </c>
+      <c r="AH127">
+        <v>1.98</v>
+      </c>
+      <c r="AI127">
+        <v>1.6</v>
+      </c>
+      <c r="AJ127">
+        <v>2.14</v>
+      </c>
+      <c r="AK127">
+        <v>1.51</v>
+      </c>
+      <c r="AL127">
+        <v>1.28</v>
+      </c>
+      <c r="AM127">
+        <v>1.38</v>
+      </c>
+      <c r="AN127">
+        <v>2.25</v>
+      </c>
+      <c r="AO127">
+        <v>1.83</v>
+      </c>
+      <c r="AP127">
+        <v>2.15</v>
+      </c>
+      <c r="AQ127">
+        <v>1.77</v>
+      </c>
+      <c r="AR127">
+        <v>1.62</v>
+      </c>
+      <c r="AS127">
+        <v>1.78</v>
+      </c>
+      <c r="AT127">
+        <v>3.4</v>
+      </c>
+      <c r="AU127">
+        <v>4</v>
+      </c>
+      <c r="AV127">
+        <v>5</v>
+      </c>
+      <c r="AW127">
+        <v>3</v>
+      </c>
+      <c r="AX127">
+        <v>5</v>
+      </c>
+      <c r="AY127">
+        <v>7</v>
+      </c>
+      <c r="AZ127">
+        <v>10</v>
+      </c>
+      <c r="BA127">
+        <v>3</v>
+      </c>
+      <c r="BB127">
+        <v>3</v>
+      </c>
+      <c r="BC127">
+        <v>6</v>
+      </c>
+      <c r="BD127">
+        <v>2.35</v>
+      </c>
+      <c r="BE127">
+        <v>6.7</v>
+      </c>
+      <c r="BF127">
+        <v>1.84</v>
+      </c>
+      <c r="BG127">
+        <v>1.35</v>
+      </c>
+      <c r="BH127">
+        <v>2.74</v>
+      </c>
+      <c r="BI127">
+        <v>1.7</v>
+      </c>
+      <c r="BJ127">
+        <v>2.1</v>
+      </c>
+      <c r="BK127">
+        <v>2.13</v>
+      </c>
+      <c r="BL127">
+        <v>1.68</v>
+      </c>
+      <c r="BM127">
+        <v>2.83</v>
+      </c>
+      <c r="BN127">
+        <v>1.33</v>
+      </c>
+      <c r="BO127">
+        <v>3.75</v>
+      </c>
+      <c r="BP127">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="249">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -759,6 +759,9 @@
   <si>
     <t>['10', '31', '82']</t>
   </si>
+  <si>
+    <t>['77']</t>
+  </si>
 </sst>
 </file>
 
@@ -1119,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2483,10 +2486,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ7">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3516,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="AQ12">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR12">
         <v>1.34</v>
@@ -4543,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ17">
         <v>2.25</v>
@@ -5782,7 +5785,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ23">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR23">
         <v>1.3</v>
@@ -7633,7 +7636,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ32">
         <v>1.15</v>
@@ -9078,7 +9081,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ39">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR39">
         <v>1.16</v>
@@ -9693,7 +9696,7 @@
         <v>1.75</v>
       </c>
       <c r="AP42">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ42">
         <v>1.15</v>
@@ -10726,7 +10729,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ47">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR47">
         <v>1.79</v>
@@ -12371,7 +12374,7 @@
         <v>1.4</v>
       </c>
       <c r="AP55">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ55">
         <v>1.08</v>
@@ -13610,7 +13613,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ61">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -14225,7 +14228,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ64">
         <v>0.77</v>
@@ -14843,7 +14846,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ67">
         <v>0.83</v>
@@ -15670,7 +15673,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ71">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR71">
         <v>1.83</v>
@@ -16491,7 +16494,7 @@
         <v>1.29</v>
       </c>
       <c r="AP75">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ75">
         <v>1.15</v>
@@ -16700,7 +16703,7 @@
         <v>2</v>
       </c>
       <c r="AQ76">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR76">
         <v>1.84</v>
@@ -18142,7 +18145,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ83">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR83">
         <v>1.62</v>
@@ -18963,7 +18966,7 @@
         <v>1.88</v>
       </c>
       <c r="AP87">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ87">
         <v>1.77</v>
@@ -20614,7 +20617,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ95">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR95">
         <v>1.4</v>
@@ -21023,7 +21026,7 @@
         <v>1.11</v>
       </c>
       <c r="AP97">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ97">
         <v>1.15</v>
@@ -22056,7 +22059,7 @@
         <v>1</v>
       </c>
       <c r="AQ102">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR102">
         <v>1.56</v>
@@ -22465,7 +22468,7 @@
         <v>2.1</v>
       </c>
       <c r="AP104">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ104">
         <v>2.25</v>
@@ -25143,7 +25146,7 @@
         <v>1.09</v>
       </c>
       <c r="AP117">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ117">
         <v>1.15</v>
@@ -25558,7 +25561,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ119">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR119">
         <v>1.51</v>
@@ -27282,6 +27285,212 @@
       </c>
       <c r="BP127">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7776442</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45731.58333333334</v>
+      </c>
+      <c r="F128">
+        <v>26</v>
+      </c>
+      <c r="G128" t="s">
+        <v>75</v>
+      </c>
+      <c r="H128" t="s">
+        <v>71</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>1</v>
+      </c>
+      <c r="N128">
+        <v>1</v>
+      </c>
+      <c r="O128" t="s">
+        <v>84</v>
+      </c>
+      <c r="P128" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q128">
+        <v>2.05</v>
+      </c>
+      <c r="R128">
+        <v>2.3</v>
+      </c>
+      <c r="S128">
+        <v>5.5</v>
+      </c>
+      <c r="T128">
+        <v>1.33</v>
+      </c>
+      <c r="U128">
+        <v>3.25</v>
+      </c>
+      <c r="V128">
+        <v>2.63</v>
+      </c>
+      <c r="W128">
+        <v>1.44</v>
+      </c>
+      <c r="X128">
+        <v>6</v>
+      </c>
+      <c r="Y128">
+        <v>1.11</v>
+      </c>
+      <c r="Z128">
+        <v>1.61</v>
+      </c>
+      <c r="AA128">
+        <v>4</v>
+      </c>
+      <c r="AB128">
+        <v>5</v>
+      </c>
+      <c r="AC128">
+        <v>1.01</v>
+      </c>
+      <c r="AD128">
+        <v>11</v>
+      </c>
+      <c r="AE128">
+        <v>1.22</v>
+      </c>
+      <c r="AF128">
+        <v>4</v>
+      </c>
+      <c r="AG128">
+        <v>1.67</v>
+      </c>
+      <c r="AH128">
+        <v>2</v>
+      </c>
+      <c r="AI128">
+        <v>1.83</v>
+      </c>
+      <c r="AJ128">
+        <v>1.83</v>
+      </c>
+      <c r="AK128">
+        <v>1.13</v>
+      </c>
+      <c r="AL128">
+        <v>1.22</v>
+      </c>
+      <c r="AM128">
+        <v>2.45</v>
+      </c>
+      <c r="AN128">
+        <v>1.42</v>
+      </c>
+      <c r="AO128">
+        <v>1.17</v>
+      </c>
+      <c r="AP128">
+        <v>1.31</v>
+      </c>
+      <c r="AQ128">
+        <v>1.31</v>
+      </c>
+      <c r="AR128">
+        <v>1.73</v>
+      </c>
+      <c r="AS128">
+        <v>1.27</v>
+      </c>
+      <c r="AT128">
+        <v>3</v>
+      </c>
+      <c r="AU128">
+        <v>2</v>
+      </c>
+      <c r="AV128">
+        <v>3</v>
+      </c>
+      <c r="AW128">
+        <v>6</v>
+      </c>
+      <c r="AX128">
+        <v>7</v>
+      </c>
+      <c r="AY128">
+        <v>10</v>
+      </c>
+      <c r="AZ128">
+        <v>11</v>
+      </c>
+      <c r="BA128">
+        <v>4</v>
+      </c>
+      <c r="BB128">
+        <v>3</v>
+      </c>
+      <c r="BC128">
+        <v>7</v>
+      </c>
+      <c r="BD128">
+        <v>1.42</v>
+      </c>
+      <c r="BE128">
+        <v>8.9</v>
+      </c>
+      <c r="BF128">
+        <v>3.32</v>
+      </c>
+      <c r="BG128">
+        <v>1.21</v>
+      </c>
+      <c r="BH128">
+        <v>3.58</v>
+      </c>
+      <c r="BI128">
+        <v>1.41</v>
+      </c>
+      <c r="BJ128">
+        <v>2.52</v>
+      </c>
+      <c r="BK128">
+        <v>1.78</v>
+      </c>
+      <c r="BL128">
+        <v>2</v>
+      </c>
+      <c r="BM128">
+        <v>2.24</v>
+      </c>
+      <c r="BN128">
+        <v>1.61</v>
+      </c>
+      <c r="BO128">
+        <v>2.92</v>
+      </c>
+      <c r="BP128">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="253">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -529,6 +529,15 @@
     <t>['52', '61']</t>
   </si>
   <si>
+    <t>['11', '33', '53', '67']</t>
+  </si>
+  <si>
+    <t>['12', '17', '49']</t>
+  </si>
+  <si>
+    <t>['73', '90+6']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -761,6 +770,9 @@
   </si>
   <si>
     <t>['77']</t>
+  </si>
+  <si>
+    <t>['1', '41']</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP128"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1378,7 +1390,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1456,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ2">
         <v>1.15</v>
@@ -1584,7 +1596,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1790,7 +1802,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2280,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ6">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2614,7 +2626,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2695,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="AQ8">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3026,7 +3038,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3104,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ10">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3438,7 +3450,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3644,7 +3656,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3850,7 +3862,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4056,7 +4068,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4262,7 +4274,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4340,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ16">
         <v>1.15</v>
@@ -4468,7 +4480,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4549,7 +4561,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR17">
         <v>1.81</v>
@@ -4674,7 +4686,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4880,7 +4892,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -4958,10 +4970,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ19">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>1.52</v>
@@ -5086,7 +5098,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5164,10 +5176,10 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ20">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR20">
         <v>1.99</v>
@@ -5292,7 +5304,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5576,7 +5588,7 @@
         <v>1.5</v>
       </c>
       <c r="AP22">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ22">
         <v>1.15</v>
@@ -5704,7 +5716,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6116,7 +6128,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6194,7 +6206,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ25">
         <v>1.15</v>
@@ -6322,7 +6334,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6403,7 +6415,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ26">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR26">
         <v>1.45</v>
@@ -6528,7 +6540,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6606,7 +6618,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ27">
         <v>0.77</v>
@@ -6734,7 +6746,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7146,7 +7158,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7352,7 +7364,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7433,7 +7445,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ31">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR31">
         <v>1.17</v>
@@ -7764,7 +7776,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7970,7 +7982,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8176,7 +8188,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8257,7 +8269,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ35">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.63</v>
@@ -8382,7 +8394,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8460,10 +8472,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ36">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR36">
         <v>2.16</v>
@@ -8588,7 +8600,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8666,10 +8678,10 @@
         <v>1.33</v>
       </c>
       <c r="AP37">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ37">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -8872,7 +8884,7 @@
         <v>2.33</v>
       </c>
       <c r="AP38">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ38">
         <v>1.77</v>
@@ -9000,7 +9012,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9206,7 +9218,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9618,7 +9630,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9824,7 +9836,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10030,7 +10042,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10111,7 +10123,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -10442,7 +10454,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10520,10 +10532,10 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ46">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>2</v>
@@ -10648,7 +10660,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10726,7 +10738,7 @@
         <v>2.25</v>
       </c>
       <c r="AP47">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ47">
         <v>1.31</v>
@@ -11060,7 +11072,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11141,7 +11153,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ49">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR49">
         <v>1.57</v>
@@ -11472,7 +11484,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11550,7 +11562,7 @@
         <v>0.8</v>
       </c>
       <c r="AP51">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ51">
         <v>1.15</v>
@@ -11678,7 +11690,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11756,7 +11768,7 @@
         <v>1.4</v>
       </c>
       <c r="AP52">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ52">
         <v>1.15</v>
@@ -11884,7 +11896,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12090,7 +12102,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12171,7 +12183,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ54">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR54">
         <v>1.69</v>
@@ -12296,7 +12308,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12377,7 +12389,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ55">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>1.41</v>
@@ -12580,7 +12592,7 @@
         <v>1.8</v>
       </c>
       <c r="AP56">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ56">
         <v>1.77</v>
@@ -12708,7 +12720,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12995,7 +13007,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ58">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR58">
         <v>1.33</v>
@@ -13120,7 +13132,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13404,7 +13416,7 @@
         <v>0.4</v>
       </c>
       <c r="AP60">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ60">
         <v>0.77</v>
@@ -13532,7 +13544,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13738,7 +13750,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13816,7 +13828,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ62">
         <v>1.15</v>
@@ -14025,7 +14037,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ63">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR63">
         <v>1.59</v>
@@ -14150,7 +14162,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14437,7 +14449,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ65">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR65">
         <v>1.81</v>
@@ -14562,7 +14574,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14768,7 +14780,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14849,7 +14861,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ67">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR67">
         <v>1.46</v>
@@ -14974,7 +14986,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15052,7 +15064,7 @@
         <v>1.5</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ68">
         <v>1.15</v>
@@ -15180,7 +15192,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15261,7 +15273,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ69">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR69">
         <v>1.4</v>
@@ -15386,7 +15398,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15592,7 +15604,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15670,7 +15682,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ71">
         <v>1.31</v>
@@ -15798,7 +15810,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15879,7 +15891,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ72">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR72">
         <v>1.68</v>
@@ -16004,7 +16016,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16082,7 +16094,7 @@
         <v>1.71</v>
       </c>
       <c r="AP73">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ73">
         <v>1.77</v>
@@ -16210,7 +16222,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16416,7 +16428,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16622,7 +16634,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16700,7 +16712,7 @@
         <v>1.43</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ76">
         <v>1.31</v>
@@ -16828,7 +16840,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16909,7 +16921,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ77">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR77">
         <v>1.89</v>
@@ -17034,7 +17046,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17115,7 +17127,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ78">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR78">
         <v>1.35</v>
@@ -17240,7 +17252,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17318,7 +17330,7 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ79">
         <v>1.15</v>
@@ -17858,7 +17870,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18476,7 +18488,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18763,7 +18775,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ86">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR86">
         <v>1.62</v>
@@ -18888,7 +18900,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19094,7 +19106,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19172,10 +19184,10 @@
         <v>1.88</v>
       </c>
       <c r="AP88">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ88">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR88">
         <v>1.6</v>
@@ -19300,7 +19312,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19378,7 +19390,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ89">
         <v>1.15</v>
@@ -19506,7 +19518,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19584,10 +19596,10 @@
         <v>1.13</v>
       </c>
       <c r="AP90">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ90">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -19712,7 +19724,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19790,7 +19802,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ91">
         <v>1.15</v>
@@ -19918,7 +19930,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -19999,7 +20011,7 @@
         <v>1</v>
       </c>
       <c r="AQ92">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR92">
         <v>1.59</v>
@@ -20124,7 +20136,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20330,7 +20342,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20742,7 +20754,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21232,7 +21244,7 @@
         <v>1.33</v>
       </c>
       <c r="AP98">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ98">
         <v>1.15</v>
@@ -21438,10 +21450,10 @@
         <v>0.89</v>
       </c>
       <c r="AP99">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ99">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR99">
         <v>1.93</v>
@@ -21566,7 +21578,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21647,7 +21659,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ100">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR100">
         <v>1.58</v>
@@ -21978,7 +21990,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22184,7 +22196,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22390,7 +22402,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22471,7 +22483,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ104">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR104">
         <v>1.76</v>
@@ -22674,7 +22686,7 @@
         <v>1.2</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ105">
         <v>1.15</v>
@@ -22883,7 +22895,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ106">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR106">
         <v>1.72</v>
@@ -23086,7 +23098,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ107">
         <v>0.77</v>
@@ -23626,7 +23638,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23832,7 +23844,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -23910,10 +23922,10 @@
         <v>0.9</v>
       </c>
       <c r="AP111">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ111">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR111">
         <v>1.61</v>
@@ -24244,7 +24256,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24734,10 +24746,10 @@
         <v>2.18</v>
       </c>
       <c r="AP115">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ115">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR115">
         <v>1.93</v>
@@ -24862,7 +24874,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -24940,7 +24952,7 @@
         <v>1.73</v>
       </c>
       <c r="AP116">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ116">
         <v>1.77</v>
@@ -25068,7 +25080,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q117">
         <v>2.42</v>
@@ -25274,7 +25286,7 @@
         <v>165</v>
       </c>
       <c r="P118" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q118">
         <v>1.82</v>
@@ -25355,7 +25367,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ118">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR118">
         <v>1.72</v>
@@ -25686,7 +25698,7 @@
         <v>167</v>
       </c>
       <c r="P120" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q120">
         <v>2.9</v>
@@ -25764,10 +25776,10 @@
         <v>1.09</v>
       </c>
       <c r="AP120">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ120">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR120">
         <v>1.5</v>
@@ -25892,7 +25904,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -26098,7 +26110,7 @@
         <v>84</v>
       </c>
       <c r="P122" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q122">
         <v>4.14</v>
@@ -26716,7 +26728,7 @@
         <v>84</v>
       </c>
       <c r="P125" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q125">
         <v>2.88</v>
@@ -26922,7 +26934,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q126">
         <v>2.26</v>
@@ -27334,7 +27346,7 @@
         <v>84</v>
       </c>
       <c r="P128" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27491,6 +27503,624 @@
       </c>
       <c r="BP128">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7776443</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45732.42708333334</v>
+      </c>
+      <c r="F129">
+        <v>26</v>
+      </c>
+      <c r="G129" t="s">
+        <v>70</v>
+      </c>
+      <c r="H129" t="s">
+        <v>76</v>
+      </c>
+      <c r="I129">
+        <v>2</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>4</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>4</v>
+      </c>
+      <c r="O129" t="s">
+        <v>171</v>
+      </c>
+      <c r="P129" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q129">
+        <v>2.38</v>
+      </c>
+      <c r="R129">
+        <v>2.3</v>
+      </c>
+      <c r="S129">
+        <v>4</v>
+      </c>
+      <c r="T129">
+        <v>1.3</v>
+      </c>
+      <c r="U129">
+        <v>3.4</v>
+      </c>
+      <c r="V129">
+        <v>2.38</v>
+      </c>
+      <c r="W129">
+        <v>1.53</v>
+      </c>
+      <c r="X129">
+        <v>5.5</v>
+      </c>
+      <c r="Y129">
+        <v>1.13</v>
+      </c>
+      <c r="Z129">
+        <v>1.81</v>
+      </c>
+      <c r="AA129">
+        <v>3.85</v>
+      </c>
+      <c r="AB129">
+        <v>3.87</v>
+      </c>
+      <c r="AC129">
+        <v>1.01</v>
+      </c>
+      <c r="AD129">
+        <v>13</v>
+      </c>
+      <c r="AE129">
+        <v>1.13</v>
+      </c>
+      <c r="AF129">
+        <v>4.55</v>
+      </c>
+      <c r="AG129">
+        <v>1.57</v>
+      </c>
+      <c r="AH129">
+        <v>2.15</v>
+      </c>
+      <c r="AI129">
+        <v>1.57</v>
+      </c>
+      <c r="AJ129">
+        <v>2.25</v>
+      </c>
+      <c r="AK129">
+        <v>1.25</v>
+      </c>
+      <c r="AL129">
+        <v>1.25</v>
+      </c>
+      <c r="AM129">
+        <v>1.91</v>
+      </c>
+      <c r="AN129">
+        <v>1.25</v>
+      </c>
+      <c r="AO129">
+        <v>0.83</v>
+      </c>
+      <c r="AP129">
+        <v>1.38</v>
+      </c>
+      <c r="AQ129">
+        <v>0.77</v>
+      </c>
+      <c r="AR129">
+        <v>1.49</v>
+      </c>
+      <c r="AS129">
+        <v>1.34</v>
+      </c>
+      <c r="AT129">
+        <v>2.83</v>
+      </c>
+      <c r="AU129">
+        <v>7</v>
+      </c>
+      <c r="AV129">
+        <v>3</v>
+      </c>
+      <c r="AW129">
+        <v>5</v>
+      </c>
+      <c r="AX129">
+        <v>4</v>
+      </c>
+      <c r="AY129">
+        <v>12</v>
+      </c>
+      <c r="AZ129">
+        <v>7</v>
+      </c>
+      <c r="BA129">
+        <v>3</v>
+      </c>
+      <c r="BB129">
+        <v>5</v>
+      </c>
+      <c r="BC129">
+        <v>8</v>
+      </c>
+      <c r="BD129">
+        <v>1.49</v>
+      </c>
+      <c r="BE129">
+        <v>6.8</v>
+      </c>
+      <c r="BF129">
+        <v>3.34</v>
+      </c>
+      <c r="BG129">
+        <v>1.23</v>
+      </c>
+      <c r="BH129">
+        <v>3.42</v>
+      </c>
+      <c r="BI129">
+        <v>1.5</v>
+      </c>
+      <c r="BJ129">
+        <v>2.46</v>
+      </c>
+      <c r="BK129">
+        <v>1.87</v>
+      </c>
+      <c r="BL129">
+        <v>1.92</v>
+      </c>
+      <c r="BM129">
+        <v>2.34</v>
+      </c>
+      <c r="BN129">
+        <v>1.56</v>
+      </c>
+      <c r="BO129">
+        <v>3.08</v>
+      </c>
+      <c r="BP129">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7776444</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45732.42708333334</v>
+      </c>
+      <c r="F130">
+        <v>26</v>
+      </c>
+      <c r="G130" t="s">
+        <v>74</v>
+      </c>
+      <c r="H130" t="s">
+        <v>73</v>
+      </c>
+      <c r="I130">
+        <v>2</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>2</v>
+      </c>
+      <c r="L130">
+        <v>3</v>
+      </c>
+      <c r="M130">
+        <v>1</v>
+      </c>
+      <c r="N130">
+        <v>4</v>
+      </c>
+      <c r="O130" t="s">
+        <v>172</v>
+      </c>
+      <c r="P130" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q130">
+        <v>3</v>
+      </c>
+      <c r="R130">
+        <v>2.1</v>
+      </c>
+      <c r="S130">
+        <v>3.25</v>
+      </c>
+      <c r="T130">
+        <v>1.4</v>
+      </c>
+      <c r="U130">
+        <v>2.75</v>
+      </c>
+      <c r="V130">
+        <v>3</v>
+      </c>
+      <c r="W130">
+        <v>1.36</v>
+      </c>
+      <c r="X130">
+        <v>7</v>
+      </c>
+      <c r="Y130">
+        <v>1.08</v>
+      </c>
+      <c r="Z130">
+        <v>2.47</v>
+      </c>
+      <c r="AA130">
+        <v>3.36</v>
+      </c>
+      <c r="AB130">
+        <v>2.72</v>
+      </c>
+      <c r="AC130">
+        <v>1.03</v>
+      </c>
+      <c r="AD130">
+        <v>9</v>
+      </c>
+      <c r="AE130">
+        <v>1.24</v>
+      </c>
+      <c r="AF130">
+        <v>3.34</v>
+      </c>
+      <c r="AG130">
+        <v>1.91</v>
+      </c>
+      <c r="AH130">
+        <v>1.83</v>
+      </c>
+      <c r="AI130">
+        <v>1.73</v>
+      </c>
+      <c r="AJ130">
+        <v>2</v>
+      </c>
+      <c r="AK130">
+        <v>1.4</v>
+      </c>
+      <c r="AL130">
+        <v>1.35</v>
+      </c>
+      <c r="AM130">
+        <v>1.5</v>
+      </c>
+      <c r="AN130">
+        <v>2</v>
+      </c>
+      <c r="AO130">
+        <v>1.08</v>
+      </c>
+      <c r="AP130">
+        <v>2.08</v>
+      </c>
+      <c r="AQ130">
+        <v>1</v>
+      </c>
+      <c r="AR130">
+        <v>1.86</v>
+      </c>
+      <c r="AS130">
+        <v>1.55</v>
+      </c>
+      <c r="AT130">
+        <v>3.41</v>
+      </c>
+      <c r="AU130">
+        <v>7</v>
+      </c>
+      <c r="AV130">
+        <v>8</v>
+      </c>
+      <c r="AW130">
+        <v>6</v>
+      </c>
+      <c r="AX130">
+        <v>12</v>
+      </c>
+      <c r="AY130">
+        <v>13</v>
+      </c>
+      <c r="AZ130">
+        <v>20</v>
+      </c>
+      <c r="BA130">
+        <v>7</v>
+      </c>
+      <c r="BB130">
+        <v>6</v>
+      </c>
+      <c r="BC130">
+        <v>13</v>
+      </c>
+      <c r="BD130">
+        <v>2.24</v>
+      </c>
+      <c r="BE130">
+        <v>6.1</v>
+      </c>
+      <c r="BF130">
+        <v>1.97</v>
+      </c>
+      <c r="BG130">
+        <v>1.31</v>
+      </c>
+      <c r="BH130">
+        <v>2.92</v>
+      </c>
+      <c r="BI130">
+        <v>1.66</v>
+      </c>
+      <c r="BJ130">
+        <v>2.15</v>
+      </c>
+      <c r="BK130">
+        <v>2.08</v>
+      </c>
+      <c r="BL130">
+        <v>1.71</v>
+      </c>
+      <c r="BM130">
+        <v>2.66</v>
+      </c>
+      <c r="BN130">
+        <v>1.37</v>
+      </c>
+      <c r="BO130">
+        <v>3.7</v>
+      </c>
+      <c r="BP130">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7776445</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45732.42708333334</v>
+      </c>
+      <c r="F131">
+        <v>26</v>
+      </c>
+      <c r="G131" t="s">
+        <v>78</v>
+      </c>
+      <c r="H131" t="s">
+        <v>72</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>2</v>
+      </c>
+      <c r="K131">
+        <v>2</v>
+      </c>
+      <c r="L131">
+        <v>2</v>
+      </c>
+      <c r="M131">
+        <v>2</v>
+      </c>
+      <c r="N131">
+        <v>4</v>
+      </c>
+      <c r="O131" t="s">
+        <v>173</v>
+      </c>
+      <c r="P131" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q131">
+        <v>3.4</v>
+      </c>
+      <c r="R131">
+        <v>2.2</v>
+      </c>
+      <c r="S131">
+        <v>2.75</v>
+      </c>
+      <c r="T131">
+        <v>1.36</v>
+      </c>
+      <c r="U131">
+        <v>3</v>
+      </c>
+      <c r="V131">
+        <v>2.63</v>
+      </c>
+      <c r="W131">
+        <v>1.44</v>
+      </c>
+      <c r="X131">
+        <v>6.5</v>
+      </c>
+      <c r="Y131">
+        <v>1.1</v>
+      </c>
+      <c r="Z131">
+        <v>3.08</v>
+      </c>
+      <c r="AA131">
+        <v>3.41</v>
+      </c>
+      <c r="AB131">
+        <v>2.21</v>
+      </c>
+      <c r="AC131">
+        <v>1.01</v>
+      </c>
+      <c r="AD131">
+        <v>11</v>
+      </c>
+      <c r="AE131">
+        <v>1.18</v>
+      </c>
+      <c r="AF131">
+        <v>3.85</v>
+      </c>
+      <c r="AG131">
+        <v>1.7</v>
+      </c>
+      <c r="AH131">
+        <v>1.95</v>
+      </c>
+      <c r="AI131">
+        <v>1.62</v>
+      </c>
+      <c r="AJ131">
+        <v>2.2</v>
+      </c>
+      <c r="AK131">
+        <v>1.65</v>
+      </c>
+      <c r="AL131">
+        <v>1.3</v>
+      </c>
+      <c r="AM131">
+        <v>1.36</v>
+      </c>
+      <c r="AN131">
+        <v>1.42</v>
+      </c>
+      <c r="AO131">
+        <v>2.25</v>
+      </c>
+      <c r="AP131">
+        <v>1.38</v>
+      </c>
+      <c r="AQ131">
+        <v>2.15</v>
+      </c>
+      <c r="AR131">
+        <v>1.59</v>
+      </c>
+      <c r="AS131">
+        <v>1.86</v>
+      </c>
+      <c r="AT131">
+        <v>3.45</v>
+      </c>
+      <c r="AU131">
+        <v>5</v>
+      </c>
+      <c r="AV131">
+        <v>4</v>
+      </c>
+      <c r="AW131">
+        <v>2</v>
+      </c>
+      <c r="AX131">
+        <v>2</v>
+      </c>
+      <c r="AY131">
+        <v>7</v>
+      </c>
+      <c r="AZ131">
+        <v>6</v>
+      </c>
+      <c r="BA131">
+        <v>3</v>
+      </c>
+      <c r="BB131">
+        <v>2</v>
+      </c>
+      <c r="BC131">
+        <v>5</v>
+      </c>
+      <c r="BD131">
+        <v>2.39</v>
+      </c>
+      <c r="BE131">
+        <v>6.05</v>
+      </c>
+      <c r="BF131">
+        <v>1.87</v>
+      </c>
+      <c r="BG131">
+        <v>1.46</v>
+      </c>
+      <c r="BH131">
+        <v>2.6</v>
+      </c>
+      <c r="BI131">
+        <v>1.7</v>
+      </c>
+      <c r="BJ131">
+        <v>2.1</v>
+      </c>
+      <c r="BK131">
+        <v>2.11</v>
+      </c>
+      <c r="BL131">
+        <v>1.69</v>
+      </c>
+      <c r="BM131">
+        <v>2.83</v>
+      </c>
+      <c r="BN131">
+        <v>1.33</v>
+      </c>
+      <c r="BO131">
+        <v>5.15</v>
+      </c>
+      <c r="BP131">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="258">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -538,6 +538,15 @@
     <t>['73', '90+6']</t>
   </si>
   <si>
+    <t>['19', '38', '67']</t>
+  </si>
+  <si>
+    <t>['11', '63']</t>
+  </si>
+  <si>
+    <t>['41', '83']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -773,6 +782,12 @@
   </si>
   <si>
     <t>['1', '41']</t>
+  </si>
+  <si>
+    <t>['3', '77', '90+2']</t>
+  </si>
+  <si>
+    <t>['68', '78']</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1390,7 +1405,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1471,7 +1486,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ2">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1596,7 +1611,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1674,10 +1689,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1802,7 +1817,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -1880,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ4">
         <v>1.77</v>
@@ -2089,7 +2104,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ5">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2292,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ6">
         <v>0.77</v>
@@ -2626,7 +2641,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2704,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2913,7 +2928,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ9">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3038,7 +3053,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3322,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ11">
         <v>0.77</v>
@@ -3450,7 +3465,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3528,7 +3543,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ12">
         <v>1.31</v>
@@ -3656,7 +3671,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3734,10 +3749,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ13">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR13">
         <v>1.92</v>
@@ -3862,7 +3877,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3940,10 +3955,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ14">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR14">
         <v>1.19</v>
@@ -4068,7 +4083,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4149,7 +4164,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR15">
         <v>1.72</v>
@@ -4274,7 +4289,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4352,10 +4367,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ16">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR16">
         <v>1.95</v>
@@ -4480,7 +4495,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4686,7 +4701,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4892,7 +4907,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -4973,7 +4988,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR19">
         <v>1.52</v>
@@ -5098,7 +5113,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5304,7 +5319,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5382,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ21">
         <v>0.77</v>
@@ -5591,7 +5606,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ22">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR22">
         <v>1.91</v>
@@ -5716,7 +5731,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6000,10 +6015,10 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR24">
         <v>1.47</v>
@@ -6128,7 +6143,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6206,10 +6221,10 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ25">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR25">
         <v>1.92</v>
@@ -6334,7 +6349,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6412,7 +6427,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ26">
         <v>0.77</v>
@@ -6540,7 +6555,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6746,7 +6761,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6824,10 +6839,10 @@
         <v>0.33</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ28">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR28">
         <v>1.43</v>
@@ -7033,7 +7048,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ29">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR29">
         <v>1.46</v>
@@ -7158,7 +7173,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7236,7 +7251,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ30">
         <v>1.77</v>
@@ -7364,7 +7379,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7442,10 +7457,10 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR31">
         <v>1.17</v>
@@ -7651,7 +7666,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ32">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -7776,7 +7791,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7854,10 +7869,10 @@
         <v>1.33</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ33">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR33">
         <v>1.62</v>
@@ -7982,7 +7997,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8060,10 +8075,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ34">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR34">
         <v>1.52</v>
@@ -8188,7 +8203,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8266,10 +8281,10 @@
         <v>1.33</v>
       </c>
       <c r="AP35">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR35">
         <v>1.63</v>
@@ -8394,7 +8409,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8472,7 +8487,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ36">
         <v>2.15</v>
@@ -8600,7 +8615,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -9012,7 +9027,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9090,7 +9105,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ39">
         <v>1.31</v>
@@ -9218,7 +9233,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9299,7 +9314,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ40">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR40">
         <v>1.35</v>
@@ -9630,7 +9645,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9711,7 +9726,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ42">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR42">
         <v>1.36</v>
@@ -9836,7 +9851,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9914,10 +9929,10 @@
         <v>0.25</v>
       </c>
       <c r="AP43">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ43">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR43">
         <v>1.64</v>
@@ -10042,7 +10057,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10120,7 +10135,7 @@
         <v>1.67</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ44">
         <v>2.15</v>
@@ -10326,10 +10341,10 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ45">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR45">
         <v>1.73</v>
@@ -10454,7 +10469,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10532,10 +10547,10 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR46">
         <v>2</v>
@@ -10660,7 +10675,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11072,7 +11087,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11356,7 +11371,7 @@
         <v>0.25</v>
       </c>
       <c r="AP50">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ50">
         <v>0.77</v>
@@ -11484,7 +11499,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11565,7 +11580,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ51">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR51">
         <v>1.86</v>
@@ -11690,7 +11705,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11771,7 +11786,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ52">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR52">
         <v>1.69</v>
@@ -11896,7 +11911,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11974,10 +11989,10 @@
         <v>0.8</v>
       </c>
       <c r="AP53">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ53">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR53">
         <v>1.54</v>
@@ -12102,7 +12117,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12180,7 +12195,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ54">
         <v>2.15</v>
@@ -12308,7 +12323,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12389,7 +12404,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ55">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR55">
         <v>1.41</v>
@@ -12592,7 +12607,7 @@
         <v>1.8</v>
       </c>
       <c r="AP56">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ56">
         <v>1.77</v>
@@ -12720,7 +12735,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12801,7 +12816,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ57">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR57">
         <v>1.74</v>
@@ -13004,7 +13019,7 @@
         <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ58">
         <v>0.77</v>
@@ -13132,7 +13147,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13213,7 +13228,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ59">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR59">
         <v>1.44</v>
@@ -13544,7 +13559,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13622,7 +13637,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ61">
         <v>1.31</v>
@@ -13750,7 +13765,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13831,7 +13846,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ62">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR62">
         <v>1.61</v>
@@ -14034,10 +14049,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ63">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR63">
         <v>1.59</v>
@@ -14162,7 +14177,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14574,7 +14589,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14652,7 +14667,7 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ66">
         <v>1.77</v>
@@ -14780,7 +14795,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14986,7 +15001,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15064,10 +15079,10 @@
         <v>1.5</v>
       </c>
       <c r="AP68">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ68">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15192,7 +15207,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15398,7 +15413,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15476,10 +15491,10 @@
         <v>1.67</v>
       </c>
       <c r="AP70">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ70">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR70">
         <v>1.92</v>
@@ -15604,7 +15619,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15810,7 +15825,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15891,7 +15906,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ72">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR72">
         <v>1.68</v>
@@ -16016,7 +16031,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16222,7 +16237,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16300,10 +16315,10 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ74">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR74">
         <v>1.53</v>
@@ -16428,7 +16443,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16509,7 +16524,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ75">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR75">
         <v>1.68</v>
@@ -16634,7 +16649,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16712,7 +16727,7 @@
         <v>1.43</v>
       </c>
       <c r="AP76">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ76">
         <v>1.31</v>
@@ -16840,7 +16855,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16918,7 +16933,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ77">
         <v>2.15</v>
@@ -17046,7 +17061,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17252,7 +17267,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17333,7 +17348,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ79">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR79">
         <v>1.71</v>
@@ -17536,7 +17551,7 @@
         <v>0.57</v>
       </c>
       <c r="AP80">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ80">
         <v>0.77</v>
@@ -17742,10 +17757,10 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ81">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR81">
         <v>1.63</v>
@@ -17870,7 +17885,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -17948,10 +17963,10 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ82">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR82">
         <v>1.78</v>
@@ -18360,10 +18375,10 @@
         <v>0.86</v>
       </c>
       <c r="AP84">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ84">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR84">
         <v>1.62</v>
@@ -18488,7 +18503,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18772,7 +18787,7 @@
         <v>0.63</v>
       </c>
       <c r="AP86">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ86">
         <v>0.77</v>
@@ -18900,7 +18915,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19106,7 +19121,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19312,7 +19327,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19390,10 +19405,10 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ89">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR89">
         <v>1.97</v>
@@ -19518,7 +19533,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19599,7 +19614,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -19724,7 +19739,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19805,7 +19820,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ91">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR91">
         <v>1.62</v>
@@ -19930,7 +19945,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20008,7 +20023,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ92">
         <v>2.15</v>
@@ -20136,7 +20151,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20217,7 +20232,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ93">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR93">
         <v>1.57</v>
@@ -20342,7 +20357,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20420,7 +20435,7 @@
         <v>0.89</v>
       </c>
       <c r="AP94">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ94">
         <v>0.77</v>
@@ -20754,7 +20769,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -20832,7 +20847,7 @@
         <v>1.78</v>
       </c>
       <c r="AP96">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ96">
         <v>1.77</v>
@@ -21041,7 +21056,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ97">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR97">
         <v>1.69</v>
@@ -21247,7 +21262,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ98">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR98">
         <v>1.61</v>
@@ -21450,7 +21465,7 @@
         <v>0.89</v>
       </c>
       <c r="AP99">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ99">
         <v>0.77</v>
@@ -21578,7 +21593,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21656,10 +21671,10 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR100">
         <v>1.58</v>
@@ -21862,10 +21877,10 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ101">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR101">
         <v>1.64</v>
@@ -21990,7 +22005,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22068,7 +22083,7 @@
         <v>1.1</v>
       </c>
       <c r="AP102">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ102">
         <v>1.31</v>
@@ -22196,7 +22211,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22277,7 +22292,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ103">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR103">
         <v>1.61</v>
@@ -22402,7 +22417,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22686,10 +22701,10 @@
         <v>1.2</v>
       </c>
       <c r="AP105">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ105">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR105">
         <v>1.9</v>
@@ -22892,10 +22907,10 @@
         <v>1.2</v>
       </c>
       <c r="AP106">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR106">
         <v>1.72</v>
@@ -23304,10 +23319,10 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ108">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR108">
         <v>1.58</v>
@@ -23510,7 +23525,7 @@
         <v>1.9</v>
       </c>
       <c r="AP109">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ109">
         <v>1.77</v>
@@ -23638,7 +23653,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23719,7 +23734,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ110">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -23844,7 +23859,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -24128,10 +24143,10 @@
         <v>1.36</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ112">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR112">
         <v>1.63</v>
@@ -24256,7 +24271,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24334,10 +24349,10 @@
         <v>1.09</v>
       </c>
       <c r="AP113">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ113">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24543,7 +24558,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ114">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR114">
         <v>1.42</v>
@@ -24746,7 +24761,7 @@
         <v>2.18</v>
       </c>
       <c r="AP115">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ115">
         <v>2.15</v>
@@ -24874,7 +24889,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -25080,7 +25095,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q117">
         <v>2.42</v>
@@ -25161,7 +25176,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ117">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR117">
         <v>1.73</v>
@@ -25286,7 +25301,7 @@
         <v>165</v>
       </c>
       <c r="P118" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q118">
         <v>1.82</v>
@@ -25364,7 +25379,7 @@
         <v>0.82</v>
       </c>
       <c r="AP118">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ118">
         <v>0.77</v>
@@ -25570,7 +25585,7 @@
         <v>1.27</v>
       </c>
       <c r="AP119">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ119">
         <v>1.31</v>
@@ -25698,7 +25713,7 @@
         <v>167</v>
       </c>
       <c r="P120" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q120">
         <v>2.9</v>
@@ -25779,7 +25794,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR120">
         <v>1.5</v>
@@ -25904,7 +25919,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -26110,7 +26125,7 @@
         <v>84</v>
       </c>
       <c r="P122" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q122">
         <v>4.14</v>
@@ -26188,10 +26203,10 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ122">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR122">
         <v>1.65</v>
@@ -26394,7 +26409,7 @@
         <v>0.75</v>
       </c>
       <c r="AP123">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ123">
         <v>0.77</v>
@@ -26600,10 +26615,10 @@
         <v>1.25</v>
       </c>
       <c r="AP124">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ124">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR124">
         <v>1.52</v>
@@ -26728,7 +26743,7 @@
         <v>84</v>
       </c>
       <c r="P125" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q125">
         <v>2.88</v>
@@ -26809,7 +26824,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ125">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR125">
         <v>1.44</v>
@@ -26934,7 +26949,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q126">
         <v>2.26</v>
@@ -27012,10 +27027,10 @@
         <v>1.25</v>
       </c>
       <c r="AP126">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ126">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR126">
         <v>1.75</v>
@@ -27346,7 +27361,7 @@
         <v>84</v>
       </c>
       <c r="P128" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27758,7 +27773,7 @@
         <v>172</v>
       </c>
       <c r="P130" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -27836,10 +27851,10 @@
         <v>1.08</v>
       </c>
       <c r="AP130">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR130">
         <v>1.86</v>
@@ -27964,7 +27979,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q131">
         <v>3.4</v>
@@ -28121,6 +28136,1036 @@
       </c>
       <c r="BP131">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7776447</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45744.64583333334</v>
+      </c>
+      <c r="F132">
+        <v>27</v>
+      </c>
+      <c r="G132" t="s">
+        <v>76</v>
+      </c>
+      <c r="H132" t="s">
+        <v>73</v>
+      </c>
+      <c r="I132">
+        <v>2</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>2</v>
+      </c>
+      <c r="L132">
+        <v>3</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>3</v>
+      </c>
+      <c r="O132" t="s">
+        <v>174</v>
+      </c>
+      <c r="P132" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q132">
+        <v>3.75</v>
+      </c>
+      <c r="R132">
+        <v>2.1</v>
+      </c>
+      <c r="S132">
+        <v>2.75</v>
+      </c>
+      <c r="T132">
+        <v>1.4</v>
+      </c>
+      <c r="U132">
+        <v>2.75</v>
+      </c>
+      <c r="V132">
+        <v>2.75</v>
+      </c>
+      <c r="W132">
+        <v>1.4</v>
+      </c>
+      <c r="X132">
+        <v>7</v>
+      </c>
+      <c r="Y132">
+        <v>1.08</v>
+      </c>
+      <c r="Z132">
+        <v>3.39</v>
+      </c>
+      <c r="AA132">
+        <v>3.35</v>
+      </c>
+      <c r="AB132">
+        <v>2.1</v>
+      </c>
+      <c r="AC132">
+        <v>1.01</v>
+      </c>
+      <c r="AD132">
+        <v>8.4</v>
+      </c>
+      <c r="AE132">
+        <v>1.26</v>
+      </c>
+      <c r="AF132">
+        <v>3.22</v>
+      </c>
+      <c r="AG132">
+        <v>1.89</v>
+      </c>
+      <c r="AH132">
+        <v>1.85</v>
+      </c>
+      <c r="AI132">
+        <v>1.73</v>
+      </c>
+      <c r="AJ132">
+        <v>2</v>
+      </c>
+      <c r="AK132">
+        <v>1.7</v>
+      </c>
+      <c r="AL132">
+        <v>1.33</v>
+      </c>
+      <c r="AM132">
+        <v>1.3</v>
+      </c>
+      <c r="AN132">
+        <v>1</v>
+      </c>
+      <c r="AO132">
+        <v>1</v>
+      </c>
+      <c r="AP132">
+        <v>1.14</v>
+      </c>
+      <c r="AQ132">
+        <v>0.93</v>
+      </c>
+      <c r="AR132">
+        <v>1.6</v>
+      </c>
+      <c r="AS132">
+        <v>1.62</v>
+      </c>
+      <c r="AT132">
+        <v>3.22</v>
+      </c>
+      <c r="AU132">
+        <v>7</v>
+      </c>
+      <c r="AV132">
+        <v>3</v>
+      </c>
+      <c r="AW132">
+        <v>1</v>
+      </c>
+      <c r="AX132">
+        <v>4</v>
+      </c>
+      <c r="AY132">
+        <v>8</v>
+      </c>
+      <c r="AZ132">
+        <v>7</v>
+      </c>
+      <c r="BA132">
+        <v>3</v>
+      </c>
+      <c r="BB132">
+        <v>11</v>
+      </c>
+      <c r="BC132">
+        <v>14</v>
+      </c>
+      <c r="BD132">
+        <v>2.47</v>
+      </c>
+      <c r="BE132">
+        <v>8</v>
+      </c>
+      <c r="BF132">
+        <v>1.7</v>
+      </c>
+      <c r="BG132">
+        <v>1.31</v>
+      </c>
+      <c r="BH132">
+        <v>2.92</v>
+      </c>
+      <c r="BI132">
+        <v>1.58</v>
+      </c>
+      <c r="BJ132">
+        <v>2.12</v>
+      </c>
+      <c r="BK132">
+        <v>2.01</v>
+      </c>
+      <c r="BL132">
+        <v>1.68</v>
+      </c>
+      <c r="BM132">
+        <v>2.62</v>
+      </c>
+      <c r="BN132">
+        <v>1.38</v>
+      </c>
+      <c r="BO132">
+        <v>3.68</v>
+      </c>
+      <c r="BP132">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7776446</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45744.64583333334</v>
+      </c>
+      <c r="F133">
+        <v>27</v>
+      </c>
+      <c r="G133" t="s">
+        <v>71</v>
+      </c>
+      <c r="H133" t="s">
+        <v>78</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133">
+        <v>3</v>
+      </c>
+      <c r="N133">
+        <v>4</v>
+      </c>
+      <c r="O133" t="s">
+        <v>135</v>
+      </c>
+      <c r="P133" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q133">
+        <v>3.6</v>
+      </c>
+      <c r="R133">
+        <v>2.1</v>
+      </c>
+      <c r="S133">
+        <v>2.88</v>
+      </c>
+      <c r="T133">
+        <v>1.4</v>
+      </c>
+      <c r="U133">
+        <v>2.75</v>
+      </c>
+      <c r="V133">
+        <v>3</v>
+      </c>
+      <c r="W133">
+        <v>1.36</v>
+      </c>
+      <c r="X133">
+        <v>7</v>
+      </c>
+      <c r="Y133">
+        <v>1.08</v>
+      </c>
+      <c r="Z133">
+        <v>3.16</v>
+      </c>
+      <c r="AA133">
+        <v>3.27</v>
+      </c>
+      <c r="AB133">
+        <v>2.23</v>
+      </c>
+      <c r="AC133">
+        <v>1.01</v>
+      </c>
+      <c r="AD133">
+        <v>8.5</v>
+      </c>
+      <c r="AE133">
+        <v>1.25</v>
+      </c>
+      <c r="AF133">
+        <v>3.28</v>
+      </c>
+      <c r="AG133">
+        <v>1.94</v>
+      </c>
+      <c r="AH133">
+        <v>1.8</v>
+      </c>
+      <c r="AI133">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133">
+        <v>1.91</v>
+      </c>
+      <c r="AK133">
+        <v>1.6</v>
+      </c>
+      <c r="AL133">
+        <v>1.33</v>
+      </c>
+      <c r="AM133">
+        <v>1.36</v>
+      </c>
+      <c r="AN133">
+        <v>0.54</v>
+      </c>
+      <c r="AO133">
+        <v>1.15</v>
+      </c>
+      <c r="AP133">
+        <v>0.5</v>
+      </c>
+      <c r="AQ133">
+        <v>1.29</v>
+      </c>
+      <c r="AR133">
+        <v>1.51</v>
+      </c>
+      <c r="AS133">
+        <v>1.39</v>
+      </c>
+      <c r="AT133">
+        <v>2.9</v>
+      </c>
+      <c r="AU133">
+        <v>6</v>
+      </c>
+      <c r="AV133">
+        <v>7</v>
+      </c>
+      <c r="AW133">
+        <v>9</v>
+      </c>
+      <c r="AX133">
+        <v>6</v>
+      </c>
+      <c r="AY133">
+        <v>15</v>
+      </c>
+      <c r="AZ133">
+        <v>13</v>
+      </c>
+      <c r="BA133">
+        <v>4</v>
+      </c>
+      <c r="BB133">
+        <v>6</v>
+      </c>
+      <c r="BC133">
+        <v>10</v>
+      </c>
+      <c r="BD133">
+        <v>2.27</v>
+      </c>
+      <c r="BE133">
+        <v>6</v>
+      </c>
+      <c r="BF133">
+        <v>1.96</v>
+      </c>
+      <c r="BG133">
+        <v>1.43</v>
+      </c>
+      <c r="BH133">
+        <v>2.46</v>
+      </c>
+      <c r="BI133">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133">
+        <v>1.86</v>
+      </c>
+      <c r="BK133">
+        <v>2.33</v>
+      </c>
+      <c r="BL133">
+        <v>1.48</v>
+      </c>
+      <c r="BM133">
+        <v>3.2</v>
+      </c>
+      <c r="BN133">
+        <v>1.26</v>
+      </c>
+      <c r="BO133">
+        <v>0</v>
+      </c>
+      <c r="BP133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7776451</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45744.67708333334</v>
+      </c>
+      <c r="F134">
+        <v>27</v>
+      </c>
+      <c r="G134" t="s">
+        <v>74</v>
+      </c>
+      <c r="H134" t="s">
+        <v>75</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>1</v>
+      </c>
+      <c r="N134">
+        <v>1</v>
+      </c>
+      <c r="O134" t="s">
+        <v>84</v>
+      </c>
+      <c r="P134" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q134">
+        <v>3.1</v>
+      </c>
+      <c r="R134">
+        <v>2.2</v>
+      </c>
+      <c r="S134">
+        <v>3</v>
+      </c>
+      <c r="T134">
+        <v>1.33</v>
+      </c>
+      <c r="U134">
+        <v>3.25</v>
+      </c>
+      <c r="V134">
+        <v>2.63</v>
+      </c>
+      <c r="W134">
+        <v>1.44</v>
+      </c>
+      <c r="X134">
+        <v>6</v>
+      </c>
+      <c r="Y134">
+        <v>1.11</v>
+      </c>
+      <c r="Z134">
+        <v>2.66</v>
+      </c>
+      <c r="AA134">
+        <v>3.35</v>
+      </c>
+      <c r="AB134">
+        <v>2.52</v>
+      </c>
+      <c r="AC134">
+        <v>1.01</v>
+      </c>
+      <c r="AD134">
+        <v>11</v>
+      </c>
+      <c r="AE134">
+        <v>1.17</v>
+      </c>
+      <c r="AF134">
+        <v>3.95</v>
+      </c>
+      <c r="AG134">
+        <v>1.65</v>
+      </c>
+      <c r="AH134">
+        <v>2.05</v>
+      </c>
+      <c r="AI134">
+        <v>1.57</v>
+      </c>
+      <c r="AJ134">
+        <v>2.25</v>
+      </c>
+      <c r="AK134">
+        <v>1.5</v>
+      </c>
+      <c r="AL134">
+        <v>1.33</v>
+      </c>
+      <c r="AM134">
+        <v>1.44</v>
+      </c>
+      <c r="AN134">
+        <v>2.08</v>
+      </c>
+      <c r="AO134">
+        <v>1.15</v>
+      </c>
+      <c r="AP134">
+        <v>1.93</v>
+      </c>
+      <c r="AQ134">
+        <v>1.29</v>
+      </c>
+      <c r="AR134">
+        <v>1.85</v>
+      </c>
+      <c r="AS134">
+        <v>1.64</v>
+      </c>
+      <c r="AT134">
+        <v>3.49</v>
+      </c>
+      <c r="AU134">
+        <v>5</v>
+      </c>
+      <c r="AV134">
+        <v>6</v>
+      </c>
+      <c r="AW134">
+        <v>9</v>
+      </c>
+      <c r="AX134">
+        <v>9</v>
+      </c>
+      <c r="AY134">
+        <v>14</v>
+      </c>
+      <c r="AZ134">
+        <v>15</v>
+      </c>
+      <c r="BA134">
+        <v>8</v>
+      </c>
+      <c r="BB134">
+        <v>7</v>
+      </c>
+      <c r="BC134">
+        <v>15</v>
+      </c>
+      <c r="BD134">
+        <v>2.06</v>
+      </c>
+      <c r="BE134">
+        <v>6.15</v>
+      </c>
+      <c r="BF134">
+        <v>2.13</v>
+      </c>
+      <c r="BG134">
+        <v>1.3</v>
+      </c>
+      <c r="BH134">
+        <v>2.97</v>
+      </c>
+      <c r="BI134">
+        <v>1.56</v>
+      </c>
+      <c r="BJ134">
+        <v>2.16</v>
+      </c>
+      <c r="BK134">
+        <v>1.98</v>
+      </c>
+      <c r="BL134">
+        <v>1.7</v>
+      </c>
+      <c r="BM134">
+        <v>2.59</v>
+      </c>
+      <c r="BN134">
+        <v>1.39</v>
+      </c>
+      <c r="BO134">
+        <v>3.58</v>
+      </c>
+      <c r="BP134">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7776449</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45744.67708333334</v>
+      </c>
+      <c r="F135">
+        <v>27</v>
+      </c>
+      <c r="G135" t="s">
+        <v>72</v>
+      </c>
+      <c r="H135" t="s">
+        <v>77</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="L135">
+        <v>2</v>
+      </c>
+      <c r="M135">
+        <v>2</v>
+      </c>
+      <c r="N135">
+        <v>4</v>
+      </c>
+      <c r="O135" t="s">
+        <v>175</v>
+      </c>
+      <c r="P135" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q135">
+        <v>2.3</v>
+      </c>
+      <c r="R135">
+        <v>2.2</v>
+      </c>
+      <c r="S135">
+        <v>4.33</v>
+      </c>
+      <c r="T135">
+        <v>1.36</v>
+      </c>
+      <c r="U135">
+        <v>3</v>
+      </c>
+      <c r="V135">
+        <v>2.63</v>
+      </c>
+      <c r="W135">
+        <v>1.44</v>
+      </c>
+      <c r="X135">
+        <v>6.5</v>
+      </c>
+      <c r="Y135">
+        <v>1.1</v>
+      </c>
+      <c r="Z135">
+        <v>1.76</v>
+      </c>
+      <c r="AA135">
+        <v>3.73</v>
+      </c>
+      <c r="AB135">
+        <v>4.3</v>
+      </c>
+      <c r="AC135">
+        <v>1.01</v>
+      </c>
+      <c r="AD135">
+        <v>11</v>
+      </c>
+      <c r="AE135">
+        <v>1.21</v>
+      </c>
+      <c r="AF135">
+        <v>3.58</v>
+      </c>
+      <c r="AG135">
+        <v>1.77</v>
+      </c>
+      <c r="AH135">
+        <v>1.98</v>
+      </c>
+      <c r="AI135">
+        <v>1.73</v>
+      </c>
+      <c r="AJ135">
+        <v>2</v>
+      </c>
+      <c r="AK135">
+        <v>1.22</v>
+      </c>
+      <c r="AL135">
+        <v>1.29</v>
+      </c>
+      <c r="AM135">
+        <v>1.95</v>
+      </c>
+      <c r="AN135">
+        <v>1.77</v>
+      </c>
+      <c r="AO135">
+        <v>1.15</v>
+      </c>
+      <c r="AP135">
+        <v>1.71</v>
+      </c>
+      <c r="AQ135">
+        <v>1.14</v>
+      </c>
+      <c r="AR135">
+        <v>1.53</v>
+      </c>
+      <c r="AS135">
+        <v>1.53</v>
+      </c>
+      <c r="AT135">
+        <v>3.06</v>
+      </c>
+      <c r="AU135">
+        <v>6</v>
+      </c>
+      <c r="AV135">
+        <v>4</v>
+      </c>
+      <c r="AW135">
+        <v>5</v>
+      </c>
+      <c r="AX135">
+        <v>9</v>
+      </c>
+      <c r="AY135">
+        <v>11</v>
+      </c>
+      <c r="AZ135">
+        <v>13</v>
+      </c>
+      <c r="BA135">
+        <v>5</v>
+      </c>
+      <c r="BB135">
+        <v>3</v>
+      </c>
+      <c r="BC135">
+        <v>8</v>
+      </c>
+      <c r="BD135">
+        <v>1.59</v>
+      </c>
+      <c r="BE135">
+        <v>8</v>
+      </c>
+      <c r="BF135">
+        <v>2.75</v>
+      </c>
+      <c r="BG135">
+        <v>1.38</v>
+      </c>
+      <c r="BH135">
+        <v>2.62</v>
+      </c>
+      <c r="BI135">
+        <v>1.72</v>
+      </c>
+      <c r="BJ135">
+        <v>1.95</v>
+      </c>
+      <c r="BK135">
+        <v>2.19</v>
+      </c>
+      <c r="BL135">
+        <v>1.54</v>
+      </c>
+      <c r="BM135">
+        <v>2.97</v>
+      </c>
+      <c r="BN135">
+        <v>1.3</v>
+      </c>
+      <c r="BO135">
+        <v>0</v>
+      </c>
+      <c r="BP135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7776450</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45744.67708333334</v>
+      </c>
+      <c r="F136">
+        <v>27</v>
+      </c>
+      <c r="G136" t="s">
+        <v>79</v>
+      </c>
+      <c r="H136" t="s">
+        <v>70</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136">
+        <v>2</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>3</v>
+      </c>
+      <c r="O136" t="s">
+        <v>176</v>
+      </c>
+      <c r="P136" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q136">
+        <v>1.95</v>
+      </c>
+      <c r="R136">
+        <v>2.38</v>
+      </c>
+      <c r="S136">
+        <v>5.5</v>
+      </c>
+      <c r="T136">
+        <v>1.3</v>
+      </c>
+      <c r="U136">
+        <v>3.4</v>
+      </c>
+      <c r="V136">
+        <v>2.5</v>
+      </c>
+      <c r="W136">
+        <v>1.5</v>
+      </c>
+      <c r="X136">
+        <v>5.5</v>
+      </c>
+      <c r="Y136">
+        <v>1.13</v>
+      </c>
+      <c r="Z136">
+        <v>1.48</v>
+      </c>
+      <c r="AA136">
+        <v>4.4</v>
+      </c>
+      <c r="AB136">
+        <v>6</v>
+      </c>
+      <c r="AC136">
+        <v>1.01</v>
+      </c>
+      <c r="AD136">
+        <v>13</v>
+      </c>
+      <c r="AE136">
+        <v>1.15</v>
+      </c>
+      <c r="AF136">
+        <v>4.25</v>
+      </c>
+      <c r="AG136">
+        <v>1.6</v>
+      </c>
+      <c r="AH136">
+        <v>2.1</v>
+      </c>
+      <c r="AI136">
+        <v>1.8</v>
+      </c>
+      <c r="AJ136">
+        <v>1.91</v>
+      </c>
+      <c r="AK136">
+        <v>1.11</v>
+      </c>
+      <c r="AL136">
+        <v>1.22</v>
+      </c>
+      <c r="AM136">
+        <v>2.62</v>
+      </c>
+      <c r="AN136">
+        <v>2.08</v>
+      </c>
+      <c r="AO136">
+        <v>1.15</v>
+      </c>
+      <c r="AP136">
+        <v>2.14</v>
+      </c>
+      <c r="AQ136">
+        <v>1.07</v>
+      </c>
+      <c r="AR136">
+        <v>1.72</v>
+      </c>
+      <c r="AS136">
+        <v>1.66</v>
+      </c>
+      <c r="AT136">
+        <v>3.38</v>
+      </c>
+      <c r="AU136">
+        <v>6</v>
+      </c>
+      <c r="AV136">
+        <v>3</v>
+      </c>
+      <c r="AW136">
+        <v>8</v>
+      </c>
+      <c r="AX136">
+        <v>6</v>
+      </c>
+      <c r="AY136">
+        <v>14</v>
+      </c>
+      <c r="AZ136">
+        <v>9</v>
+      </c>
+      <c r="BA136">
+        <v>5</v>
+      </c>
+      <c r="BB136">
+        <v>2</v>
+      </c>
+      <c r="BC136">
+        <v>7</v>
+      </c>
+      <c r="BD136">
+        <v>1.3</v>
+      </c>
+      <c r="BE136">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF136">
+        <v>4.15</v>
+      </c>
+      <c r="BG136">
+        <v>1.3</v>
+      </c>
+      <c r="BH136">
+        <v>2.97</v>
+      </c>
+      <c r="BI136">
+        <v>1.56</v>
+      </c>
+      <c r="BJ136">
+        <v>2.16</v>
+      </c>
+      <c r="BK136">
+        <v>1.97</v>
+      </c>
+      <c r="BL136">
+        <v>1.71</v>
+      </c>
+      <c r="BM136">
+        <v>2.56</v>
+      </c>
+      <c r="BN136">
+        <v>1.4</v>
+      </c>
+      <c r="BO136">
+        <v>3.5</v>
+      </c>
+      <c r="BP136">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="264">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -547,6 +547,18 @@
     <t>['41', '83']</t>
   </si>
   <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['4', '24', '55', '68', '87', '90+4']</t>
+  </si>
+  <si>
+    <t>['32', '39']</t>
+  </si>
+  <si>
+    <t>['17', '56', '90+1']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -788,6 +800,12 @@
   </si>
   <si>
     <t>['68', '78']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['20', '49']</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP136"/>
+  <dimension ref="A1:BP140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1405,7 +1423,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1483,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
         <v>1.29</v>
@@ -1611,7 +1629,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1817,7 +1835,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -1898,7 +1916,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ4">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2101,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ5">
         <v>1.29</v>
@@ -2310,7 +2328,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ6">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2513,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ7">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2641,7 +2659,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2925,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ9">
         <v>1.07</v>
@@ -3053,7 +3071,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3134,7 +3152,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ10">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3465,7 +3483,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3546,7 +3564,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ12">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR12">
         <v>1.34</v>
@@ -3671,7 +3689,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3877,7 +3895,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4083,7 +4101,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4161,7 +4179,7 @@
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ15">
         <v>1.14</v>
@@ -4289,7 +4307,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4495,7 +4513,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4573,10 +4591,10 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ17">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR17">
         <v>1.81</v>
@@ -4701,7 +4719,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4779,10 +4797,10 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ18">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR18">
         <v>1.54</v>
@@ -4907,7 +4925,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -4985,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19">
         <v>0.93</v>
@@ -5113,7 +5131,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5194,7 +5212,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ20">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR20">
         <v>1.99</v>
@@ -5319,7 +5337,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5731,7 +5749,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5809,10 +5827,10 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ23">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR23">
         <v>1.3</v>
@@ -6143,7 +6161,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6349,7 +6367,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6430,7 +6448,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ26">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR26">
         <v>1.45</v>
@@ -6555,7 +6573,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6633,7 +6651,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27">
         <v>0.77</v>
@@ -6761,7 +6779,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7045,7 +7063,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ29">
         <v>1.29</v>
@@ -7173,7 +7191,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7254,7 +7272,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ30">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR30">
         <v>1.62</v>
@@ -7379,7 +7397,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7663,7 +7681,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ32">
         <v>1.29</v>
@@ -7791,7 +7809,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7997,7 +8015,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8203,7 +8221,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8409,7 +8427,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8490,7 +8508,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ36">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR36">
         <v>2.16</v>
@@ -8615,7 +8633,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8693,10 +8711,10 @@
         <v>1.33</v>
       </c>
       <c r="AP37">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -8902,7 +8920,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ38">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR38">
         <v>2.02</v>
@@ -9027,7 +9045,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9108,7 +9126,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ39">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR39">
         <v>1.16</v>
@@ -9233,7 +9251,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9311,7 +9329,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ40">
         <v>1.29</v>
@@ -9517,7 +9535,7 @@
         <v>0.33</v>
       </c>
       <c r="AP41">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ41">
         <v>0.77</v>
@@ -9645,7 +9663,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9723,7 +9741,7 @@
         <v>1.75</v>
       </c>
       <c r="AP42">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ42">
         <v>1.14</v>
@@ -9851,7 +9869,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10057,7 +10075,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10138,7 +10156,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ44">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -10469,7 +10487,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10675,7 +10693,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10753,10 +10771,10 @@
         <v>2.25</v>
       </c>
       <c r="AP47">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR47">
         <v>1.79</v>
@@ -10959,10 +10977,10 @@
         <v>2</v>
       </c>
       <c r="AP48">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ48">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR48">
         <v>1.41</v>
@@ -11087,7 +11105,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11165,10 +11183,10 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ49">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR49">
         <v>1.57</v>
@@ -11499,7 +11517,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11705,7 +11723,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11783,7 +11801,7 @@
         <v>1.4</v>
       </c>
       <c r="AP52">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ52">
         <v>1.14</v>
@@ -11911,7 +11929,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12117,7 +12135,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12198,7 +12216,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ54">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR54">
         <v>1.69</v>
@@ -12323,7 +12341,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12401,7 +12419,7 @@
         <v>1.4</v>
       </c>
       <c r="AP55">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ55">
         <v>0.93</v>
@@ -12610,7 +12628,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ56">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR56">
         <v>1.95</v>
@@ -12735,7 +12753,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12813,7 +12831,7 @@
         <v>0.83</v>
       </c>
       <c r="AP57">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ57">
         <v>1.29</v>
@@ -13022,7 +13040,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ58">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR58">
         <v>1.33</v>
@@ -13147,7 +13165,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13225,7 +13243,7 @@
         <v>1.2</v>
       </c>
       <c r="AP59">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ59">
         <v>1.07</v>
@@ -13559,7 +13577,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13640,7 +13658,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ61">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -13765,7 +13783,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13843,7 +13861,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62">
         <v>1.29</v>
@@ -14177,7 +14195,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14255,7 +14273,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ64">
         <v>0.77</v>
@@ -14461,10 +14479,10 @@
         <v>2.2</v>
       </c>
       <c r="AP65">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ65">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR65">
         <v>1.81</v>
@@ -14589,7 +14607,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14670,7 +14688,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ66">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR66">
         <v>1.6</v>
@@ -14795,7 +14813,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14873,10 +14891,10 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ67">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR67">
         <v>1.46</v>
@@ -15001,7 +15019,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15207,7 +15225,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15285,10 +15303,10 @@
         <v>1.83</v>
       </c>
       <c r="AP69">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ69">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR69">
         <v>1.4</v>
@@ -15413,7 +15431,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15619,7 +15637,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15700,7 +15718,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ71">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR71">
         <v>1.83</v>
@@ -15825,7 +15843,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15903,7 +15921,7 @@
         <v>1.14</v>
       </c>
       <c r="AP72">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ72">
         <v>0.93</v>
@@ -16031,7 +16049,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16109,10 +16127,10 @@
         <v>1.71</v>
       </c>
       <c r="AP73">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ73">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR73">
         <v>1.6</v>
@@ -16237,7 +16255,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16443,7 +16461,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16521,7 +16539,7 @@
         <v>1.29</v>
       </c>
       <c r="AP75">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ75">
         <v>1.07</v>
@@ -16649,7 +16667,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16730,7 +16748,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ76">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR76">
         <v>1.84</v>
@@ -16855,7 +16873,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16936,7 +16954,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ77">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR77">
         <v>1.89</v>
@@ -17061,7 +17079,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17139,10 +17157,10 @@
         <v>0.57</v>
       </c>
       <c r="AP78">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ78">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR78">
         <v>1.35</v>
@@ -17267,7 +17285,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17885,7 +17903,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18169,10 +18187,10 @@
         <v>1.38</v>
       </c>
       <c r="AP83">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ83">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR83">
         <v>1.62</v>
@@ -18503,7 +18521,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18581,7 +18599,7 @@
         <v>0.63</v>
       </c>
       <c r="AP85">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ85">
         <v>0.77</v>
@@ -18790,7 +18808,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ86">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR86">
         <v>1.62</v>
@@ -18915,7 +18933,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -18993,10 +19011,10 @@
         <v>1.88</v>
       </c>
       <c r="AP87">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ87">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR87">
         <v>1.73</v>
@@ -19121,7 +19139,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19199,10 +19217,10 @@
         <v>1.88</v>
       </c>
       <c r="AP88">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ88">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR88">
         <v>1.6</v>
@@ -19327,7 +19345,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19533,7 +19551,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19739,7 +19757,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19817,7 +19835,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91">
         <v>1.29</v>
@@ -19945,7 +19963,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20026,7 +20044,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ92">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR92">
         <v>1.59</v>
@@ -20151,7 +20169,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20229,7 +20247,7 @@
         <v>1.22</v>
       </c>
       <c r="AP93">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ93">
         <v>1.29</v>
@@ -20357,7 +20375,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20641,10 +20659,10 @@
         <v>1.22</v>
       </c>
       <c r="AP95">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ95">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR95">
         <v>1.4</v>
@@ -20769,7 +20787,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -20850,7 +20868,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ96">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR96">
         <v>1.68</v>
@@ -21053,7 +21071,7 @@
         <v>1.11</v>
       </c>
       <c r="AP97">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ97">
         <v>1.14</v>
@@ -21468,7 +21486,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ99">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR99">
         <v>1.93</v>
@@ -21593,7 +21611,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -22005,7 +22023,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22086,7 +22104,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ102">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR102">
         <v>1.56</v>
@@ -22211,7 +22229,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22289,7 +22307,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ103">
         <v>1.07</v>
@@ -22417,7 +22435,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22495,10 +22513,10 @@
         <v>2.1</v>
       </c>
       <c r="AP104">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ104">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR104">
         <v>1.76</v>
@@ -23113,7 +23131,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ107">
         <v>0.77</v>
@@ -23528,7 +23546,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ109">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR109">
         <v>1.53</v>
@@ -23653,7 +23671,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23731,7 +23749,7 @@
         <v>1.2</v>
       </c>
       <c r="AP110">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ110">
         <v>1.29</v>
@@ -23859,7 +23877,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -23940,7 +23958,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ111">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR111">
         <v>1.61</v>
@@ -24271,7 +24289,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24555,7 +24573,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ114">
         <v>1.14</v>
@@ -24764,7 +24782,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ115">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR115">
         <v>1.93</v>
@@ -24889,7 +24907,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -24970,7 +24988,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ116">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR116">
         <v>1.59</v>
@@ -25095,7 +25113,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q117">
         <v>2.42</v>
@@ -25173,7 +25191,7 @@
         <v>1.09</v>
       </c>
       <c r="AP117">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ117">
         <v>1.29</v>
@@ -25301,7 +25319,7 @@
         <v>165</v>
       </c>
       <c r="P118" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q118">
         <v>1.82</v>
@@ -25382,7 +25400,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ118">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR118">
         <v>1.72</v>
@@ -25588,7 +25606,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ119">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR119">
         <v>1.51</v>
@@ -25713,7 +25731,7 @@
         <v>167</v>
       </c>
       <c r="P120" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q120">
         <v>2.9</v>
@@ -25791,7 +25809,7 @@
         <v>1.09</v>
       </c>
       <c r="AP120">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ120">
         <v>0.93</v>
@@ -25919,7 +25937,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -25997,7 +26015,7 @@
         <v>0.82</v>
       </c>
       <c r="AP121">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ121">
         <v>0.77</v>
@@ -26125,7 +26143,7 @@
         <v>84</v>
       </c>
       <c r="P122" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q122">
         <v>4.14</v>
@@ -26743,7 +26761,7 @@
         <v>84</v>
       </c>
       <c r="P125" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q125">
         <v>2.88</v>
@@ -26821,7 +26839,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ125">
         <v>1.29</v>
@@ -26949,7 +26967,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q126">
         <v>2.26</v>
@@ -27233,10 +27251,10 @@
         <v>1.83</v>
       </c>
       <c r="AP127">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ127">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR127">
         <v>1.62</v>
@@ -27361,7 +27379,7 @@
         <v>84</v>
       </c>
       <c r="P128" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27439,10 +27457,10 @@
         <v>1.17</v>
       </c>
       <c r="AP128">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ128">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR128">
         <v>1.73</v>
@@ -27645,10 +27663,10 @@
         <v>0.83</v>
       </c>
       <c r="AP129">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ129">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR129">
         <v>1.49</v>
@@ -27773,7 +27791,7 @@
         <v>172</v>
       </c>
       <c r="P130" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -27979,7 +27997,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q131">
         <v>3.4</v>
@@ -28060,7 +28078,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ131">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR131">
         <v>1.59</v>
@@ -28391,7 +28409,7 @@
         <v>135</v>
       </c>
       <c r="P133" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28803,7 +28821,7 @@
         <v>175</v>
       </c>
       <c r="P135" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29009,7 +29027,7 @@
         <v>176</v>
       </c>
       <c r="P136" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q136">
         <v>1.95</v>
@@ -29166,6 +29184,830 @@
       </c>
       <c r="BP136">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7776452</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45747.60416666666</v>
+      </c>
+      <c r="F137">
+        <v>28</v>
+      </c>
+      <c r="G137" t="s">
+        <v>73</v>
+      </c>
+      <c r="H137" t="s">
+        <v>72</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
+      </c>
+      <c r="K137">
+        <v>2</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="M137">
+        <v>1</v>
+      </c>
+      <c r="N137">
+        <v>2</v>
+      </c>
+      <c r="O137" t="s">
+        <v>177</v>
+      </c>
+      <c r="P137" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q137">
+        <v>3.4</v>
+      </c>
+      <c r="R137">
+        <v>2.1</v>
+      </c>
+      <c r="S137">
+        <v>2.88</v>
+      </c>
+      <c r="T137">
+        <v>1.4</v>
+      </c>
+      <c r="U137">
+        <v>2.75</v>
+      </c>
+      <c r="V137">
+        <v>3</v>
+      </c>
+      <c r="W137">
+        <v>1.36</v>
+      </c>
+      <c r="X137">
+        <v>7</v>
+      </c>
+      <c r="Y137">
+        <v>1.08</v>
+      </c>
+      <c r="Z137">
+        <v>2.98</v>
+      </c>
+      <c r="AA137">
+        <v>3.3</v>
+      </c>
+      <c r="AB137">
+        <v>2.32</v>
+      </c>
+      <c r="AC137">
+        <v>1.01</v>
+      </c>
+      <c r="AD137">
+        <v>8.5</v>
+      </c>
+      <c r="AE137">
+        <v>1.25</v>
+      </c>
+      <c r="AF137">
+        <v>3.28</v>
+      </c>
+      <c r="AG137">
+        <v>1.89</v>
+      </c>
+      <c r="AH137">
+        <v>1.85</v>
+      </c>
+      <c r="AI137">
+        <v>1.73</v>
+      </c>
+      <c r="AJ137">
+        <v>2</v>
+      </c>
+      <c r="AK137">
+        <v>1.6</v>
+      </c>
+      <c r="AL137">
+        <v>1.3</v>
+      </c>
+      <c r="AM137">
+        <v>1.36</v>
+      </c>
+      <c r="AN137">
+        <v>1.23</v>
+      </c>
+      <c r="AO137">
+        <v>2.15</v>
+      </c>
+      <c r="AP137">
+        <v>1.21</v>
+      </c>
+      <c r="AQ137">
+        <v>2.07</v>
+      </c>
+      <c r="AR137">
+        <v>1.48</v>
+      </c>
+      <c r="AS137">
+        <v>1.8</v>
+      </c>
+      <c r="AT137">
+        <v>3.28</v>
+      </c>
+      <c r="AU137">
+        <v>3</v>
+      </c>
+      <c r="AV137">
+        <v>3</v>
+      </c>
+      <c r="AW137">
+        <v>12</v>
+      </c>
+      <c r="AX137">
+        <v>8</v>
+      </c>
+      <c r="AY137">
+        <v>15</v>
+      </c>
+      <c r="AZ137">
+        <v>11</v>
+      </c>
+      <c r="BA137">
+        <v>6</v>
+      </c>
+      <c r="BB137">
+        <v>4</v>
+      </c>
+      <c r="BC137">
+        <v>10</v>
+      </c>
+      <c r="BD137">
+        <v>2.05</v>
+      </c>
+      <c r="BE137">
+        <v>6.25</v>
+      </c>
+      <c r="BF137">
+        <v>2.13</v>
+      </c>
+      <c r="BG137">
+        <v>1.28</v>
+      </c>
+      <c r="BH137">
+        <v>3.08</v>
+      </c>
+      <c r="BI137">
+        <v>1.52</v>
+      </c>
+      <c r="BJ137">
+        <v>2.24</v>
+      </c>
+      <c r="BK137">
+        <v>1.92</v>
+      </c>
+      <c r="BL137">
+        <v>1.75</v>
+      </c>
+      <c r="BM137">
+        <v>2.49</v>
+      </c>
+      <c r="BN137">
+        <v>1.42</v>
+      </c>
+      <c r="BO137">
+        <v>3.42</v>
+      </c>
+      <c r="BP137">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7776454</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45747.60416666666</v>
+      </c>
+      <c r="F138">
+        <v>28</v>
+      </c>
+      <c r="G138" t="s">
+        <v>70</v>
+      </c>
+      <c r="H138" t="s">
+        <v>71</v>
+      </c>
+      <c r="I138">
+        <v>2</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>3</v>
+      </c>
+      <c r="L138">
+        <v>6</v>
+      </c>
+      <c r="M138">
+        <v>2</v>
+      </c>
+      <c r="N138">
+        <v>8</v>
+      </c>
+      <c r="O138" t="s">
+        <v>178</v>
+      </c>
+      <c r="P138" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q138">
+        <v>2.4</v>
+      </c>
+      <c r="R138">
+        <v>2.25</v>
+      </c>
+      <c r="S138">
+        <v>4</v>
+      </c>
+      <c r="T138">
+        <v>1.33</v>
+      </c>
+      <c r="U138">
+        <v>3.25</v>
+      </c>
+      <c r="V138">
+        <v>2.63</v>
+      </c>
+      <c r="W138">
+        <v>1.44</v>
+      </c>
+      <c r="X138">
+        <v>6</v>
+      </c>
+      <c r="Y138">
+        <v>1.11</v>
+      </c>
+      <c r="Z138">
+        <v>1.88</v>
+      </c>
+      <c r="AA138">
+        <v>3.67</v>
+      </c>
+      <c r="AB138">
+        <v>3.78</v>
+      </c>
+      <c r="AC138">
+        <v>1.01</v>
+      </c>
+      <c r="AD138">
+        <v>11</v>
+      </c>
+      <c r="AE138">
+        <v>1.16</v>
+      </c>
+      <c r="AF138">
+        <v>4.05</v>
+      </c>
+      <c r="AG138">
+        <v>1.7</v>
+      </c>
+      <c r="AH138">
+        <v>1.95</v>
+      </c>
+      <c r="AI138">
+        <v>1.67</v>
+      </c>
+      <c r="AJ138">
+        <v>2.1</v>
+      </c>
+      <c r="AK138">
+        <v>1.27</v>
+      </c>
+      <c r="AL138">
+        <v>1.27</v>
+      </c>
+      <c r="AM138">
+        <v>1.83</v>
+      </c>
+      <c r="AN138">
+        <v>1.38</v>
+      </c>
+      <c r="AO138">
+        <v>1.31</v>
+      </c>
+      <c r="AP138">
+        <v>1.5</v>
+      </c>
+      <c r="AQ138">
+        <v>1.21</v>
+      </c>
+      <c r="AR138">
+        <v>1.52</v>
+      </c>
+      <c r="AS138">
+        <v>1.25</v>
+      </c>
+      <c r="AT138">
+        <v>2.77</v>
+      </c>
+      <c r="AU138">
+        <v>11</v>
+      </c>
+      <c r="AV138">
+        <v>3</v>
+      </c>
+      <c r="AW138">
+        <v>9</v>
+      </c>
+      <c r="AX138">
+        <v>7</v>
+      </c>
+      <c r="AY138">
+        <v>20</v>
+      </c>
+      <c r="AZ138">
+        <v>10</v>
+      </c>
+      <c r="BA138">
+        <v>3</v>
+      </c>
+      <c r="BB138">
+        <v>8</v>
+      </c>
+      <c r="BC138">
+        <v>11</v>
+      </c>
+      <c r="BD138">
+        <v>1.62</v>
+      </c>
+      <c r="BE138">
+        <v>6.55</v>
+      </c>
+      <c r="BF138">
+        <v>2.88</v>
+      </c>
+      <c r="BG138">
+        <v>1.21</v>
+      </c>
+      <c r="BH138">
+        <v>3.58</v>
+      </c>
+      <c r="BI138">
+        <v>1.41</v>
+      </c>
+      <c r="BJ138">
+        <v>2.52</v>
+      </c>
+      <c r="BK138">
+        <v>1.75</v>
+      </c>
+      <c r="BL138">
+        <v>1.92</v>
+      </c>
+      <c r="BM138">
+        <v>2.21</v>
+      </c>
+      <c r="BN138">
+        <v>1.53</v>
+      </c>
+      <c r="BO138">
+        <v>2.92</v>
+      </c>
+      <c r="BP138">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7776453</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45747.63541666666</v>
+      </c>
+      <c r="F139">
+        <v>28</v>
+      </c>
+      <c r="G139" t="s">
+        <v>77</v>
+      </c>
+      <c r="H139" t="s">
+        <v>76</v>
+      </c>
+      <c r="I139">
+        <v>2</v>
+      </c>
+      <c r="J139">
+        <v>1</v>
+      </c>
+      <c r="K139">
+        <v>3</v>
+      </c>
+      <c r="L139">
+        <v>2</v>
+      </c>
+      <c r="M139">
+        <v>1</v>
+      </c>
+      <c r="N139">
+        <v>3</v>
+      </c>
+      <c r="O139" t="s">
+        <v>179</v>
+      </c>
+      <c r="P139" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q139">
+        <v>2.3</v>
+      </c>
+      <c r="R139">
+        <v>2.3</v>
+      </c>
+      <c r="S139">
+        <v>4.33</v>
+      </c>
+      <c r="T139">
+        <v>1.33</v>
+      </c>
+      <c r="U139">
+        <v>3.25</v>
+      </c>
+      <c r="V139">
+        <v>2.5</v>
+      </c>
+      <c r="W139">
+        <v>1.5</v>
+      </c>
+      <c r="X139">
+        <v>6</v>
+      </c>
+      <c r="Y139">
+        <v>1.11</v>
+      </c>
+      <c r="Z139">
+        <v>1.77</v>
+      </c>
+      <c r="AA139">
+        <v>3.95</v>
+      </c>
+      <c r="AB139">
+        <v>3.97</v>
+      </c>
+      <c r="AC139">
+        <v>1.01</v>
+      </c>
+      <c r="AD139">
+        <v>11.5</v>
+      </c>
+      <c r="AE139">
+        <v>1.16</v>
+      </c>
+      <c r="AF139">
+        <v>4.1</v>
+      </c>
+      <c r="AG139">
+        <v>1.65</v>
+      </c>
+      <c r="AH139">
+        <v>2.05</v>
+      </c>
+      <c r="AI139">
+        <v>1.67</v>
+      </c>
+      <c r="AJ139">
+        <v>2.1</v>
+      </c>
+      <c r="AK139">
+        <v>1.23</v>
+      </c>
+      <c r="AL139">
+        <v>1.25</v>
+      </c>
+      <c r="AM139">
+        <v>1.98</v>
+      </c>
+      <c r="AN139">
+        <v>2.15</v>
+      </c>
+      <c r="AO139">
+        <v>0.77</v>
+      </c>
+      <c r="AP139">
+        <v>2.21</v>
+      </c>
+      <c r="AQ139">
+        <v>0.71</v>
+      </c>
+      <c r="AR139">
+        <v>1.58</v>
+      </c>
+      <c r="AS139">
+        <v>1.31</v>
+      </c>
+      <c r="AT139">
+        <v>2.89</v>
+      </c>
+      <c r="AU139">
+        <v>5</v>
+      </c>
+      <c r="AV139">
+        <v>4</v>
+      </c>
+      <c r="AW139">
+        <v>6</v>
+      </c>
+      <c r="AX139">
+        <v>5</v>
+      </c>
+      <c r="AY139">
+        <v>11</v>
+      </c>
+      <c r="AZ139">
+        <v>9</v>
+      </c>
+      <c r="BA139">
+        <v>3</v>
+      </c>
+      <c r="BB139">
+        <v>4</v>
+      </c>
+      <c r="BC139">
+        <v>7</v>
+      </c>
+      <c r="BD139">
+        <v>1.48</v>
+      </c>
+      <c r="BE139">
+        <v>8.4</v>
+      </c>
+      <c r="BF139">
+        <v>3.1</v>
+      </c>
+      <c r="BG139">
+        <v>1.3</v>
+      </c>
+      <c r="BH139">
+        <v>2.97</v>
+      </c>
+      <c r="BI139">
+        <v>1.56</v>
+      </c>
+      <c r="BJ139">
+        <v>2.16</v>
+      </c>
+      <c r="BK139">
+        <v>1.98</v>
+      </c>
+      <c r="BL139">
+        <v>1.7</v>
+      </c>
+      <c r="BM139">
+        <v>2.59</v>
+      </c>
+      <c r="BN139">
+        <v>1.39</v>
+      </c>
+      <c r="BO139">
+        <v>3.58</v>
+      </c>
+      <c r="BP139">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7776455</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45747.63541666666</v>
+      </c>
+      <c r="F140">
+        <v>28</v>
+      </c>
+      <c r="G140" t="s">
+        <v>75</v>
+      </c>
+      <c r="H140" t="s">
+        <v>79</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>1</v>
+      </c>
+      <c r="L140">
+        <v>3</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>3</v>
+      </c>
+      <c r="O140" t="s">
+        <v>180</v>
+      </c>
+      <c r="P140" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q140">
+        <v>3.5</v>
+      </c>
+      <c r="R140">
+        <v>2.2</v>
+      </c>
+      <c r="S140">
+        <v>2.63</v>
+      </c>
+      <c r="T140">
+        <v>1.33</v>
+      </c>
+      <c r="U140">
+        <v>3.25</v>
+      </c>
+      <c r="V140">
+        <v>2.63</v>
+      </c>
+      <c r="W140">
+        <v>1.44</v>
+      </c>
+      <c r="X140">
+        <v>6</v>
+      </c>
+      <c r="Y140">
+        <v>1.11</v>
+      </c>
+      <c r="Z140">
+        <v>3.23</v>
+      </c>
+      <c r="AA140">
+        <v>3.55</v>
+      </c>
+      <c r="AB140">
+        <v>2.09</v>
+      </c>
+      <c r="AC140">
+        <v>1.01</v>
+      </c>
+      <c r="AD140">
+        <v>12</v>
+      </c>
+      <c r="AE140">
+        <v>1.18</v>
+      </c>
+      <c r="AF140">
+        <v>3.94</v>
+      </c>
+      <c r="AG140">
+        <v>1.67</v>
+      </c>
+      <c r="AH140">
+        <v>2</v>
+      </c>
+      <c r="AI140">
+        <v>1.62</v>
+      </c>
+      <c r="AJ140">
+        <v>2.2</v>
+      </c>
+      <c r="AK140">
+        <v>1.75</v>
+      </c>
+      <c r="AL140">
+        <v>1.27</v>
+      </c>
+      <c r="AM140">
+        <v>1.3</v>
+      </c>
+      <c r="AN140">
+        <v>1.31</v>
+      </c>
+      <c r="AO140">
+        <v>1.77</v>
+      </c>
+      <c r="AP140">
+        <v>1.43</v>
+      </c>
+      <c r="AQ140">
+        <v>1.64</v>
+      </c>
+      <c r="AR140">
+        <v>1.67</v>
+      </c>
+      <c r="AS140">
+        <v>1.76</v>
+      </c>
+      <c r="AT140">
+        <v>3.43</v>
+      </c>
+      <c r="AU140">
+        <v>6</v>
+      </c>
+      <c r="AV140">
+        <v>2</v>
+      </c>
+      <c r="AW140">
+        <v>12</v>
+      </c>
+      <c r="AX140">
+        <v>2</v>
+      </c>
+      <c r="AY140">
+        <v>18</v>
+      </c>
+      <c r="AZ140">
+        <v>4</v>
+      </c>
+      <c r="BA140">
+        <v>2</v>
+      </c>
+      <c r="BB140">
+        <v>2</v>
+      </c>
+      <c r="BC140">
+        <v>4</v>
+      </c>
+      <c r="BD140">
+        <v>2.36</v>
+      </c>
+      <c r="BE140">
+        <v>6.25</v>
+      </c>
+      <c r="BF140">
+        <v>1.87</v>
+      </c>
+      <c r="BG140">
+        <v>1.27</v>
+      </c>
+      <c r="BH140">
+        <v>3.14</v>
+      </c>
+      <c r="BI140">
+        <v>1.5</v>
+      </c>
+      <c r="BJ140">
+        <v>2.28</v>
+      </c>
+      <c r="BK140">
+        <v>1.88</v>
+      </c>
+      <c r="BL140">
+        <v>1.78</v>
+      </c>
+      <c r="BM140">
+        <v>2.43</v>
+      </c>
+      <c r="BN140">
+        <v>1.44</v>
+      </c>
+      <c r="BO140">
+        <v>3.34</v>
+      </c>
+      <c r="BP140">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="265">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -807,6 +807,9 @@
   <si>
     <t>['20', '49']</t>
   </si>
+  <si>
+    <t>['16', '35', '90']</t>
+  </si>
 </sst>
 </file>
 
@@ -1167,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP140"/>
+  <dimension ref="A1:BP141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3149,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ10">
         <v>2.07</v>
@@ -3358,7 +3361,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ11">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -5209,7 +5212,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ20">
         <v>0.71</v>
@@ -5418,7 +5421,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ21">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR21">
         <v>1.63</v>
@@ -5621,7 +5624,7 @@
         <v>1.5</v>
       </c>
       <c r="AP22">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ22">
         <v>1.07</v>
@@ -6654,7 +6657,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ27">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR27">
         <v>1.47</v>
@@ -8917,7 +8920,7 @@
         <v>2.33</v>
       </c>
       <c r="AP38">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ38">
         <v>1.64</v>
@@ -9538,7 +9541,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ41">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR41">
         <v>1.58</v>
@@ -11392,7 +11395,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ50">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR50">
         <v>1.24</v>
@@ -11595,7 +11598,7 @@
         <v>0.8</v>
       </c>
       <c r="AP51">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ51">
         <v>1.29</v>
@@ -13449,10 +13452,10 @@
         <v>0.4</v>
       </c>
       <c r="AP60">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ60">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR60">
         <v>1.75</v>
@@ -14276,7 +14279,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ64">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR64">
         <v>1.41</v>
@@ -15715,7 +15718,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ71">
         <v>1.21</v>
@@ -17363,7 +17366,7 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ79">
         <v>1.14</v>
@@ -17572,7 +17575,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ80">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR80">
         <v>1.62</v>
@@ -18602,7 +18605,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ85">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -19629,7 +19632,7 @@
         <v>1.13</v>
       </c>
       <c r="AP90">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ90">
         <v>0.93</v>
@@ -20456,7 +20459,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ94">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR94">
         <v>1.69</v>
@@ -21277,7 +21280,7 @@
         <v>1.33</v>
       </c>
       <c r="AP98">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ98">
         <v>1.07</v>
@@ -23134,7 +23137,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ107">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR107">
         <v>1.57</v>
@@ -23955,7 +23958,7 @@
         <v>0.9</v>
       </c>
       <c r="AP111">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ111">
         <v>0.71</v>
@@ -24985,7 +24988,7 @@
         <v>1.73</v>
       </c>
       <c r="AP116">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ116">
         <v>1.64</v>
@@ -26018,7 +26021,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ121">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR121">
         <v>1.63</v>
@@ -26430,7 +26433,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ123">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR123">
         <v>1.49</v>
@@ -28075,7 +28078,7 @@
         <v>2.25</v>
       </c>
       <c r="AP131">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ131">
         <v>2.07</v>
@@ -30008,6 +30011,212 @@
       </c>
       <c r="BP140">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7776456</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45748.60416666666</v>
+      </c>
+      <c r="F141">
+        <v>28</v>
+      </c>
+      <c r="G141" t="s">
+        <v>78</v>
+      </c>
+      <c r="H141" t="s">
+        <v>74</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>2</v>
+      </c>
+      <c r="K141">
+        <v>2</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>3</v>
+      </c>
+      <c r="N141">
+        <v>3</v>
+      </c>
+      <c r="O141" t="s">
+        <v>84</v>
+      </c>
+      <c r="P141" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q141">
+        <v>2.63</v>
+      </c>
+      <c r="R141">
+        <v>2.2</v>
+      </c>
+      <c r="S141">
+        <v>3.6</v>
+      </c>
+      <c r="T141">
+        <v>1.33</v>
+      </c>
+      <c r="U141">
+        <v>3.25</v>
+      </c>
+      <c r="V141">
+        <v>2.63</v>
+      </c>
+      <c r="W141">
+        <v>1.44</v>
+      </c>
+      <c r="X141">
+        <v>6</v>
+      </c>
+      <c r="Y141">
+        <v>1.11</v>
+      </c>
+      <c r="Z141">
+        <v>2.11</v>
+      </c>
+      <c r="AA141">
+        <v>3.47</v>
+      </c>
+      <c r="AB141">
+        <v>3.23</v>
+      </c>
+      <c r="AC141">
+        <v>1.01</v>
+      </c>
+      <c r="AD141">
+        <v>11.5</v>
+      </c>
+      <c r="AE141">
+        <v>1.18</v>
+      </c>
+      <c r="AF141">
+        <v>3.9</v>
+      </c>
+      <c r="AG141">
+        <v>1.67</v>
+      </c>
+      <c r="AH141">
+        <v>2</v>
+      </c>
+      <c r="AI141">
+        <v>1.62</v>
+      </c>
+      <c r="AJ141">
+        <v>2.2</v>
+      </c>
+      <c r="AK141">
+        <v>1.32</v>
+      </c>
+      <c r="AL141">
+        <v>1.29</v>
+      </c>
+      <c r="AM141">
+        <v>1.68</v>
+      </c>
+      <c r="AN141">
+        <v>1.38</v>
+      </c>
+      <c r="AO141">
+        <v>0.77</v>
+      </c>
+      <c r="AP141">
+        <v>1.29</v>
+      </c>
+      <c r="AQ141">
+        <v>0.93</v>
+      </c>
+      <c r="AR141">
+        <v>1.57</v>
+      </c>
+      <c r="AS141">
+        <v>1.28</v>
+      </c>
+      <c r="AT141">
+        <v>2.85</v>
+      </c>
+      <c r="AU141">
+        <v>4</v>
+      </c>
+      <c r="AV141">
+        <v>4</v>
+      </c>
+      <c r="AW141">
+        <v>5</v>
+      </c>
+      <c r="AX141">
+        <v>5</v>
+      </c>
+      <c r="AY141">
+        <v>9</v>
+      </c>
+      <c r="AZ141">
+        <v>9</v>
+      </c>
+      <c r="BA141">
+        <v>5</v>
+      </c>
+      <c r="BB141">
+        <v>6</v>
+      </c>
+      <c r="BC141">
+        <v>11</v>
+      </c>
+      <c r="BD141">
+        <v>1.69</v>
+      </c>
+      <c r="BE141">
+        <v>6.15</v>
+      </c>
+      <c r="BF141">
+        <v>2.75</v>
+      </c>
+      <c r="BG141">
+        <v>1.41</v>
+      </c>
+      <c r="BH141">
+        <v>2.52</v>
+      </c>
+      <c r="BI141">
+        <v>1.77</v>
+      </c>
+      <c r="BJ141">
+        <v>1.9</v>
+      </c>
+      <c r="BK141">
+        <v>2.28</v>
+      </c>
+      <c r="BL141">
+        <v>1.5</v>
+      </c>
+      <c r="BM141">
+        <v>3.08</v>
+      </c>
+      <c r="BN141">
+        <v>1.28</v>
+      </c>
+      <c r="BO141">
+        <v>0</v>
+      </c>
+      <c r="BP141">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="269">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -559,6 +559,12 @@
     <t>['17', '56', '90+1']</t>
   </si>
   <si>
+    <t>['41', '48', '66']</t>
+  </si>
+  <si>
+    <t>['64', '65']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -809,6 +815,12 @@
   </si>
   <si>
     <t>['16', '35', '90']</t>
+  </si>
+  <si>
+    <t>['16', '66']</t>
+  </si>
+  <si>
+    <t>['25', '28']</t>
   </si>
 </sst>
 </file>
@@ -1170,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP141"/>
+  <dimension ref="A1:BP144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1426,7 +1438,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1507,7 +1519,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1632,7 +1644,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1838,7 +1850,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -1916,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4">
         <v>1.64</v>
@@ -2125,7 +2137,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ5">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2537,7 +2549,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ7">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2662,7 +2674,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2740,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ8">
         <v>0.93</v>
@@ -3074,7 +3086,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3358,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ11">
         <v>0.93</v>
@@ -3486,7 +3498,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3564,10 +3576,10 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ12">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR12">
         <v>1.34</v>
@@ -3692,7 +3704,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3770,10 +3782,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ13">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR13">
         <v>1.92</v>
@@ -3898,7 +3910,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3976,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14">
         <v>1.07</v>
@@ -4104,7 +4116,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4310,7 +4322,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4391,7 +4403,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ16">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR16">
         <v>1.95</v>
@@ -4516,7 +4528,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4722,7 +4734,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4928,7 +4940,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5134,7 +5146,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5340,7 +5352,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5752,7 +5764,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5833,7 +5845,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ23">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR23">
         <v>1.3</v>
@@ -6036,7 +6048,7 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
         <v>1.14</v>
@@ -6164,7 +6176,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6245,7 +6257,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ25">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR25">
         <v>1.92</v>
@@ -6370,7 +6382,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6448,7 +6460,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ26">
         <v>0.71</v>
@@ -6576,7 +6588,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6782,7 +6794,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6860,10 +6872,10 @@
         <v>0.33</v>
       </c>
       <c r="AP28">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ28">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR28">
         <v>1.43</v>
@@ -7069,7 +7081,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ29">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR29">
         <v>1.46</v>
@@ -7194,7 +7206,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7400,7 +7412,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7478,7 +7490,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ31">
         <v>0.93</v>
@@ -7687,7 +7699,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ32">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -7812,7 +7824,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7890,7 +7902,7 @@
         <v>1.33</v>
       </c>
       <c r="AP33">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ33">
         <v>1.14</v>
@@ -8018,7 +8030,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8224,7 +8236,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8302,7 +8314,7 @@
         <v>1.33</v>
       </c>
       <c r="AP35">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ35">
         <v>0.93</v>
@@ -8430,7 +8442,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8636,7 +8648,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -9048,7 +9060,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9126,10 +9138,10 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ39">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR39">
         <v>1.16</v>
@@ -9254,7 +9266,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9335,7 +9347,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ40">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR40">
         <v>1.35</v>
@@ -9666,7 +9678,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9872,7 +9884,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9953,7 +9965,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ43">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR43">
         <v>1.64</v>
@@ -10078,7 +10090,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10156,7 +10168,7 @@
         <v>1.67</v>
       </c>
       <c r="AP44">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ44">
         <v>2.07</v>
@@ -10362,7 +10374,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ45">
         <v>1.07</v>
@@ -10490,7 +10502,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10696,7 +10708,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10777,7 +10789,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR47">
         <v>1.79</v>
@@ -11108,7 +11120,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11392,7 +11404,7 @@
         <v>0.25</v>
       </c>
       <c r="AP50">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ50">
         <v>0.93</v>
@@ -11520,7 +11532,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11601,7 +11613,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ51">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR51">
         <v>1.86</v>
@@ -11726,7 +11738,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11932,7 +11944,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12010,10 +12022,10 @@
         <v>0.8</v>
       </c>
       <c r="AP53">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ53">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR53">
         <v>1.54</v>
@@ -12138,7 +12150,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12344,7 +12356,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12756,7 +12768,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12837,7 +12849,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ57">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR57">
         <v>1.74</v>
@@ -13040,7 +13052,7 @@
         <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58">
         <v>0.71</v>
@@ -13168,7 +13180,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13580,7 +13592,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13658,10 +13670,10 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ61">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -13786,7 +13798,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13867,7 +13879,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ62">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR62">
         <v>1.61</v>
@@ -14198,7 +14210,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14610,7 +14622,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14688,7 +14700,7 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ66">
         <v>1.64</v>
@@ -14816,7 +14828,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15022,7 +15034,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15228,7 +15240,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15434,7 +15446,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15512,7 +15524,7 @@
         <v>1.67</v>
       </c>
       <c r="AP70">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ70">
         <v>1.14</v>
@@ -15640,7 +15652,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15721,7 +15733,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ71">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR71">
         <v>1.83</v>
@@ -15846,7 +15858,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -16052,7 +16064,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16258,7 +16270,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16336,10 +16348,10 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ74">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR74">
         <v>1.53</v>
@@ -16464,7 +16476,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16670,7 +16682,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16751,7 +16763,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ76">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR76">
         <v>1.84</v>
@@ -16876,7 +16888,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16954,7 +16966,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ77">
         <v>2.07</v>
@@ -17082,7 +17094,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17288,7 +17300,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17572,7 +17584,7 @@
         <v>0.57</v>
       </c>
       <c r="AP80">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ80">
         <v>0.93</v>
@@ -17778,7 +17790,7 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ81">
         <v>1.07</v>
@@ -17906,7 +17918,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -17984,10 +17996,10 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ82">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR82">
         <v>1.78</v>
@@ -18193,7 +18205,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ83">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR83">
         <v>1.62</v>
@@ -18396,10 +18408,10 @@
         <v>0.86</v>
       </c>
       <c r="AP84">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR84">
         <v>1.62</v>
@@ -18524,7 +18536,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18936,7 +18948,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19142,7 +19154,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19348,7 +19360,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19554,7 +19566,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19760,7 +19772,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19841,7 +19853,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ91">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR91">
         <v>1.62</v>
@@ -19966,7 +19978,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20044,7 +20056,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ92">
         <v>2.07</v>
@@ -20172,7 +20184,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20253,7 +20265,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ93">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR93">
         <v>1.57</v>
@@ -20378,7 +20390,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20456,7 +20468,7 @@
         <v>0.89</v>
       </c>
       <c r="AP94">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ94">
         <v>0.93</v>
@@ -20665,7 +20677,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ95">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR95">
         <v>1.4</v>
@@ -20790,7 +20802,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21614,7 +21626,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21692,7 +21704,7 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ100">
         <v>0.93</v>
@@ -21901,7 +21913,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ101">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR101">
         <v>1.64</v>
@@ -22026,7 +22038,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22104,10 +22116,10 @@
         <v>1.1</v>
       </c>
       <c r="AP102">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ102">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR102">
         <v>1.56</v>
@@ -22232,7 +22244,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22438,7 +22450,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22725,7 +22737,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ105">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR105">
         <v>1.9</v>
@@ -22928,7 +22940,7 @@
         <v>1.2</v>
       </c>
       <c r="AP106">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ106">
         <v>0.93</v>
@@ -23546,7 +23558,7 @@
         <v>1.9</v>
       </c>
       <c r="AP109">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ109">
         <v>1.64</v>
@@ -23674,7 +23686,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23755,7 +23767,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ110">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -23880,7 +23892,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -24164,10 +24176,10 @@
         <v>1.36</v>
       </c>
       <c r="AP112">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ112">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR112">
         <v>1.63</v>
@@ -24292,7 +24304,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24910,7 +24922,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -25116,7 +25128,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q117">
         <v>2.42</v>
@@ -25197,7 +25209,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ117">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR117">
         <v>1.73</v>
@@ -25322,7 +25334,7 @@
         <v>165</v>
       </c>
       <c r="P118" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q118">
         <v>1.82</v>
@@ -25400,7 +25412,7 @@
         <v>0.82</v>
       </c>
       <c r="AP118">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ118">
         <v>0.71</v>
@@ -25606,10 +25618,10 @@
         <v>1.27</v>
       </c>
       <c r="AP119">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ119">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR119">
         <v>1.51</v>
@@ -25734,7 +25746,7 @@
         <v>167</v>
       </c>
       <c r="P120" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q120">
         <v>2.9</v>
@@ -25940,7 +25952,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -26146,7 +26158,7 @@
         <v>84</v>
       </c>
       <c r="P122" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q122">
         <v>4.14</v>
@@ -26224,7 +26236,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ122">
         <v>1.14</v>
@@ -26636,7 +26648,7 @@
         <v>1.25</v>
       </c>
       <c r="AP124">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ124">
         <v>1.07</v>
@@ -26764,7 +26776,7 @@
         <v>84</v>
       </c>
       <c r="P125" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q125">
         <v>2.88</v>
@@ -26845,7 +26857,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ125">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR125">
         <v>1.44</v>
@@ -26970,7 +26982,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q126">
         <v>2.26</v>
@@ -27048,10 +27060,10 @@
         <v>1.25</v>
       </c>
       <c r="AP126">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ126">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR126">
         <v>1.75</v>
@@ -27382,7 +27394,7 @@
         <v>84</v>
       </c>
       <c r="P128" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27463,7 +27475,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ128">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR128">
         <v>1.73</v>
@@ -27794,7 +27806,7 @@
         <v>172</v>
       </c>
       <c r="P130" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28000,7 +28012,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q131">
         <v>3.4</v>
@@ -28284,7 +28296,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ132">
         <v>0.93</v>
@@ -28412,7 +28424,7 @@
         <v>135</v>
       </c>
       <c r="P133" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28493,7 +28505,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ133">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR133">
         <v>1.51</v>
@@ -28699,7 +28711,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ134">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR134">
         <v>1.85</v>
@@ -28824,7 +28836,7 @@
         <v>175</v>
       </c>
       <c r="P135" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -28902,7 +28914,7 @@
         <v>1.15</v>
       </c>
       <c r="AP135">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ135">
         <v>1.14</v>
@@ -29030,7 +29042,7 @@
         <v>176</v>
       </c>
       <c r="P136" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q136">
         <v>1.95</v>
@@ -29108,7 +29120,7 @@
         <v>1.15</v>
       </c>
       <c r="AP136">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ136">
         <v>1.07</v>
@@ -29236,7 +29248,7 @@
         <v>177</v>
       </c>
       <c r="P137" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29442,7 +29454,7 @@
         <v>178</v>
       </c>
       <c r="P138" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29523,7 +29535,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ138">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR138">
         <v>1.52</v>
@@ -30060,7 +30072,7 @@
         <v>84</v>
       </c>
       <c r="P141" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q141">
         <v>2.63</v>
@@ -30217,6 +30229,624 @@
       </c>
       <c r="BP141">
         <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7776459</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45751.60416666666</v>
+      </c>
+      <c r="F142">
+        <v>29</v>
+      </c>
+      <c r="G142" t="s">
+        <v>76</v>
+      </c>
+      <c r="H142" t="s">
+        <v>78</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>2</v>
+      </c>
+      <c r="N142">
+        <v>2</v>
+      </c>
+      <c r="O142" t="s">
+        <v>84</v>
+      </c>
+      <c r="P142" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q142">
+        <v>3.4</v>
+      </c>
+      <c r="R142">
+        <v>2.2</v>
+      </c>
+      <c r="S142">
+        <v>2.88</v>
+      </c>
+      <c r="T142">
+        <v>1.36</v>
+      </c>
+      <c r="U142">
+        <v>3</v>
+      </c>
+      <c r="V142">
+        <v>2.63</v>
+      </c>
+      <c r="W142">
+        <v>1.44</v>
+      </c>
+      <c r="X142">
+        <v>6.5</v>
+      </c>
+      <c r="Y142">
+        <v>1.1</v>
+      </c>
+      <c r="Z142">
+        <v>3.21</v>
+      </c>
+      <c r="AA142">
+        <v>3.45</v>
+      </c>
+      <c r="AB142">
+        <v>2.13</v>
+      </c>
+      <c r="AC142">
+        <v>1.02</v>
+      </c>
+      <c r="AD142">
+        <v>10</v>
+      </c>
+      <c r="AE142">
+        <v>1.21</v>
+      </c>
+      <c r="AF142">
+        <v>3.58</v>
+      </c>
+      <c r="AG142">
+        <v>1.77</v>
+      </c>
+      <c r="AH142">
+        <v>1.98</v>
+      </c>
+      <c r="AI142">
+        <v>1.67</v>
+      </c>
+      <c r="AJ142">
+        <v>2.1</v>
+      </c>
+      <c r="AK142">
+        <v>1.61</v>
+      </c>
+      <c r="AL142">
+        <v>1.3</v>
+      </c>
+      <c r="AM142">
+        <v>1.39</v>
+      </c>
+      <c r="AN142">
+        <v>1.14</v>
+      </c>
+      <c r="AO142">
+        <v>1.29</v>
+      </c>
+      <c r="AP142">
+        <v>1.07</v>
+      </c>
+      <c r="AQ142">
+        <v>1.4</v>
+      </c>
+      <c r="AR142">
+        <v>1.59</v>
+      </c>
+      <c r="AS142">
+        <v>1.42</v>
+      </c>
+      <c r="AT142">
+        <v>3.01</v>
+      </c>
+      <c r="AU142">
+        <v>4</v>
+      </c>
+      <c r="AV142">
+        <v>4</v>
+      </c>
+      <c r="AW142">
+        <v>6</v>
+      </c>
+      <c r="AX142">
+        <v>5</v>
+      </c>
+      <c r="AY142">
+        <v>10</v>
+      </c>
+      <c r="AZ142">
+        <v>9</v>
+      </c>
+      <c r="BA142">
+        <v>11</v>
+      </c>
+      <c r="BB142">
+        <v>4</v>
+      </c>
+      <c r="BC142">
+        <v>15</v>
+      </c>
+      <c r="BD142">
+        <v>2.28</v>
+      </c>
+      <c r="BE142">
+        <v>6</v>
+      </c>
+      <c r="BF142">
+        <v>1.95</v>
+      </c>
+      <c r="BG142">
+        <v>1.46</v>
+      </c>
+      <c r="BH142">
+        <v>2.56</v>
+      </c>
+      <c r="BI142">
+        <v>1.79</v>
+      </c>
+      <c r="BJ142">
+        <v>2</v>
+      </c>
+      <c r="BK142">
+        <v>2.21</v>
+      </c>
+      <c r="BL142">
+        <v>1.62</v>
+      </c>
+      <c r="BM142">
+        <v>3.04</v>
+      </c>
+      <c r="BN142">
+        <v>1.29</v>
+      </c>
+      <c r="BO142">
+        <v>0</v>
+      </c>
+      <c r="BP142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7776461</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45751.63541666666</v>
+      </c>
+      <c r="F143">
+        <v>29</v>
+      </c>
+      <c r="G143" t="s">
+        <v>79</v>
+      </c>
+      <c r="H143" t="s">
+        <v>71</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>1</v>
+      </c>
+      <c r="L143">
+        <v>3</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>3</v>
+      </c>
+      <c r="O143" t="s">
+        <v>181</v>
+      </c>
+      <c r="P143" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q143">
+        <v>1.74</v>
+      </c>
+      <c r="R143">
+        <v>2.46</v>
+      </c>
+      <c r="S143">
+        <v>7.3</v>
+      </c>
+      <c r="T143">
+        <v>1.29</v>
+      </c>
+      <c r="U143">
+        <v>3.26</v>
+      </c>
+      <c r="V143">
+        <v>2.41</v>
+      </c>
+      <c r="W143">
+        <v>1.5</v>
+      </c>
+      <c r="X143">
+        <v>5.65</v>
+      </c>
+      <c r="Y143">
+        <v>1.08</v>
+      </c>
+      <c r="Z143">
+        <v>1.38</v>
+      </c>
+      <c r="AA143">
+        <v>4.8</v>
+      </c>
+      <c r="AB143">
+        <v>7.3</v>
+      </c>
+      <c r="AC143">
+        <v>1.01</v>
+      </c>
+      <c r="AD143">
+        <v>13</v>
+      </c>
+      <c r="AE143">
+        <v>1.15</v>
+      </c>
+      <c r="AF143">
+        <v>4.25</v>
+      </c>
+      <c r="AG143">
+        <v>1.65</v>
+      </c>
+      <c r="AH143">
+        <v>2.05</v>
+      </c>
+      <c r="AI143">
+        <v>2.02</v>
+      </c>
+      <c r="AJ143">
+        <v>1.67</v>
+      </c>
+      <c r="AK143">
+        <v>1.03</v>
+      </c>
+      <c r="AL143">
+        <v>1.12</v>
+      </c>
+      <c r="AM143">
+        <v>3.22</v>
+      </c>
+      <c r="AN143">
+        <v>2.14</v>
+      </c>
+      <c r="AO143">
+        <v>1.21</v>
+      </c>
+      <c r="AP143">
+        <v>2.2</v>
+      </c>
+      <c r="AQ143">
+        <v>1.13</v>
+      </c>
+      <c r="AR143">
+        <v>1.72</v>
+      </c>
+      <c r="AS143">
+        <v>1.25</v>
+      </c>
+      <c r="AT143">
+        <v>2.97</v>
+      </c>
+      <c r="AU143">
+        <v>8</v>
+      </c>
+      <c r="AV143">
+        <v>0</v>
+      </c>
+      <c r="AW143">
+        <v>8</v>
+      </c>
+      <c r="AX143">
+        <v>12</v>
+      </c>
+      <c r="AY143">
+        <v>16</v>
+      </c>
+      <c r="AZ143">
+        <v>12</v>
+      </c>
+      <c r="BA143">
+        <v>4</v>
+      </c>
+      <c r="BB143">
+        <v>0</v>
+      </c>
+      <c r="BC143">
+        <v>4</v>
+      </c>
+      <c r="BD143">
+        <v>1.21</v>
+      </c>
+      <c r="BE143">
+        <v>10.5</v>
+      </c>
+      <c r="BF143">
+        <v>5.1</v>
+      </c>
+      <c r="BG143">
+        <v>1.22</v>
+      </c>
+      <c r="BH143">
+        <v>3.5</v>
+      </c>
+      <c r="BI143">
+        <v>1.48</v>
+      </c>
+      <c r="BJ143">
+        <v>2.55</v>
+      </c>
+      <c r="BK143">
+        <v>1.83</v>
+      </c>
+      <c r="BL143">
+        <v>1.97</v>
+      </c>
+      <c r="BM143">
+        <v>2.31</v>
+      </c>
+      <c r="BN143">
+        <v>1.58</v>
+      </c>
+      <c r="BO143">
+        <v>2.97</v>
+      </c>
+      <c r="BP143">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7776457</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45751.63541666666</v>
+      </c>
+      <c r="F144">
+        <v>29</v>
+      </c>
+      <c r="G144" t="s">
+        <v>72</v>
+      </c>
+      <c r="H144" t="s">
+        <v>75</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>2</v>
+      </c>
+      <c r="K144">
+        <v>2</v>
+      </c>
+      <c r="L144">
+        <v>2</v>
+      </c>
+      <c r="M144">
+        <v>2</v>
+      </c>
+      <c r="N144">
+        <v>4</v>
+      </c>
+      <c r="O144" t="s">
+        <v>182</v>
+      </c>
+      <c r="P144" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q144">
+        <v>2.25</v>
+      </c>
+      <c r="R144">
+        <v>2.26</v>
+      </c>
+      <c r="S144">
+        <v>4.35</v>
+      </c>
+      <c r="T144">
+        <v>1.3</v>
+      </c>
+      <c r="U144">
+        <v>3.2</v>
+      </c>
+      <c r="V144">
+        <v>2.44</v>
+      </c>
+      <c r="W144">
+        <v>1.49</v>
+      </c>
+      <c r="X144">
+        <v>5.55</v>
+      </c>
+      <c r="Y144">
+        <v>1.08</v>
+      </c>
+      <c r="Z144">
+        <v>1.78</v>
+      </c>
+      <c r="AA144">
+        <v>3.8</v>
+      </c>
+      <c r="AB144">
+        <v>4.1</v>
+      </c>
+      <c r="AC144">
+        <v>1.01</v>
+      </c>
+      <c r="AD144">
+        <v>11</v>
+      </c>
+      <c r="AE144">
+        <v>1.16</v>
+      </c>
+      <c r="AF144">
+        <v>4.05</v>
+      </c>
+      <c r="AG144">
+        <v>1.79</v>
+      </c>
+      <c r="AH144">
+        <v>1.95</v>
+      </c>
+      <c r="AI144">
+        <v>1.6</v>
+      </c>
+      <c r="AJ144">
+        <v>2.14</v>
+      </c>
+      <c r="AK144">
+        <v>1.2</v>
+      </c>
+      <c r="AL144">
+        <v>1.22</v>
+      </c>
+      <c r="AM144">
+        <v>1.94</v>
+      </c>
+      <c r="AN144">
+        <v>1.71</v>
+      </c>
+      <c r="AO144">
+        <v>1.29</v>
+      </c>
+      <c r="AP144">
+        <v>1.67</v>
+      </c>
+      <c r="AQ144">
+        <v>1.27</v>
+      </c>
+      <c r="AR144">
+        <v>1.53</v>
+      </c>
+      <c r="AS144">
+        <v>1.65</v>
+      </c>
+      <c r="AT144">
+        <v>3.18</v>
+      </c>
+      <c r="AU144">
+        <v>6</v>
+      </c>
+      <c r="AV144">
+        <v>8</v>
+      </c>
+      <c r="AW144">
+        <v>8</v>
+      </c>
+      <c r="AX144">
+        <v>9</v>
+      </c>
+      <c r="AY144">
+        <v>14</v>
+      </c>
+      <c r="AZ144">
+        <v>17</v>
+      </c>
+      <c r="BA144">
+        <v>3</v>
+      </c>
+      <c r="BB144">
+        <v>3</v>
+      </c>
+      <c r="BC144">
+        <v>6</v>
+      </c>
+      <c r="BD144">
+        <v>1.69</v>
+      </c>
+      <c r="BE144">
+        <v>8.1</v>
+      </c>
+      <c r="BF144">
+        <v>2.48</v>
+      </c>
+      <c r="BG144">
+        <v>1.27</v>
+      </c>
+      <c r="BH144">
+        <v>3.14</v>
+      </c>
+      <c r="BI144">
+        <v>1.58</v>
+      </c>
+      <c r="BJ144">
+        <v>2.3</v>
+      </c>
+      <c r="BK144">
+        <v>1.97</v>
+      </c>
+      <c r="BL144">
+        <v>1.83</v>
+      </c>
+      <c r="BM144">
+        <v>2.5</v>
+      </c>
+      <c r="BN144">
+        <v>1.49</v>
+      </c>
+      <c r="BO144">
+        <v>3.34</v>
+      </c>
+      <c r="BP144">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="270">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -563,6 +563,9 @@
   </si>
   <si>
     <t>['64', '65']</t>
+  </si>
+  <si>
+    <t>['11', '27', '58', '61', '76', '82', '84']</t>
   </si>
   <si>
     <t>['25', '90+2']</t>
@@ -1182,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP144"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1438,7 +1441,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1644,7 +1647,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1850,7 +1853,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2674,7 +2677,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2755,7 +2758,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ8">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2958,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ9">
         <v>1.07</v>
@@ -3086,7 +3089,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3498,7 +3501,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3704,7 +3707,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3910,7 +3913,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4116,7 +4119,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4322,7 +4325,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4528,7 +4531,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4734,7 +4737,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4812,7 +4815,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ18">
         <v>1.64</v>
@@ -4940,7 +4943,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5021,7 +5024,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ19">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR19">
         <v>1.52</v>
@@ -5146,7 +5149,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5352,7 +5355,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5764,7 +5767,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6176,7 +6179,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6382,7 +6385,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6588,7 +6591,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6794,7 +6797,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7078,7 +7081,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ29">
         <v>1.4</v>
@@ -7206,7 +7209,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7412,7 +7415,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7493,7 +7496,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ31">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR31">
         <v>1.17</v>
@@ -7824,7 +7827,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -8030,7 +8033,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8236,7 +8239,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8317,7 +8320,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ35">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR35">
         <v>1.63</v>
@@ -8442,7 +8445,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8648,7 +8651,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -9060,7 +9063,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9266,7 +9269,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9550,7 +9553,7 @@
         <v>0.33</v>
       </c>
       <c r="AP41">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ41">
         <v>0.93</v>
@@ -9678,7 +9681,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9884,7 +9887,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10090,7 +10093,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10502,7 +10505,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10583,7 +10586,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ46">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR46">
         <v>2</v>
@@ -10708,7 +10711,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11120,7 +11123,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11198,7 +11201,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ49">
         <v>0.71</v>
@@ -11532,7 +11535,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11738,7 +11741,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11944,7 +11947,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12150,7 +12153,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12356,7 +12359,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12437,7 +12440,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ55">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR55">
         <v>1.41</v>
@@ -12768,7 +12771,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12846,7 +12849,7 @@
         <v>0.83</v>
       </c>
       <c r="AP57">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ57">
         <v>1.27</v>
@@ -13180,7 +13183,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13592,7 +13595,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13798,7 +13801,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -14085,7 +14088,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ63">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR63">
         <v>1.59</v>
@@ -14210,7 +14213,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14494,7 +14497,7 @@
         <v>2.2</v>
       </c>
       <c r="AP65">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ65">
         <v>2.07</v>
@@ -14622,7 +14625,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14828,7 +14831,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15034,7 +15037,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15240,7 +15243,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15446,7 +15449,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15652,7 +15655,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15858,7 +15861,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15936,10 +15939,10 @@
         <v>1.14</v>
       </c>
       <c r="AP72">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ72">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR72">
         <v>1.68</v>
@@ -16064,7 +16067,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16270,7 +16273,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16476,7 +16479,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16682,7 +16685,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16888,7 +16891,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17094,7 +17097,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17300,7 +17303,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17918,7 +17921,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18202,7 +18205,7 @@
         <v>1.38</v>
       </c>
       <c r="AP83">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ83">
         <v>1.13</v>
@@ -18536,7 +18539,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18948,7 +18951,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19154,7 +19157,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19360,7 +19363,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19566,7 +19569,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19647,7 +19650,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ90">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -19772,7 +19775,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19978,7 +19981,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20184,7 +20187,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20262,7 +20265,7 @@
         <v>1.22</v>
       </c>
       <c r="AP93">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ93">
         <v>1.4</v>
@@ -20390,7 +20393,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20802,7 +20805,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21626,7 +21629,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -21707,7 +21710,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ100">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR100">
         <v>1.58</v>
@@ -22038,7 +22041,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22244,7 +22247,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22322,7 +22325,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ103">
         <v>1.07</v>
@@ -22450,7 +22453,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22943,7 +22946,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ106">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR106">
         <v>1.72</v>
@@ -23686,7 +23689,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23892,7 +23895,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -24304,7 +24307,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24922,7 +24925,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -25128,7 +25131,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q117">
         <v>2.42</v>
@@ -25334,7 +25337,7 @@
         <v>165</v>
       </c>
       <c r="P118" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q118">
         <v>1.82</v>
@@ -25746,7 +25749,7 @@
         <v>167</v>
       </c>
       <c r="P120" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q120">
         <v>2.9</v>
@@ -25827,7 +25830,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ120">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR120">
         <v>1.5</v>
@@ -25952,7 +25955,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -26030,7 +26033,7 @@
         <v>0.82</v>
       </c>
       <c r="AP121">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ121">
         <v>0.93</v>
@@ -26158,7 +26161,7 @@
         <v>84</v>
       </c>
       <c r="P122" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q122">
         <v>4.14</v>
@@ -26776,7 +26779,7 @@
         <v>84</v>
       </c>
       <c r="P125" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q125">
         <v>2.88</v>
@@ -26982,7 +26985,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q126">
         <v>2.26</v>
@@ -27266,7 +27269,7 @@
         <v>1.83</v>
       </c>
       <c r="AP127">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ127">
         <v>1.64</v>
@@ -27394,7 +27397,7 @@
         <v>84</v>
       </c>
       <c r="P128" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27806,7 +27809,7 @@
         <v>172</v>
       </c>
       <c r="P130" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -27887,7 +27890,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ130">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR130">
         <v>1.86</v>
@@ -28012,7 +28015,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q131">
         <v>3.4</v>
@@ -28299,7 +28302,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ132">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR132">
         <v>1.6</v>
@@ -28424,7 +28427,7 @@
         <v>135</v>
       </c>
       <c r="P133" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28836,7 +28839,7 @@
         <v>175</v>
       </c>
       <c r="P135" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29042,7 +29045,7 @@
         <v>176</v>
       </c>
       <c r="P136" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q136">
         <v>1.95</v>
@@ -29248,7 +29251,7 @@
         <v>177</v>
       </c>
       <c r="P137" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29454,7 +29457,7 @@
         <v>178</v>
       </c>
       <c r="P138" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29738,7 +29741,7 @@
         <v>0.77</v>
       </c>
       <c r="AP139">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ139">
         <v>0.71</v>
@@ -30072,7 +30075,7 @@
         <v>84</v>
       </c>
       <c r="P141" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q141">
         <v>2.63</v>
@@ -30278,7 +30281,7 @@
         <v>84</v>
       </c>
       <c r="P142" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q142">
         <v>3.4</v>
@@ -30690,7 +30693,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -30847,6 +30850,212 @@
       </c>
       <c r="BP144">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7776458</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45752.54166666666</v>
+      </c>
+      <c r="F145">
+        <v>29</v>
+      </c>
+      <c r="G145" t="s">
+        <v>77</v>
+      </c>
+      <c r="H145" t="s">
+        <v>73</v>
+      </c>
+      <c r="I145">
+        <v>2</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>2</v>
+      </c>
+      <c r="L145">
+        <v>7</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>7</v>
+      </c>
+      <c r="O145" t="s">
+        <v>183</v>
+      </c>
+      <c r="P145" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q145">
+        <v>3</v>
+      </c>
+      <c r="R145">
+        <v>2.05</v>
+      </c>
+      <c r="S145">
+        <v>3.5</v>
+      </c>
+      <c r="T145">
+        <v>1.44</v>
+      </c>
+      <c r="U145">
+        <v>2.63</v>
+      </c>
+      <c r="V145">
+        <v>3.25</v>
+      </c>
+      <c r="W145">
+        <v>1.33</v>
+      </c>
+      <c r="X145">
+        <v>7.5</v>
+      </c>
+      <c r="Y145">
+        <v>1.07</v>
+      </c>
+      <c r="Z145">
+        <v>2.3</v>
+      </c>
+      <c r="AA145">
+        <v>3.1</v>
+      </c>
+      <c r="AB145">
+        <v>2.95</v>
+      </c>
+      <c r="AC145">
+        <v>1</v>
+      </c>
+      <c r="AD145">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE145">
+        <v>1.32</v>
+      </c>
+      <c r="AF145">
+        <v>3.36</v>
+      </c>
+      <c r="AG145">
+        <v>1.95</v>
+      </c>
+      <c r="AH145">
+        <v>1.7</v>
+      </c>
+      <c r="AI145">
+        <v>1.83</v>
+      </c>
+      <c r="AJ145">
+        <v>1.83</v>
+      </c>
+      <c r="AK145">
+        <v>1.28</v>
+      </c>
+      <c r="AL145">
+        <v>1.28</v>
+      </c>
+      <c r="AM145">
+        <v>1.65</v>
+      </c>
+      <c r="AN145">
+        <v>2.21</v>
+      </c>
+      <c r="AO145">
+        <v>0.93</v>
+      </c>
+      <c r="AP145">
+        <v>2.27</v>
+      </c>
+      <c r="AQ145">
+        <v>0.87</v>
+      </c>
+      <c r="AR145">
+        <v>1.59</v>
+      </c>
+      <c r="AS145">
+        <v>1.59</v>
+      </c>
+      <c r="AT145">
+        <v>3.18</v>
+      </c>
+      <c r="AU145">
+        <v>10</v>
+      </c>
+      <c r="AV145">
+        <v>2</v>
+      </c>
+      <c r="AW145">
+        <v>8</v>
+      </c>
+      <c r="AX145">
+        <v>9</v>
+      </c>
+      <c r="AY145">
+        <v>18</v>
+      </c>
+      <c r="AZ145">
+        <v>11</v>
+      </c>
+      <c r="BA145">
+        <v>6</v>
+      </c>
+      <c r="BB145">
+        <v>1</v>
+      </c>
+      <c r="BC145">
+        <v>7</v>
+      </c>
+      <c r="BD145">
+        <v>2.03</v>
+      </c>
+      <c r="BE145">
+        <v>5.95</v>
+      </c>
+      <c r="BF145">
+        <v>2.19</v>
+      </c>
+      <c r="BG145">
+        <v>1.44</v>
+      </c>
+      <c r="BH145">
+        <v>2.42</v>
+      </c>
+      <c r="BI145">
+        <v>1.83</v>
+      </c>
+      <c r="BJ145">
+        <v>1.83</v>
+      </c>
+      <c r="BK145">
+        <v>2.35</v>
+      </c>
+      <c r="BL145">
+        <v>1.47</v>
+      </c>
+      <c r="BM145">
+        <v>3.28</v>
+      </c>
+      <c r="BN145">
+        <v>1.25</v>
+      </c>
+      <c r="BO145">
+        <v>0</v>
+      </c>
+      <c r="BP145">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="271">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -566,6 +566,9 @@
   </si>
   <si>
     <t>['11', '27', '58', '61', '76', '82', '84']</t>
+  </si>
+  <si>
+    <t>['40', '88']</t>
   </si>
   <si>
     <t>['25', '90+2']</t>
@@ -1185,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1441,7 +1444,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1647,7 +1650,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1853,7 +1856,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -2343,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>0.71</v>
@@ -2677,7 +2680,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2964,7 +2967,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ9">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3089,7 +3092,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -3501,7 +3504,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3707,7 +3710,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3913,7 +3916,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3994,7 +3997,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ14">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>1.19</v>
@@ -4119,7 +4122,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4325,7 +4328,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4403,7 +4406,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.4</v>
@@ -4531,7 +4534,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4737,7 +4740,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4943,7 +4946,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -5149,7 +5152,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5355,7 +5358,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5642,7 +5645,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ22">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>1.91</v>
@@ -5767,7 +5770,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6179,7 +6182,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6257,7 +6260,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>1.27</v>
@@ -6385,7 +6388,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6591,7 +6594,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6797,7 +6800,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -7209,7 +7212,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7415,7 +7418,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7827,7 +7830,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -8033,7 +8036,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8114,7 +8117,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ34">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.52</v>
@@ -8239,7 +8242,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8445,7 +8448,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8523,7 +8526,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>2.07</v>
@@ -8651,7 +8654,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -9063,7 +9066,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9269,7 +9272,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9681,7 +9684,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9887,7 +9890,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10093,7 +10096,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10380,7 +10383,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ45">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>1.73</v>
@@ -10505,7 +10508,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10583,7 +10586,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.87</v>
@@ -10711,7 +10714,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11123,7 +11126,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11535,7 +11538,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11741,7 +11744,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11947,7 +11950,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12153,7 +12156,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12359,7 +12362,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12643,7 +12646,7 @@
         <v>1.8</v>
       </c>
       <c r="AP56">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
         <v>1.64</v>
@@ -12771,7 +12774,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13183,7 +13186,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13264,7 +13267,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ59">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.44</v>
@@ -13595,7 +13598,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13801,7 +13804,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -14213,7 +14216,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14625,7 +14628,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14831,7 +14834,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15037,7 +15040,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15115,10 +15118,10 @@
         <v>1.5</v>
       </c>
       <c r="AP68">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15243,7 +15246,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15449,7 +15452,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15655,7 +15658,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15861,7 +15864,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -16067,7 +16070,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -16273,7 +16276,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16479,7 +16482,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16560,7 +16563,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ75">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>1.68</v>
@@ -16685,7 +16688,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16763,7 +16766,7 @@
         <v>1.43</v>
       </c>
       <c r="AP76">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ76">
         <v>1.13</v>
@@ -16891,7 +16894,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17097,7 +17100,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17303,7 +17306,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17796,7 +17799,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ81">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.63</v>
@@ -17921,7 +17924,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -18539,7 +18542,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18951,7 +18954,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19157,7 +19160,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19363,7 +19366,7 @@
         <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q89">
         <v>3.2</v>
@@ -19441,7 +19444,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ89">
         <v>1.14</v>
@@ -19569,7 +19572,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q90">
         <v>2.6</v>
@@ -19775,7 +19778,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19981,7 +19984,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20187,7 +20190,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20393,7 +20396,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20805,7 +20808,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q96">
         <v>3.75</v>
@@ -21298,7 +21301,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ98">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR98">
         <v>1.61</v>
@@ -21501,7 +21504,7 @@
         <v>0.89</v>
       </c>
       <c r="AP99">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ99">
         <v>0.71</v>
@@ -21629,7 +21632,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q100">
         <v>2.2</v>
@@ -22041,7 +22044,7 @@
         <v>84</v>
       </c>
       <c r="P102" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q102">
         <v>2.97</v>
@@ -22247,7 +22250,7 @@
         <v>155</v>
       </c>
       <c r="P103" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q103">
         <v>2.36</v>
@@ -22328,7 +22331,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ103">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR103">
         <v>1.61</v>
@@ -22453,7 +22456,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q104">
         <v>2.99</v>
@@ -22737,7 +22740,7 @@
         <v>1.2</v>
       </c>
       <c r="AP105">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ105">
         <v>1.4</v>
@@ -23689,7 +23692,7 @@
         <v>84</v>
       </c>
       <c r="P110" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q110">
         <v>3.3</v>
@@ -23895,7 +23898,7 @@
         <v>160</v>
       </c>
       <c r="P111" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q111">
         <v>2.32</v>
@@ -24307,7 +24310,7 @@
         <v>162</v>
       </c>
       <c r="P113" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -24388,7 +24391,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ113">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24797,7 +24800,7 @@
         <v>2.18</v>
       </c>
       <c r="AP115">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ115">
         <v>2.07</v>
@@ -24925,7 +24928,7 @@
         <v>163</v>
       </c>
       <c r="P116" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q116">
         <v>3.6</v>
@@ -25131,7 +25134,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q117">
         <v>2.42</v>
@@ -25337,7 +25340,7 @@
         <v>165</v>
       </c>
       <c r="P118" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q118">
         <v>1.82</v>
@@ -25749,7 +25752,7 @@
         <v>167</v>
       </c>
       <c r="P120" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q120">
         <v>2.9</v>
@@ -25955,7 +25958,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -26161,7 +26164,7 @@
         <v>84</v>
       </c>
       <c r="P122" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q122">
         <v>4.14</v>
@@ -26654,7 +26657,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ124">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>1.52</v>
@@ -26779,7 +26782,7 @@
         <v>84</v>
       </c>
       <c r="P125" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q125">
         <v>2.88</v>
@@ -26985,7 +26988,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q126">
         <v>2.26</v>
@@ -27397,7 +27400,7 @@
         <v>84</v>
       </c>
       <c r="P128" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27809,7 +27812,7 @@
         <v>172</v>
       </c>
       <c r="P130" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -27887,7 +27890,7 @@
         <v>1.08</v>
       </c>
       <c r="AP130">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ130">
         <v>0.87</v>
@@ -28015,7 +28018,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q131">
         <v>3.4</v>
@@ -28427,7 +28430,7 @@
         <v>135</v>
       </c>
       <c r="P133" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28711,7 +28714,7 @@
         <v>1.15</v>
       </c>
       <c r="AP134">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>1.27</v>
@@ -28839,7 +28842,7 @@
         <v>175</v>
       </c>
       <c r="P135" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29045,7 +29048,7 @@
         <v>176</v>
       </c>
       <c r="P136" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q136">
         <v>1.95</v>
@@ -29126,7 +29129,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ136">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -29251,7 +29254,7 @@
         <v>177</v>
       </c>
       <c r="P137" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29457,7 +29460,7 @@
         <v>178</v>
       </c>
       <c r="P138" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30075,7 +30078,7 @@
         <v>84</v>
       </c>
       <c r="P141" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q141">
         <v>2.63</v>
@@ -30281,7 +30284,7 @@
         <v>84</v>
       </c>
       <c r="P142" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q142">
         <v>3.4</v>
@@ -30693,7 +30696,7 @@
         <v>182</v>
       </c>
       <c r="P144" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31056,6 +31059,212 @@
       </c>
       <c r="BP145">
         <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7776462</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45753.38541666666</v>
+      </c>
+      <c r="F146">
+        <v>29</v>
+      </c>
+      <c r="G146" t="s">
+        <v>74</v>
+      </c>
+      <c r="H146" t="s">
+        <v>70</v>
+      </c>
+      <c r="I146">
+        <v>1</v>
+      </c>
+      <c r="J146">
+        <v>1</v>
+      </c>
+      <c r="K146">
+        <v>2</v>
+      </c>
+      <c r="L146">
+        <v>2</v>
+      </c>
+      <c r="M146">
+        <v>1</v>
+      </c>
+      <c r="N146">
+        <v>3</v>
+      </c>
+      <c r="O146" t="s">
+        <v>184</v>
+      </c>
+      <c r="P146" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q146">
+        <v>2.58</v>
+      </c>
+      <c r="R146">
+        <v>2.47</v>
+      </c>
+      <c r="S146">
+        <v>3.59</v>
+      </c>
+      <c r="T146">
+        <v>1.24</v>
+      </c>
+      <c r="U146">
+        <v>3.48</v>
+      </c>
+      <c r="V146">
+        <v>2.29</v>
+      </c>
+      <c r="W146">
+        <v>1.59</v>
+      </c>
+      <c r="X146">
+        <v>5.55</v>
+      </c>
+      <c r="Y146">
+        <v>1.1</v>
+      </c>
+      <c r="Z146">
+        <v>2.31</v>
+      </c>
+      <c r="AA146">
+        <v>3.5</v>
+      </c>
+      <c r="AB146">
+        <v>2.85</v>
+      </c>
+      <c r="AC146">
+        <v>1</v>
+      </c>
+      <c r="AD146">
+        <v>12</v>
+      </c>
+      <c r="AE146">
+        <v>1.11</v>
+      </c>
+      <c r="AF146">
+        <v>4.8</v>
+      </c>
+      <c r="AG146">
+        <v>1.53</v>
+      </c>
+      <c r="AH146">
+        <v>2.25</v>
+      </c>
+      <c r="AI146">
+        <v>1.47</v>
+      </c>
+      <c r="AJ146">
+        <v>2.42</v>
+      </c>
+      <c r="AK146">
+        <v>1.32</v>
+      </c>
+      <c r="AL146">
+        <v>1.22</v>
+      </c>
+      <c r="AM146">
+        <v>1.67</v>
+      </c>
+      <c r="AN146">
+        <v>1.93</v>
+      </c>
+      <c r="AO146">
+        <v>1.07</v>
+      </c>
+      <c r="AP146">
+        <v>2</v>
+      </c>
+      <c r="AQ146">
+        <v>1</v>
+      </c>
+      <c r="AR146">
+        <v>1.84</v>
+      </c>
+      <c r="AS146">
+        <v>1.62</v>
+      </c>
+      <c r="AT146">
+        <v>3.46</v>
+      </c>
+      <c r="AU146">
+        <v>8</v>
+      </c>
+      <c r="AV146">
+        <v>5</v>
+      </c>
+      <c r="AW146">
+        <v>2</v>
+      </c>
+      <c r="AX146">
+        <v>2</v>
+      </c>
+      <c r="AY146">
+        <v>10</v>
+      </c>
+      <c r="AZ146">
+        <v>7</v>
+      </c>
+      <c r="BA146">
+        <v>4</v>
+      </c>
+      <c r="BB146">
+        <v>1</v>
+      </c>
+      <c r="BC146">
+        <v>5</v>
+      </c>
+      <c r="BD146">
+        <v>1.6</v>
+      </c>
+      <c r="BE146">
+        <v>6.55</v>
+      </c>
+      <c r="BF146">
+        <v>2.94</v>
+      </c>
+      <c r="BG146">
+        <v>1.24</v>
+      </c>
+      <c r="BH146">
+        <v>3.34</v>
+      </c>
+      <c r="BI146">
+        <v>1.52</v>
+      </c>
+      <c r="BJ146">
+        <v>2.44</v>
+      </c>
+      <c r="BK146">
+        <v>1.88</v>
+      </c>
+      <c r="BL146">
+        <v>1.92</v>
+      </c>
+      <c r="BM146">
+        <v>2.38</v>
+      </c>
+      <c r="BN146">
+        <v>1.55</v>
+      </c>
+      <c r="BO146">
+        <v>3.14</v>
+      </c>
+      <c r="BP146">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>
